--- a/input_processing/clean_excel_files_PL/reg_income.xlsx
+++ b/input_processing/clean_excel_files_PL/reg_income.xlsx
@@ -475,7 +475,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="1">
-        <v>7245.6798653212591</v>
+        <v>7245.6798653129981</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>0.57367927939832652</v>
+        <v>0.57367927939832619</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -700,115 +700,115 @@
         <v>29</v>
       </c>
       <c r="B2" s="1">
-        <v>0.018498367075062784</v>
+        <v>0.018498367075062288</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0017548545330585044</v>
+        <v>0.0017548545330584894</v>
       </c>
       <c r="D2" s="1">
-        <v>2.4572087603574754e-06</v>
+        <v>2.4572087603222918e-06</v>
       </c>
       <c r="E2" s="1">
-        <v>-1.9593847293554486e-09</v>
+        <v>-1.9593847289747701e-09</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.00010206918500284338</v>
+        <v>-0.00010206918500249362</v>
       </c>
       <c r="G2" s="1">
-        <v>-1.8035105178842912e-05</v>
+        <v>-1.8035105178769343e-05</v>
       </c>
       <c r="H2" s="1">
-        <v>0.00016264092128566663</v>
+        <v>0.00016264092128573919</v>
       </c>
       <c r="I2" s="1">
-        <v>0.00020680808421588915</v>
+        <v>0.00020680808421594742</v>
       </c>
       <c r="J2" s="1">
-        <v>-8.7153856521272037e-06</v>
+        <v>-8.7153856521252928e-06</v>
       </c>
       <c r="K2" s="1">
-        <v>-3.0440788059787206e-05</v>
+        <v>-3.0440788059822734e-05</v>
       </c>
       <c r="L2" s="1">
-        <v>-2.3162698263293946e-05</v>
+        <v>-2.3162698263257273e-05</v>
       </c>
       <c r="M2" s="1">
-        <v>2.944085734012645e-05</v>
+        <v>2.9440857340126765e-05</v>
       </c>
       <c r="N2" s="1">
-        <v>-0.0018329003487245327</v>
+        <v>-0.0018329003487240825</v>
       </c>
       <c r="O2" s="1">
-        <v>2.0319598118490377e-06</v>
+        <v>2.0319598118562946e-06</v>
       </c>
       <c r="P2" s="1">
-        <v>-9.7676588504064008e-05</v>
+        <v>-9.767658846916232e-05</v>
       </c>
       <c r="Q2" s="1">
-        <v>-0.00026176895267021095</v>
+        <v>-0.00026176895263734824</v>
       </c>
       <c r="R2" s="1">
-        <v>-7.0923232997222127e-05</v>
+        <v>-7.092323296223411e-05</v>
       </c>
       <c r="S2" s="1">
-        <v>0.00014101263549054052</v>
+        <v>0.00014101263552363945</v>
       </c>
       <c r="T2" s="1">
-        <v>9.5117774016051845e-06</v>
+        <v>9.5117774015979779e-06</v>
       </c>
       <c r="U2" s="1">
-        <v>-2.6929279263032234e-06</v>
+        <v>-2.6929279263089595e-06</v>
       </c>
       <c r="V2" s="1">
-        <v>-2.0068735687118123e-05</v>
+        <v>-2.0068735687166926e-05</v>
       </c>
       <c r="W2" s="1">
-        <v>-2.5432879730762264e-05</v>
+        <v>-2.5432879730769972e-05</v>
       </c>
       <c r="X2" s="1">
-        <v>-0.00026348219367271301</v>
+        <v>-0.00026348219363690772</v>
       </c>
       <c r="Y2" s="1">
-        <v>-0.00027818846895300491</v>
+        <v>-0.00027818846891748499</v>
       </c>
       <c r="Z2" s="1">
-        <v>0.00010511101503655053</v>
+        <v>0.00010511101507029488</v>
       </c>
       <c r="AA2" s="1">
-        <v>-0.00015603137491062381</v>
+        <v>-0.00015603137491074513</v>
       </c>
       <c r="AB2" s="1">
-        <v>0.00017693113481951663</v>
+        <v>0.00017693113481946662</v>
       </c>
       <c r="AC2" s="1">
-        <v>0.00019335639665853918</v>
+        <v>0.00019335639665834001</v>
       </c>
       <c r="AD2" s="1">
-        <v>0.00022658984800174789</v>
+        <v>0.00022658984800173011</v>
       </c>
       <c r="AE2" s="1">
-        <v>0.00011484912744162687</v>
+        <v>0.00011484912744158963</v>
       </c>
       <c r="AF2" s="1">
-        <v>0.00069630728065239126</v>
+        <v>0.00069630728065236643</v>
       </c>
       <c r="AG2" s="1">
-        <v>-9.5444803732204248e-06</v>
+        <v>-9.5444803732092575e-06</v>
       </c>
       <c r="AH2" s="1">
-        <v>3.3924509545058812e-05</v>
+        <v>3.3924509545089589e-05</v>
       </c>
       <c r="AI2" s="1">
-        <v>1.9318954850772527e-05</v>
+        <v>1.9318954850809688e-05</v>
       </c>
       <c r="AJ2" s="1">
-        <v>2.5770834566505603e-05</v>
+        <v>2.5770834566524956e-05</v>
       </c>
       <c r="AK2" s="1">
-        <v>-3.994819555932575e-06</v>
+        <v>-3.9948195559330154e-06</v>
       </c>
       <c r="AL2" s="1">
-        <v>-0.00084948509481593416</v>
+        <v>-0.00084948509485140329</v>
       </c>
     </row>
     <row r="3">
@@ -816,115 +816,115 @@
         <v>30</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.0097178948022712593</v>
+        <v>-0.0097178948022726783</v>
       </c>
       <c r="C3" s="1">
-        <v>2.4572087603574754e-06</v>
+        <v>2.4572087603222918e-06</v>
       </c>
       <c r="D3" s="1">
-        <v>7.1246701579470424e-05</v>
+        <v>7.1246701579791646e-05</v>
       </c>
       <c r="E3" s="1">
-        <v>-6.8815950491768523e-07</v>
+        <v>-6.8815950492100877e-07</v>
       </c>
       <c r="F3" s="1">
-        <v>-9.977287556510808e-05</v>
+        <v>-9.9772875566836406e-05</v>
       </c>
       <c r="G3" s="1">
-        <v>-0.00013015492880154967</v>
+        <v>-0.00013015492880210375</v>
       </c>
       <c r="H3" s="1">
-        <v>-0.00016180166485304869</v>
+        <v>-0.00016180166485381595</v>
       </c>
       <c r="I3" s="1">
-        <v>-0.00010930037831665966</v>
+        <v>-0.00010930037831721779</v>
       </c>
       <c r="J3" s="1">
-        <v>1.5620082030994373e-06</v>
+        <v>1.5620082031165677e-06</v>
       </c>
       <c r="K3" s="1">
-        <v>9.2340882560000678e-06</v>
+        <v>9.2340882558352436e-06</v>
       </c>
       <c r="L3" s="1">
-        <v>-1.3374015828804641e-05</v>
+        <v>-1.3374015828743272e-05</v>
       </c>
       <c r="M3" s="1">
-        <v>-4.7617717177342688e-06</v>
+        <v>-4.7617717177425494e-06</v>
       </c>
       <c r="N3" s="1">
-        <v>2.4916074500750096e-05</v>
+        <v>2.4916074499971313e-05</v>
       </c>
       <c r="O3" s="1">
-        <v>-1.3442204499456174e-06</v>
+        <v>-1.3442204499919734e-06</v>
       </c>
       <c r="P3" s="1">
-        <v>6.2318194595786705e-05</v>
+        <v>6.2318194547055774e-05</v>
       </c>
       <c r="Q3" s="1">
-        <v>0.00011241424737369268</v>
+        <v>0.00011241424731644372</v>
       </c>
       <c r="R3" s="1">
-        <v>3.2769385125475873e-05</v>
+        <v>3.2769385073399854e-05</v>
       </c>
       <c r="S3" s="1">
-        <v>-8.5679708139436647e-05</v>
+        <v>-8.567970819804016e-05</v>
       </c>
       <c r="T3" s="1">
-        <v>-1.0907752677686043e-05</v>
+        <v>-1.0907752677580672e-05</v>
       </c>
       <c r="U3" s="1">
-        <v>-7.8494086436863185e-06</v>
+        <v>-7.8494086433453505e-06</v>
       </c>
       <c r="V3" s="1">
-        <v>1.6185001188869622e-05</v>
+        <v>1.6185001189615004e-05</v>
       </c>
       <c r="W3" s="1">
-        <v>6.4068447314234521e-06</v>
+        <v>6.4068447322269229e-06</v>
       </c>
       <c r="X3" s="1">
-        <v>-0.00055454691565844983</v>
+        <v>-0.00055454691573372523</v>
       </c>
       <c r="Y3" s="1">
-        <v>-0.00065869397070566159</v>
+        <v>-0.0006586939707827102</v>
       </c>
       <c r="Z3" s="1">
-        <v>-0.0006313664102661087</v>
+        <v>-0.00063136641034565043</v>
       </c>
       <c r="AA3" s="1">
-        <v>0.00030664793768514015</v>
+        <v>0.00030664793768516319</v>
       </c>
       <c r="AB3" s="1">
-        <v>1.6471746527999335e-05</v>
+        <v>1.6471746527498543e-05</v>
       </c>
       <c r="AC3" s="1">
-        <v>0.00015400732713688288</v>
+        <v>0.00015400732713753294</v>
       </c>
       <c r="AD3" s="1">
-        <v>6.862649303486748e-05</v>
+        <v>6.8626493034722088e-05</v>
       </c>
       <c r="AE3" s="1">
-        <v>0.00017306963129176239</v>
+        <v>0.00017306963129245666</v>
       </c>
       <c r="AF3" s="1">
-        <v>0.00010611991847014912</v>
+        <v>0.00010611991846971224</v>
       </c>
       <c r="AG3" s="1">
-        <v>2.8935186044736372e-05</v>
+        <v>2.8935186044526796e-05</v>
       </c>
       <c r="AH3" s="1">
-        <v>6.9042561322281524e-07</v>
+        <v>6.9042561320218829e-07</v>
       </c>
       <c r="AI3" s="1">
-        <v>1.7512065808804116e-05</v>
+        <v>1.7512065808717326e-05</v>
       </c>
       <c r="AJ3" s="1">
-        <v>2.3881238001463383e-05</v>
+        <v>2.3881238001379845e-05</v>
       </c>
       <c r="AK3" s="1">
-        <v>-2.3471768138907142e-06</v>
+        <v>-2.3471768138588251e-06</v>
       </c>
       <c r="AL3" s="1">
-        <v>-0.00097243503089864184</v>
+        <v>-0.00097243503083369661</v>
       </c>
     </row>
     <row r="4">
@@ -932,115 +932,115 @@
         <v>31</v>
       </c>
       <c r="B4" s="1">
-        <v>8.4679516246601572e-05</v>
+        <v>8.4679516246616182e-05</v>
       </c>
       <c r="C4" s="1">
-        <v>-1.9593847293554486e-09</v>
+        <v>-1.9593847289747701e-09</v>
       </c>
       <c r="D4" s="1">
-        <v>-6.8815950491768523e-07</v>
+        <v>-6.8815950492100877e-07</v>
       </c>
       <c r="E4" s="1">
-        <v>7.075957676629919e-09</v>
+        <v>7.0759576766642627e-09</v>
       </c>
       <c r="F4" s="1">
-        <v>2.698706764103469e-07</v>
+        <v>2.6987067642738242e-07</v>
       </c>
       <c r="G4" s="1">
-        <v>6.5764010419503671e-07</v>
+        <v>6.5764010420083539e-07</v>
       </c>
       <c r="H4" s="1">
-        <v>1.135822632210282e-06</v>
+        <v>1.1358226322182367e-06</v>
       </c>
       <c r="I4" s="1">
-        <v>8.6310795059177224e-07</v>
+        <v>8.6310795059755896e-07</v>
       </c>
       <c r="J4" s="1">
-        <v>-1.7424518882276331e-08</v>
+        <v>-1.7424518882450608e-08</v>
       </c>
       <c r="K4" s="1">
-        <v>-7.9396797980925402e-08</v>
+        <v>-7.9396797979307198e-08</v>
       </c>
       <c r="L4" s="1">
-        <v>1.1250810948001433e-07</v>
+        <v>1.1250810947943124e-07</v>
       </c>
       <c r="M4" s="1">
-        <v>3.9142724579218388e-08</v>
+        <v>3.9142724579313996e-08</v>
       </c>
       <c r="N4" s="1">
-        <v>-2.5903643769748114e-07</v>
+        <v>-2.5903643769020344e-07</v>
       </c>
       <c r="O4" s="1">
-        <v>1.3132480775486905e-08</v>
+        <v>1.3132480775942129e-08</v>
       </c>
       <c r="P4" s="1">
-        <v>-8.0795369675873505e-07</v>
+        <v>-8.0795369630638314e-07</v>
       </c>
       <c r="Q4" s="1">
-        <v>-1.3437543377330105e-06</v>
+        <v>-1.3437543371949023e-06</v>
       </c>
       <c r="R4" s="1">
-        <v>-7.6459609355421659e-07</v>
+        <v>-7.6459609307119774e-07</v>
       </c>
       <c r="S4" s="1">
-        <v>1.6785511279013216e-07</v>
+        <v>1.6785511334203511e-07</v>
       </c>
       <c r="T4" s="1">
-        <v>1.1866416477474847e-07</v>
+        <v>1.1866416477374167e-07</v>
       </c>
       <c r="U4" s="1">
-        <v>6.7766432895908924e-08</v>
+        <v>6.776643289258469e-08</v>
       </c>
       <c r="V4" s="1">
-        <v>-1.5440898339794633e-07</v>
+        <v>-1.5440898340530281e-07</v>
       </c>
       <c r="W4" s="1">
-        <v>-5.0671466925641377e-08</v>
+        <v>-5.0671466933557257e-08</v>
       </c>
       <c r="X4" s="1">
-        <v>4.6713630258071757e-06</v>
+        <v>4.6713630265179465e-06</v>
       </c>
       <c r="Y4" s="1">
-        <v>5.9549460063740453e-06</v>
+        <v>5.9549460071057547e-06</v>
       </c>
       <c r="Z4" s="1">
-        <v>5.7235865045181206e-06</v>
+        <v>5.7235865052717335e-06</v>
       </c>
       <c r="AA4" s="1">
-        <v>-2.3734237045282386e-06</v>
+        <v>-2.3734237045292631e-06</v>
       </c>
       <c r="AB4" s="1">
-        <v>-1.4200885892225273e-07</v>
+        <v>-1.4200885891730547e-07</v>
       </c>
       <c r="AC4" s="1">
-        <v>-2.4700097629126476e-06</v>
+        <v>-2.4700097629193896e-06</v>
       </c>
       <c r="AD4" s="1">
-        <v>-3.4190658259346549e-07</v>
+        <v>-3.4190658259218621e-07</v>
       </c>
       <c r="AE4" s="1">
-        <v>-1.5425722565011119e-06</v>
+        <v>-1.5425722565083636e-06</v>
       </c>
       <c r="AF4" s="1">
-        <v>-6.770993893134014e-07</v>
+        <v>-6.7709938930937333e-07</v>
       </c>
       <c r="AG4" s="1">
-        <v>-2.9554011974343353e-07</v>
+        <v>-2.9554011974143877e-07</v>
       </c>
       <c r="AH4" s="1">
-        <v>-7.1685799009015749e-08</v>
+        <v>-7.168579900884126e-08</v>
       </c>
       <c r="AI4" s="1">
-        <v>-2.1051976594319231e-07</v>
+        <v>-2.1051976594240415e-07</v>
       </c>
       <c r="AJ4" s="1">
-        <v>-2.8661483694152515e-07</v>
+        <v>-2.8661483694076981e-07</v>
       </c>
       <c r="AK4" s="1">
-        <v>1.9677432665468871e-08</v>
+        <v>1.9677432665158857e-08</v>
       </c>
       <c r="AL4" s="1">
-        <v>9.1336556548105908e-06</v>
+        <v>9.1336556542037442e-06</v>
       </c>
     </row>
     <row r="5">
@@ -1048,115 +1048,115 @@
         <v>32</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.27741281192685985</v>
+        <v>-0.27741281192686085</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.00010206918500284338</v>
+        <v>-0.00010206918500249362</v>
       </c>
       <c r="D5" s="1">
-        <v>-9.977287556510808e-05</v>
+        <v>-9.9772875566836406e-05</v>
       </c>
       <c r="E5" s="1">
-        <v>2.698706764103469e-07</v>
+        <v>2.6987067642738242e-07</v>
       </c>
       <c r="F5" s="1">
-        <v>0.022453637163978527</v>
+        <v>0.022453637164003032</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0050791120739594828</v>
+        <v>0.0050791120739673359</v>
       </c>
       <c r="H5" s="1">
-        <v>0.0046290300122653859</v>
+        <v>0.0046290300122740144</v>
       </c>
       <c r="I5" s="1">
-        <v>0.0032899684621230715</v>
+        <v>0.0032899684621289882</v>
       </c>
       <c r="J5" s="1">
-        <v>-5.5718214656657206e-05</v>
+        <v>-5.5718214657025835e-05</v>
       </c>
       <c r="K5" s="1">
-        <v>0.00011559401863519691</v>
+        <v>0.00011559401863542806</v>
       </c>
       <c r="L5" s="1">
-        <v>-7.5971259927617172e-05</v>
+        <v>-7.5971259927412691e-05</v>
       </c>
       <c r="M5" s="1">
-        <v>6.5753103534519058e-06</v>
+        <v>6.5753103537348825e-06</v>
       </c>
       <c r="N5" s="1">
-        <v>0.0001295071869027338</v>
+        <v>0.00012950718691609074</v>
       </c>
       <c r="O5" s="1">
-        <v>7.2280341222147156e-07</v>
+        <v>7.2280341278688564e-07</v>
       </c>
       <c r="P5" s="1">
-        <v>0.017574894910762133</v>
+        <v>0.017574894911781849</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.017683304496518004</v>
+        <v>0.017683304497449783</v>
       </c>
       <c r="R5" s="1">
-        <v>0.018872890395427076</v>
+        <v>0.018872890396459945</v>
       </c>
       <c r="S5" s="1">
-        <v>0.022134298978477449</v>
+        <v>0.022134298979494614</v>
       </c>
       <c r="T5" s="1">
-        <v>0.00011030231493322539</v>
+        <v>0.00011030231493217024</v>
       </c>
       <c r="U5" s="1">
-        <v>-8.6388543875278541e-05</v>
+        <v>-8.638854387795652e-05</v>
       </c>
       <c r="V5" s="1">
-        <v>0.00015029657207344359</v>
+        <v>0.00015029657206438746</v>
       </c>
       <c r="W5" s="1">
-        <v>-3.6740018577273594e-05</v>
+        <v>-3.6740018586093023e-05</v>
       </c>
       <c r="X5" s="1">
-        <v>0.020882061654932102</v>
+        <v>0.0208820616561626</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.021477836863667273</v>
+        <v>0.021477836864862616</v>
       </c>
       <c r="Z5" s="1">
-        <v>0.021653582213319655</v>
+        <v>0.02165358221458355</v>
       </c>
       <c r="AA5" s="1">
-        <v>0.00054615923700245233</v>
+        <v>0.00054615923700768176</v>
       </c>
       <c r="AB5" s="1">
-        <v>-0.00080010563935088144</v>
+        <v>-0.00080010563934895438</v>
       </c>
       <c r="AC5" s="1">
-        <v>-8.0399581780699232e-06</v>
+        <v>-8.0399581794976006e-06</v>
       </c>
       <c r="AD5" s="1">
-        <v>-2.4706411334543565e-05</v>
+        <v>-2.4706411332341008e-05</v>
       </c>
       <c r="AE5" s="1">
-        <v>-0.0004986110511323691</v>
+        <v>-0.00049861105113622193</v>
       </c>
       <c r="AF5" s="1">
-        <v>-0.00075115552716347248</v>
+        <v>-0.00075115552715650062</v>
       </c>
       <c r="AG5" s="1">
-        <v>-0.00016332808938981751</v>
+        <v>-0.0001633280893883985</v>
       </c>
       <c r="AH5" s="1">
-        <v>-0.00021652712268065838</v>
+        <v>-0.00021652712268000482</v>
       </c>
       <c r="AI5" s="1">
-        <v>8.4793944348940734e-05</v>
+        <v>8.4793944350403105e-05</v>
       </c>
       <c r="AJ5" s="1">
-        <v>7.8321520189435917e-05</v>
+        <v>7.8321520190037866e-05</v>
       </c>
       <c r="AK5" s="1">
-        <v>2.6047144065958778e-05</v>
+        <v>2.604714406604443e-05</v>
       </c>
       <c r="AL5" s="1">
-        <v>-0.021192789809307333</v>
+        <v>-0.021192789810487105</v>
       </c>
     </row>
     <row r="6">
@@ -1164,115 +1164,115 @@
         <v>33</v>
       </c>
       <c r="B6" s="1">
-        <v>-0.040428537388344843</v>
+        <v>-0.04042853738834367</v>
       </c>
       <c r="C6" s="1">
-        <v>-1.8035105178842912e-05</v>
+        <v>-1.8035105178769343e-05</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.00013015492880154967</v>
+        <v>-0.00013015492880210375</v>
       </c>
       <c r="E6" s="1">
-        <v>6.5764010419503671e-07</v>
+        <v>6.5764010420083539e-07</v>
       </c>
       <c r="F6" s="1">
-        <v>0.0050791120739594828</v>
+        <v>0.0050791120739673359</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0086458593255994177</v>
+        <v>0.0086458593256012739</v>
       </c>
       <c r="H6" s="1">
-        <v>0.0044771359604882481</v>
+        <v>0.0044771359604904425</v>
       </c>
       <c r="I6" s="1">
-        <v>0.0032971343651619855</v>
+        <v>0.0032971343651634999</v>
       </c>
       <c r="J6" s="1">
-        <v>-1.6522116223343655e-05</v>
+        <v>-1.6522116223434565e-05</v>
       </c>
       <c r="K6" s="1">
-        <v>-1.5886815749693506e-05</v>
+        <v>-1.5886815749459034e-05</v>
       </c>
       <c r="L6" s="1">
-        <v>4.8410575871309317e-05</v>
+        <v>4.8410575871283906e-05</v>
       </c>
       <c r="M6" s="1">
-        <v>1.9236919879593996e-05</v>
+        <v>1.9236919879639695e-05</v>
       </c>
       <c r="N6" s="1">
-        <v>2.5811446687763696e-05</v>
+        <v>2.5811446692939135e-05</v>
       </c>
       <c r="O6" s="1">
-        <v>8.430867523379178e-07</v>
+        <v>8.4308675253676884e-07</v>
       </c>
       <c r="P6" s="1">
-        <v>-0.0025612762142994162</v>
+        <v>-0.0025612762139291569</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.00053931682966464425</v>
+        <v>0.00053931683002650659</v>
       </c>
       <c r="R6" s="1">
-        <v>0.0015151353853942943</v>
+        <v>0.0015151353857721314</v>
       </c>
       <c r="S6" s="1">
-        <v>0.0047959391956321719</v>
+        <v>0.0047959391960137147</v>
       </c>
       <c r="T6" s="1">
-        <v>6.0896170010413605e-05</v>
+        <v>6.0896170009967104e-05</v>
       </c>
       <c r="U6" s="1">
-        <v>4.914285960256896e-05</v>
+        <v>4.914285960145581e-05</v>
       </c>
       <c r="V6" s="1">
-        <v>2.4179731639195287e-05</v>
+        <v>2.4179731636134964e-05</v>
       </c>
       <c r="W6" s="1">
-        <v>-4.5906057484904285e-05</v>
+        <v>-4.5906057487950534e-05</v>
       </c>
       <c r="X6" s="1">
-        <v>0.0034251536520370548</v>
+        <v>0.0034251536524958284</v>
       </c>
       <c r="Y6" s="1">
-        <v>0.0041698235072124478</v>
+        <v>0.0041698235076642462</v>
       </c>
       <c r="Z6" s="1">
-        <v>0.0043141288214769494</v>
+        <v>0.0043141288219489538</v>
       </c>
       <c r="AA6" s="1">
-        <v>0.0004572597289908171</v>
+        <v>0.00045725972899315036</v>
       </c>
       <c r="AB6" s="1">
-        <v>-0.00052467239634628468</v>
+        <v>-0.00052467239634531356</v>
       </c>
       <c r="AC6" s="1">
-        <v>-3.7187003444040675e-05</v>
+        <v>-3.7187003445085195e-05</v>
       </c>
       <c r="AD6" s="1">
-        <v>3.2536224191486354e-05</v>
+        <v>3.2536224192396786e-05</v>
       </c>
       <c r="AE6" s="1">
-        <v>-0.00028498321159713981</v>
+        <v>-0.00028498321159828478</v>
       </c>
       <c r="AF6" s="1">
-        <v>-0.00044609028407857697</v>
+        <v>-0.00044609028407598431</v>
       </c>
       <c r="AG6" s="1">
-        <v>-0.00020161923183942753</v>
+        <v>-0.00020161923183867596</v>
       </c>
       <c r="AH6" s="1">
-        <v>-0.00029782438912136146</v>
+        <v>-0.00029782438912112679</v>
       </c>
       <c r="AI6" s="1">
-        <v>-0.00020969143890345841</v>
+        <v>-0.00020969143890286947</v>
       </c>
       <c r="AJ6" s="1">
-        <v>-5.8569217146796056e-05</v>
+        <v>-5.8569217146417236e-05</v>
       </c>
       <c r="AK6" s="1">
-        <v>2.6997927960038088e-05</v>
+        <v>2.6997927960021554e-05</v>
       </c>
       <c r="AL6" s="1">
-        <v>-0.0034340330730213246</v>
+        <v>-0.0034340330734633265</v>
       </c>
     </row>
     <row r="7">
@@ -1280,115 +1280,115 @@
         <v>34</v>
       </c>
       <c r="B7" s="1">
-        <v>0.039358404159334705</v>
+        <v>0.039358404159336356</v>
       </c>
       <c r="C7" s="1">
-        <v>0.00016264092128566663</v>
+        <v>0.00016264092128573919</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.00016180166485304869</v>
+        <v>-0.00016180166485381595</v>
       </c>
       <c r="E7" s="1">
-        <v>1.135822632210282e-06</v>
+        <v>1.1358226322182367e-06</v>
       </c>
       <c r="F7" s="1">
-        <v>0.0046290300122653859</v>
+        <v>0.0046290300122740144</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0044771359604882481</v>
+        <v>0.0044771359604904425</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0054996371600479861</v>
+        <v>0.0054996371600505509</v>
       </c>
       <c r="I7" s="1">
-        <v>0.0032467702671121887</v>
+        <v>0.0032467702671139741</v>
       </c>
       <c r="J7" s="1">
-        <v>-2.8416412741885287e-05</v>
+        <v>-2.8416412741974137e-05</v>
       </c>
       <c r="K7" s="1">
-        <v>-2.7921769305589995e-06</v>
+        <v>-2.7921769302570695e-06</v>
       </c>
       <c r="L7" s="1">
-        <v>1.7631736137975847e-05</v>
+        <v>1.7631736137938924e-05</v>
       </c>
       <c r="M7" s="1">
-        <v>1.6716946290231064e-05</v>
+        <v>1.6716946290276831e-05</v>
       </c>
       <c r="N7" s="1">
-        <v>-0.00016019986749175706</v>
+        <v>-0.00016019986748625267</v>
       </c>
       <c r="O7" s="1">
-        <v>1.3948236825587661e-06</v>
+        <v>1.3948236827726807e-06</v>
       </c>
       <c r="P7" s="1">
-        <v>0.0002508164567880926</v>
+        <v>0.00025081645717822042</v>
       </c>
       <c r="Q7" s="1">
-        <v>-0.000956487523724678</v>
+        <v>-0.00095648752333873737</v>
       </c>
       <c r="R7" s="1">
-        <v>0.0010384969413550734</v>
+        <v>0.0010384969417520169</v>
       </c>
       <c r="S7" s="1">
-        <v>0.0042723082330759429</v>
+        <v>0.0042723082334802714</v>
       </c>
       <c r="T7" s="1">
-        <v>7.2372875798721974e-05</v>
+        <v>7.237287579824651e-05</v>
       </c>
       <c r="U7" s="1">
-        <v>2.9114204305561339e-05</v>
+        <v>2.9114204304326636e-05</v>
       </c>
       <c r="V7" s="1">
-        <v>5.1972346467689482e-05</v>
+        <v>5.1972346464425003e-05</v>
       </c>
       <c r="W7" s="1">
-        <v>-4.9845849220843882e-05</v>
+        <v>-4.9845849224094022e-05</v>
       </c>
       <c r="X7" s="1">
-        <v>0.0031460719514642089</v>
+        <v>0.0031460719519514468</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.0036037377633782266</v>
+        <v>0.0036037377638609047</v>
       </c>
       <c r="Z7" s="1">
-        <v>0.0040077533179542092</v>
+        <v>0.0040077533184546873</v>
       </c>
       <c r="AA7" s="1">
-        <v>0.00025443491395772092</v>
+        <v>0.00025443491395967232</v>
       </c>
       <c r="AB7" s="1">
-        <v>-0.00017760195287848854</v>
+        <v>-0.00017760195287728657</v>
       </c>
       <c r="AC7" s="1">
-        <v>-0.00016060390037165104</v>
+        <v>-0.00016060390037307161</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.00025297884207914323</v>
+        <v>0.00025297884207999992</v>
       </c>
       <c r="AE7" s="1">
-        <v>-5.3935154648180754e-05</v>
+        <v>-5.3935154649732573e-05</v>
       </c>
       <c r="AF7" s="1">
-        <v>-0.00045170735578779417</v>
+        <v>-0.00045170735578525302</v>
       </c>
       <c r="AG7" s="1">
-        <v>-0.00022568533869324423</v>
+        <v>-0.00022568533869240506</v>
       </c>
       <c r="AH7" s="1">
-        <v>-0.00020708557683970252</v>
+        <v>-0.00020708557683944619</v>
       </c>
       <c r="AI7" s="1">
-        <v>-9.8553689358878279e-05</v>
+        <v>-9.8553689358255731e-05</v>
       </c>
       <c r="AJ7" s="1">
-        <v>-1.340793102954296e-05</v>
+        <v>-1.3407931029119254e-05</v>
       </c>
       <c r="AK7" s="1">
-        <v>8.5736453995748215e-06</v>
+        <v>8.5736453995497223e-06</v>
       </c>
       <c r="AL7" s="1">
-        <v>-0.0024502434910213941</v>
+        <v>-0.0024502434914878378</v>
       </c>
     </row>
     <row r="8">
@@ -1396,115 +1396,115 @@
         <v>35</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.020103424880080174</v>
+        <v>-0.020103424880079202</v>
       </c>
       <c r="C8" s="1">
-        <v>0.00020680808421588915</v>
+        <v>0.00020680808421594742</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.00010930037831665966</v>
+        <v>-0.00010930037831721779</v>
       </c>
       <c r="E8" s="1">
-        <v>8.6310795059177224e-07</v>
+        <v>8.6310795059755896e-07</v>
       </c>
       <c r="F8" s="1">
-        <v>0.0032899684621230715</v>
+        <v>0.0032899684621289882</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0032971343651619855</v>
+        <v>0.0032971343651634999</v>
       </c>
       <c r="H8" s="1">
-        <v>0.0032467702671121887</v>
+        <v>0.0032467702671139741</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0038422385347500251</v>
+        <v>0.003842238534751229</v>
       </c>
       <c r="J8" s="1">
-        <v>-9.0025023866854002e-06</v>
+        <v>-9.0025023867514281e-06</v>
       </c>
       <c r="K8" s="1">
-        <v>1.4464702579939823e-05</v>
+        <v>1.4464702580145225e-05</v>
       </c>
       <c r="L8" s="1">
-        <v>-1.5404459781610198e-05</v>
+        <v>-1.5404459781622948e-05</v>
       </c>
       <c r="M8" s="1">
-        <v>1.4389508425830998e-05</v>
+        <v>1.4389508425868288e-05</v>
       </c>
       <c r="N8" s="1">
-        <v>-0.00012784645723076294</v>
+        <v>-0.00012784645722704798</v>
       </c>
       <c r="O8" s="1">
-        <v>-1.0339770255125495e-06</v>
+        <v>-1.033977025362987e-06</v>
       </c>
       <c r="P8" s="1">
-        <v>5.4960952700438236e-05</v>
+        <v>5.4960952960800876e-05</v>
       </c>
       <c r="Q8" s="1">
-        <v>9.1946761603610666e-05</v>
+        <v>9.1946761864627785e-05</v>
       </c>
       <c r="R8" s="1">
-        <v>-0.00076748884461731227</v>
+        <v>-0.00076748884435072875</v>
       </c>
       <c r="S8" s="1">
-        <v>0.0030241914464016265</v>
+        <v>0.003024191446676117</v>
       </c>
       <c r="T8" s="1">
-        <v>4.5561638979319116e-05</v>
+        <v>4.5561638978989261e-05</v>
       </c>
       <c r="U8" s="1">
-        <v>3.4065995292866807e-05</v>
+        <v>3.4065995292014922e-05</v>
       </c>
       <c r="V8" s="1">
-        <v>0.00011033036714415255</v>
+        <v>0.00011033036714183992</v>
       </c>
       <c r="W8" s="1">
-        <v>-5.2430592832602031e-05</v>
+        <v>-5.2430592834899699e-05</v>
       </c>
       <c r="X8" s="1">
-        <v>0.001180147778312262</v>
+        <v>0.001180147778641697</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.0013848364760086923</v>
+        <v>0.0013848364763364685</v>
       </c>
       <c r="Z8" s="1">
-        <v>0.0016107494537340469</v>
+        <v>0.0016107494540751374</v>
       </c>
       <c r="AA8" s="1">
-        <v>0.00061202778242823647</v>
+        <v>0.00061202778242956885</v>
       </c>
       <c r="AB8" s="1">
-        <v>0.00015327152039843053</v>
+        <v>0.00015327152039929483</v>
       </c>
       <c r="AC8" s="1">
-        <v>0.00011185002130279813</v>
+        <v>0.00011185002130178554</v>
       </c>
       <c r="AD8" s="1">
-        <v>3.9091697350303129e-05</v>
+        <v>3.9091697350918088e-05</v>
       </c>
       <c r="AE8" s="1">
-        <v>-1.0296938046014587e-05</v>
+        <v>-1.0296938047119281e-05</v>
       </c>
       <c r="AF8" s="1">
-        <v>-0.00046364917288914913</v>
+        <v>-0.00046364917288734366</v>
       </c>
       <c r="AG8" s="1">
-        <v>-0.00018088263239688859</v>
+        <v>-0.00018088263239628621</v>
       </c>
       <c r="AH8" s="1">
-        <v>-0.00019226002972683905</v>
+        <v>-0.00019226002972664934</v>
       </c>
       <c r="AI8" s="1">
-        <v>-5.3451448485928232e-05</v>
+        <v>-5.3451448485485661e-05</v>
       </c>
       <c r="AJ8" s="1">
-        <v>-7.5919483127538494e-05</v>
+        <v>-7.5919483127230526e-05</v>
       </c>
       <c r="AK8" s="1">
-        <v>-3.7075244263497958e-06</v>
+        <v>-3.7075244263599602e-06</v>
       </c>
       <c r="AL8" s="1">
-        <v>-0.0014014341750661827</v>
+        <v>-0.0014014341753842178</v>
       </c>
     </row>
     <row r="9">
@@ -1515,112 +1515,112 @@
         <v>0.71529674226040463</v>
       </c>
       <c r="C9" s="1">
-        <v>-8.7153856521272037e-06</v>
+        <v>-8.7153856521252928e-06</v>
       </c>
       <c r="D9" s="1">
-        <v>1.5620082030994373e-06</v>
+        <v>1.5620082031165677e-06</v>
       </c>
       <c r="E9" s="1">
-        <v>-1.7424518882276331e-08</v>
+        <v>-1.7424518882450608e-08</v>
       </c>
       <c r="F9" s="1">
-        <v>-5.5718214656657206e-05</v>
+        <v>-5.5718214657025835e-05</v>
       </c>
       <c r="G9" s="1">
-        <v>-1.6522116223343655e-05</v>
+        <v>-1.6522116223434565e-05</v>
       </c>
       <c r="H9" s="1">
-        <v>-2.8416412741885287e-05</v>
+        <v>-2.8416412741974137e-05</v>
       </c>
       <c r="I9" s="1">
-        <v>-9.0025023866854002e-06</v>
+        <v>-9.0025023867514281e-06</v>
       </c>
       <c r="J9" s="1">
-        <v>0.00018656263612723529</v>
+        <v>0.00018656263612723764</v>
       </c>
       <c r="K9" s="1">
-        <v>3.9316078277207584e-06</v>
+        <v>3.9316078277147665e-06</v>
       </c>
       <c r="L9" s="1">
-        <v>-3.1990838641891013e-06</v>
+        <v>-3.1990838641936693e-06</v>
       </c>
       <c r="M9" s="1">
-        <v>-9.629760596317176e-05</v>
+        <v>-9.6297605963173292e-05</v>
       </c>
       <c r="N9" s="1">
-        <v>6.9230656755237243e-05</v>
+        <v>6.923065675494417e-05</v>
       </c>
       <c r="O9" s="1">
-        <v>-9.0892201845079287e-07</v>
+        <v>-9.0892201845836736e-07</v>
       </c>
       <c r="P9" s="1">
-        <v>-1.5890419950983993e-05</v>
+        <v>-1.5890419972119254e-05</v>
       </c>
       <c r="Q9" s="1">
-        <v>-2.6939425460752069e-05</v>
+        <v>-2.6939425480981272e-05</v>
       </c>
       <c r="R9" s="1">
-        <v>-4.383433273796585e-05</v>
+        <v>-4.3834332758812042e-05</v>
       </c>
       <c r="S9" s="1">
-        <v>-0.00014679834605191787</v>
+        <v>-0.00014679834607250172</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.00017186141713062831</v>
+        <v>-0.00017186141713061039</v>
       </c>
       <c r="U9" s="1">
-        <v>3.2443636863720368e-06</v>
+        <v>3.2443636864150796e-06</v>
       </c>
       <c r="V9" s="1">
-        <v>1.663675364706994e-05</v>
+        <v>1.663675364717527e-05</v>
       </c>
       <c r="W9" s="1">
-        <v>0.0001326808006227672</v>
+        <v>0.00013268080062286484</v>
       </c>
       <c r="X9" s="1">
-        <v>-0.00042837014297512205</v>
+        <v>-0.00042837014299954311</v>
       </c>
       <c r="Y9" s="1">
-        <v>-0.00046011995418190796</v>
+        <v>-0.00046011995420648649</v>
       </c>
       <c r="Z9" s="1">
-        <v>-0.00049233701362342674</v>
+        <v>-0.00049233701364818645</v>
       </c>
       <c r="AA9" s="1">
-        <v>1.9075395905195623e-05</v>
+        <v>1.9075395905088165e-05</v>
       </c>
       <c r="AB9" s="1">
-        <v>-2.3870307439553413e-05</v>
+        <v>-2.3870307439601826e-05</v>
       </c>
       <c r="AC9" s="1">
-        <v>-1.3817399271839829e-05</v>
+        <v>-1.3817399271830618e-05</v>
       </c>
       <c r="AD9" s="1">
-        <v>-1.5691099153444037e-05</v>
+        <v>-1.5691099153479379e-05</v>
       </c>
       <c r="AE9" s="1">
-        <v>-2.4093106921045247e-05</v>
+        <v>-2.4093106921026318e-05</v>
       </c>
       <c r="AF9" s="1">
-        <v>-4.300288743538768e-05</v>
+        <v>-4.3002887435480278e-05</v>
       </c>
       <c r="AG9" s="1">
-        <v>-4.7552776869514134e-05</v>
+        <v>-4.7552776869551302e-05</v>
       </c>
       <c r="AH9" s="1">
-        <v>-3.6164875914466468e-05</v>
+        <v>-3.6164875914483172e-05</v>
       </c>
       <c r="AI9" s="1">
-        <v>-5.690446433278891e-05</v>
+        <v>-5.6904464332823001e-05</v>
       </c>
       <c r="AJ9" s="1">
-        <v>-2.2005824852954966e-05</v>
+        <v>-2.2005824852979811e-05</v>
       </c>
       <c r="AK9" s="1">
-        <v>3.841588999009404e-06</v>
+        <v>3.841588999006552e-06</v>
       </c>
       <c r="AL9" s="1">
-        <v>0.00034126079343411921</v>
+        <v>0.00034126079345844106</v>
       </c>
     </row>
     <row r="10">
@@ -1628,115 +1628,115 @@
         <v>37</v>
       </c>
       <c r="B10" s="1">
-        <v>0.016637559195080996</v>
+        <v>0.016637559195080143</v>
       </c>
       <c r="C10" s="1">
-        <v>-3.0440788059787206e-05</v>
+        <v>-3.0440788059822734e-05</v>
       </c>
       <c r="D10" s="1">
-        <v>9.2340882560000678e-06</v>
+        <v>9.2340882558352436e-06</v>
       </c>
       <c r="E10" s="1">
-        <v>-7.9396797980925402e-08</v>
+        <v>-7.9396797979307198e-08</v>
       </c>
       <c r="F10" s="1">
-        <v>0.00011559401863519691</v>
+        <v>0.00011559401863542806</v>
       </c>
       <c r="G10" s="1">
-        <v>-1.5886815749693506e-05</v>
+        <v>-1.5886815749459034e-05</v>
       </c>
       <c r="H10" s="1">
-        <v>-2.7921769305589995e-06</v>
+        <v>-2.7921769302570695e-06</v>
       </c>
       <c r="I10" s="1">
-        <v>1.4464702579939823e-05</v>
+        <v>1.4464702580145225e-05</v>
       </c>
       <c r="J10" s="1">
-        <v>3.9316078277207584e-06</v>
+        <v>3.9316078277147665e-06</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0002449185721206183</v>
+        <v>0.00024491857212059163</v>
       </c>
       <c r="L10" s="1">
-        <v>-0.00015712448717088921</v>
+        <v>-0.00015712448717085706</v>
       </c>
       <c r="M10" s="1">
-        <v>-1.138054988337054e-05</v>
+        <v>-1.1380549883363547e-05</v>
       </c>
       <c r="N10" s="1">
-        <v>4.1106307505251225e-05</v>
+        <v>4.1106307505336674e-05</v>
       </c>
       <c r="O10" s="1">
-        <v>-1.6570918695660659e-07</v>
+        <v>-1.657091869507452e-07</v>
       </c>
       <c r="P10" s="1">
-        <v>0.00014075649255679398</v>
+        <v>0.00014075649256319777</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.00012461942023962537</v>
+        <v>0.00012461942024397869</v>
       </c>
       <c r="R10" s="1">
-        <v>0.0001109763480569417</v>
+        <v>0.00011097634806405425</v>
       </c>
       <c r="S10" s="1">
-        <v>0.00011726469664380053</v>
+        <v>0.00011726469664914079</v>
       </c>
       <c r="T10" s="1">
-        <v>-5.2278432530244372e-06</v>
+        <v>-5.2278432530070086e-06</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.00024917057608289992</v>
+        <v>-0.00024917057608288393</v>
       </c>
       <c r="V10" s="1">
-        <v>0.00015006452857256277</v>
+        <v>0.00015006452857250298</v>
       </c>
       <c r="W10" s="1">
-        <v>1.82916784940932e-05</v>
+        <v>1.8291678494074247e-05</v>
       </c>
       <c r="X10" s="1">
-        <v>6.8672731479027979e-05</v>
+        <v>6.8672731485651086e-05</v>
       </c>
       <c r="Y10" s="1">
-        <v>1.1433355032000357e-05</v>
+        <v>1.1433355040772746e-05</v>
       </c>
       <c r="Z10" s="1">
-        <v>-1.8126425720113047e-05</v>
+        <v>-1.8126425713237498e-05</v>
       </c>
       <c r="AA10" s="1">
-        <v>0.00064985580312339664</v>
+        <v>0.00064985580312263845</v>
       </c>
       <c r="AB10" s="1">
-        <v>0.00055637960424016948</v>
+        <v>0.00055637960424009087</v>
       </c>
       <c r="AC10" s="1">
-        <v>0.00058622495876161176</v>
+        <v>0.00058622495876110934</v>
       </c>
       <c r="AD10" s="1">
-        <v>1.170422956090962e-05</v>
+        <v>1.1704229560753207e-05</v>
       </c>
       <c r="AE10" s="1">
-        <v>-3.647673240879665e-06</v>
+        <v>-3.6476732412744502e-06</v>
       </c>
       <c r="AF10" s="1">
-        <v>-5.47726219558427e-06</v>
+        <v>-5.477262195828595e-06</v>
       </c>
       <c r="AG10" s="1">
-        <v>3.6931049345794055e-05</v>
+        <v>3.693104934573109e-05</v>
       </c>
       <c r="AH10" s="1">
-        <v>-8.8976663517633994e-06</v>
+        <v>-8.8976663518011432e-06</v>
       </c>
       <c r="AI10" s="1">
-        <v>1.3443650714663468e-05</v>
+        <v>1.3443650714617443e-05</v>
       </c>
       <c r="AJ10" s="1">
-        <v>2.1756948892418958e-05</v>
+        <v>2.1756948892352821e-05</v>
       </c>
       <c r="AK10" s="1">
-        <v>-4.1396484164253931e-07</v>
+        <v>-4.1396484164695066e-07</v>
       </c>
       <c r="AL10" s="1">
-        <v>-0.00087113916615671398</v>
+        <v>-0.00087113916615868452</v>
       </c>
     </row>
     <row r="11">
@@ -1744,115 +1744,115 @@
         <v>38</v>
       </c>
       <c r="B11" s="1">
-        <v>-0.01050569909251535</v>
+        <v>-0.010505699092514519</v>
       </c>
       <c r="C11" s="1">
-        <v>-2.3162698263293946e-05</v>
+        <v>-2.3162698263257273e-05</v>
       </c>
       <c r="D11" s="1">
-        <v>-1.3374015828804641e-05</v>
+        <v>-1.3374015828743272e-05</v>
       </c>
       <c r="E11" s="1">
-        <v>1.1250810948001433e-07</v>
+        <v>1.1250810947943124e-07</v>
       </c>
       <c r="F11" s="1">
-        <v>-7.5971259927617172e-05</v>
+        <v>-7.5971259927412691e-05</v>
       </c>
       <c r="G11" s="1">
-        <v>4.8410575871309317e-05</v>
+        <v>4.8410575871283906e-05</v>
       </c>
       <c r="H11" s="1">
-        <v>1.7631736137975847e-05</v>
+        <v>1.7631736137938924e-05</v>
       </c>
       <c r="I11" s="1">
-        <v>-1.5404459781610198e-05</v>
+        <v>-1.5404459781622948e-05</v>
       </c>
       <c r="J11" s="1">
-        <v>-3.1990838641891013e-06</v>
+        <v>-3.1990838641936693e-06</v>
       </c>
       <c r="K11" s="1">
-        <v>-0.00015712448717088921</v>
+        <v>-0.00015712448717085706</v>
       </c>
       <c r="L11" s="1">
-        <v>0.00018288385837410623</v>
+        <v>0.00018288385837407267</v>
       </c>
       <c r="M11" s="1">
-        <v>8.8057189783537797e-06</v>
+        <v>8.8057189783542438e-06</v>
       </c>
       <c r="N11" s="1">
-        <v>6.0849567422365265e-06</v>
+        <v>6.0849567423139047e-06</v>
       </c>
       <c r="O11" s="1">
-        <v>1.0049198051697741e-07</v>
+        <v>1.0049198052331095e-07</v>
       </c>
       <c r="P11" s="1">
-        <v>-9.8777582017101756e-05</v>
+        <v>-9.8777582012711944e-05</v>
       </c>
       <c r="Q11" s="1">
-        <v>-8.3940790746369411e-05</v>
+        <v>-8.3940790739927624e-05</v>
       </c>
       <c r="R11" s="1">
-        <v>-5.9831030580844121e-05</v>
+        <v>-5.9831030576428112e-05</v>
       </c>
       <c r="S11" s="1">
-        <v>-6.2384645609330974e-05</v>
+        <v>-6.2384645603126085e-05</v>
       </c>
       <c r="T11" s="1">
-        <v>1.5358442570351905e-06</v>
+        <v>1.5358442570040722e-06</v>
       </c>
       <c r="U11" s="1">
-        <v>0.00016166096857994717</v>
+        <v>0.0001616609685798857</v>
       </c>
       <c r="V11" s="1">
-        <v>-0.00017213043765208462</v>
+        <v>-0.00017213043765222413</v>
       </c>
       <c r="W11" s="1">
-        <v>-1.5859190370739438e-05</v>
+        <v>-1.5859190370915997e-05</v>
       </c>
       <c r="X11" s="1">
-        <v>1.5649191214688145e-05</v>
+        <v>1.5649191223885873e-05</v>
       </c>
       <c r="Y11" s="1">
-        <v>5.4963951685436705e-06</v>
+        <v>5.4963951757263616e-06</v>
       </c>
       <c r="Z11" s="1">
-        <v>-8.3347339625704391e-05</v>
+        <v>-8.3347339615637777e-05</v>
       </c>
       <c r="AA11" s="1">
-        <v>-4.1163920117300018e-05</v>
+        <v>-4.1163920116798466e-05</v>
       </c>
       <c r="AB11" s="1">
-        <v>-1.9375510236418637e-05</v>
+        <v>-1.9375510236351711e-05</v>
       </c>
       <c r="AC11" s="1">
-        <v>2.1611608991420687e-05</v>
+        <v>2.1611608991628807e-05</v>
       </c>
       <c r="AD11" s="1">
-        <v>-5.084441346616486e-05</v>
+        <v>-5.0844413466025743e-05</v>
       </c>
       <c r="AE11" s="1">
-        <v>2.0457992734635474e-05</v>
+        <v>2.0457992734769983e-05</v>
       </c>
       <c r="AF11" s="1">
-        <v>1.0531096945841482e-05</v>
+        <v>1.0531096946118869e-05</v>
       </c>
       <c r="AG11" s="1">
-        <v>-2.3570093689754078e-05</v>
+        <v>-2.3570093689684537e-05</v>
       </c>
       <c r="AH11" s="1">
-        <v>-7.9239280543692123e-06</v>
+        <v>-7.9239280543415652e-06</v>
       </c>
       <c r="AI11" s="1">
-        <v>-1.9093120517715411e-05</v>
+        <v>-1.9093120517670003e-05</v>
       </c>
       <c r="AJ11" s="1">
-        <v>-1.5979458165976204e-06</v>
+        <v>-1.5979458165457956e-06</v>
       </c>
       <c r="AK11" s="1">
-        <v>-1.0857226890041353e-06</v>
+        <v>-1.0857226890158006e-06</v>
       </c>
       <c r="AL11" s="1">
-        <v>0.0003177250207875166</v>
+        <v>0.00031772502077733654</v>
       </c>
     </row>
     <row r="12">
@@ -1863,112 +1863,112 @@
         <v>0.37032069028887155</v>
       </c>
       <c r="C12" s="1">
-        <v>2.944085734012645e-05</v>
+        <v>2.9440857340126765e-05</v>
       </c>
       <c r="D12" s="1">
-        <v>-4.7617717177342688e-06</v>
+        <v>-4.7617717177425494e-06</v>
       </c>
       <c r="E12" s="1">
-        <v>3.9142724579218388e-08</v>
+        <v>3.9142724579313996e-08</v>
       </c>
       <c r="F12" s="1">
-        <v>6.5753103534519058e-06</v>
+        <v>6.5753103537348825e-06</v>
       </c>
       <c r="G12" s="1">
-        <v>1.9236919879593996e-05</v>
+        <v>1.9236919879639695e-05</v>
       </c>
       <c r="H12" s="1">
-        <v>1.6716946290231064e-05</v>
+        <v>1.6716946290276831e-05</v>
       </c>
       <c r="I12" s="1">
-        <v>1.4389508425830998e-05</v>
+        <v>1.4389508425868288e-05</v>
       </c>
       <c r="J12" s="1">
-        <v>-9.629760596317176e-05</v>
+        <v>-9.6297605963173292e-05</v>
       </c>
       <c r="K12" s="1">
-        <v>-1.138054988337054e-05</v>
+        <v>-1.1380549883363547e-05</v>
       </c>
       <c r="L12" s="1">
-        <v>8.8057189783537797e-06</v>
+        <v>8.8057189783542438e-06</v>
       </c>
       <c r="M12" s="1">
-        <v>0.000197194785479612</v>
+        <v>0.00019719478547961287</v>
       </c>
       <c r="N12" s="1">
-        <v>-5.4067058192569005e-05</v>
+        <v>-5.4067058192325927e-05</v>
       </c>
       <c r="O12" s="1">
-        <v>6.5480984904726635e-07</v>
+        <v>6.5480984905363869e-07</v>
       </c>
       <c r="P12" s="1">
-        <v>-5.1659555183136688e-05</v>
+        <v>-5.1659555165668802e-05</v>
       </c>
       <c r="Q12" s="1">
-        <v>6.2091231300211879e-07</v>
+        <v>6.2091233054715269e-07</v>
       </c>
       <c r="R12" s="1">
-        <v>-6.0116844500292144e-05</v>
+        <v>-6.0116844483280171e-05</v>
       </c>
       <c r="S12" s="1">
-        <v>4.0450632494849119e-05</v>
+        <v>4.0450632511859438e-05</v>
       </c>
       <c r="T12" s="1">
-        <v>8.4463579805249501e-05</v>
+        <v>8.4463579805232994e-05</v>
       </c>
       <c r="U12" s="1">
-        <v>1.309822716670862e-05</v>
+        <v>1.3098227166670149e-05</v>
       </c>
       <c r="V12" s="1">
-        <v>-1.7453580828604919e-05</v>
+        <v>-1.7453580828694193e-05</v>
       </c>
       <c r="W12" s="1">
-        <v>-0.00023490384988515743</v>
+        <v>-0.00023490384988524314</v>
       </c>
       <c r="X12" s="1">
-        <v>0.00019164360641002139</v>
+        <v>0.00019164360643084133</v>
       </c>
       <c r="Y12" s="1">
-        <v>0.00017868822374644635</v>
+        <v>0.00017868822376718846</v>
       </c>
       <c r="Z12" s="1">
-        <v>0.00024096496135118069</v>
+        <v>0.00024096496137166151</v>
       </c>
       <c r="AA12" s="1">
-        <v>5.2703957415744592e-05</v>
+        <v>5.2703957415865108e-05</v>
       </c>
       <c r="AB12" s="1">
-        <v>2.7363902590949198e-05</v>
+        <v>2.7363902590985183e-05</v>
       </c>
       <c r="AC12" s="1">
-        <v>5.2723457177004285e-05</v>
+        <v>5.2723457176985115e-05</v>
       </c>
       <c r="AD12" s="1">
-        <v>-1.6370943141980253e-05</v>
+        <v>-1.6370943141943552e-05</v>
       </c>
       <c r="AE12" s="1">
-        <v>-5.7529476346296735e-05</v>
+        <v>-5.7529476346300591e-05</v>
       </c>
       <c r="AF12" s="1">
-        <v>-4.9955903661385066e-05</v>
+        <v>-4.9955903661294074e-05</v>
       </c>
       <c r="AG12" s="1">
-        <v>1.9182932206294718e-05</v>
+        <v>1.9182932206328806e-05</v>
       </c>
       <c r="AH12" s="1">
-        <v>2.9254598987517492e-05</v>
+        <v>2.9254598987531018e-05</v>
       </c>
       <c r="AI12" s="1">
-        <v>-4.2924420730634032e-06</v>
+        <v>-4.2924420730354342e-06</v>
       </c>
       <c r="AJ12" s="1">
-        <v>2.2279585569666447e-05</v>
+        <v>2.2279585569689317e-05</v>
       </c>
       <c r="AK12" s="1">
-        <v>-1.6762621207695698e-06</v>
+        <v>-1.6762621207704787e-06</v>
       </c>
       <c r="AL12" s="1">
-        <v>-0.00014310115244555363</v>
+        <v>-0.00014310115246613799</v>
       </c>
     </row>
     <row r="13">
@@ -1976,115 +1976,115 @@
         <v>40</v>
       </c>
       <c r="B13" s="1">
-        <v>-0.086105085888025082</v>
+        <v>-0.086105085888026331</v>
       </c>
       <c r="C13" s="1">
-        <v>-0.0018329003487245327</v>
+        <v>-0.0018329003487240825</v>
       </c>
       <c r="D13" s="1">
-        <v>2.4916074500750096e-05</v>
+        <v>2.4916074499971313e-05</v>
       </c>
       <c r="E13" s="1">
-        <v>-2.5903643769748114e-07</v>
+        <v>-2.5903643769020344e-07</v>
       </c>
       <c r="F13" s="1">
-        <v>0.0001295071869027338</v>
+        <v>0.00012950718691609074</v>
       </c>
       <c r="G13" s="1">
-        <v>2.5811446687763696e-05</v>
+        <v>2.5811446692939135e-05</v>
       </c>
       <c r="H13" s="1">
-        <v>-0.00016019986749175706</v>
+        <v>-0.00016019986748625267</v>
       </c>
       <c r="I13" s="1">
-        <v>-0.00012784645723076294</v>
+        <v>-0.00012784645722704798</v>
       </c>
       <c r="J13" s="1">
-        <v>6.9230656755237243e-05</v>
+        <v>6.923065675494417e-05</v>
       </c>
       <c r="K13" s="1">
-        <v>4.1106307505251225e-05</v>
+        <v>4.1106307505336674e-05</v>
       </c>
       <c r="L13" s="1">
-        <v>6.0849567422365265e-06</v>
+        <v>6.0849567423139047e-06</v>
       </c>
       <c r="M13" s="1">
-        <v>-5.4067058192569005e-05</v>
+        <v>-5.4067058192325927e-05</v>
       </c>
       <c r="N13" s="1">
-        <v>0.03200148742996696</v>
+        <v>0.032001487429972109</v>
       </c>
       <c r="O13" s="1">
-        <v>3.7079688952230513e-07</v>
+        <v>3.7079688982295366e-07</v>
       </c>
       <c r="P13" s="1">
-        <v>-0.0069457326317082227</v>
+        <v>-0.0069457326312877127</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.00097240469385634788</v>
+        <v>0.000972404694207318</v>
       </c>
       <c r="R13" s="1">
-        <v>-0.0024947513191331538</v>
+        <v>-0.0024947513187056451</v>
       </c>
       <c r="S13" s="1">
-        <v>-0.0029128041446057334</v>
+        <v>-0.0029128041441911917</v>
       </c>
       <c r="T13" s="1">
-        <v>-0.0015371183499032013</v>
+        <v>-0.0015371183499037031</v>
       </c>
       <c r="U13" s="1">
-        <v>-0.00052356174362737417</v>
+        <v>-0.00052356174362866925</v>
       </c>
       <c r="V13" s="1">
-        <v>0.00051330786188360654</v>
+        <v>0.00051330786187834447</v>
       </c>
       <c r="W13" s="1">
-        <v>-0.00058533840420309713</v>
+        <v>-0.00058533840420834336</v>
       </c>
       <c r="X13" s="1">
-        <v>0.01129787240271835</v>
+        <v>0.011297872403237246</v>
       </c>
       <c r="Y13" s="1">
-        <v>0.011419740148282218</v>
+        <v>0.011419740148772829</v>
       </c>
       <c r="Z13" s="1">
-        <v>0.011054692434949444</v>
+        <v>0.011054692435492584</v>
       </c>
       <c r="AA13" s="1">
-        <v>0.001502875202934737</v>
+        <v>0.0015028752029381265</v>
       </c>
       <c r="AB13" s="1">
-        <v>-0.00018758123733207666</v>
+        <v>-0.00018758123733128562</v>
       </c>
       <c r="AC13" s="1">
-        <v>-0.00017570613249802284</v>
+        <v>-0.00017570613249740397</v>
       </c>
       <c r="AD13" s="1">
-        <v>-0.00026076025471245378</v>
+        <v>-0.00026076025471121259</v>
       </c>
       <c r="AE13" s="1">
-        <v>1.9673136917242734e-05</v>
+        <v>1.9673136915017084e-05</v>
       </c>
       <c r="AF13" s="1">
-        <v>-0.00096376385235637761</v>
+        <v>-0.00096376385235219259</v>
       </c>
       <c r="AG13" s="1">
-        <v>0.00048838442078575836</v>
+        <v>0.00048838442078615214</v>
       </c>
       <c r="AH13" s="1">
-        <v>0.00012528393140078214</v>
+        <v>0.00012528393140102826</v>
       </c>
       <c r="AI13" s="1">
-        <v>0.00012258185353706055</v>
+        <v>0.0001225818535376122</v>
       </c>
       <c r="AJ13" s="1">
-        <v>0.00015561236279167372</v>
+        <v>0.00015561236279166678</v>
       </c>
       <c r="AK13" s="1">
-        <v>2.5852452685503268e-05</v>
+        <v>2.585245268558415e-05</v>
       </c>
       <c r="AL13" s="1">
-        <v>-0.011519716844985336</v>
+        <v>-0.011519716845475822</v>
       </c>
     </row>
     <row r="14">
@@ -2092,115 +2092,115 @@
         <v>41</v>
       </c>
       <c r="B14" s="1">
-        <v>-0.0014998556624415624</v>
+        <v>-0.0014998556624415712</v>
       </c>
       <c r="C14" s="1">
-        <v>2.0319598118490377e-06</v>
+        <v>2.0319598118562946e-06</v>
       </c>
       <c r="D14" s="1">
-        <v>-1.3442204499456174e-06</v>
+        <v>-1.3442204499919734e-06</v>
       </c>
       <c r="E14" s="1">
-        <v>1.3132480775486905e-08</v>
+        <v>1.3132480775942129e-08</v>
       </c>
       <c r="F14" s="1">
-        <v>7.2280341222147156e-07</v>
+        <v>7.2280341278688564e-07</v>
       </c>
       <c r="G14" s="1">
-        <v>8.430867523379178e-07</v>
+        <v>8.4308675253676884e-07</v>
       </c>
       <c r="H14" s="1">
-        <v>1.3948236825587661e-06</v>
+        <v>1.3948236827726807e-06</v>
       </c>
       <c r="I14" s="1">
-        <v>-1.0339770255125495e-06</v>
+        <v>-1.033977025362987e-06</v>
       </c>
       <c r="J14" s="1">
-        <v>-9.0892201845079287e-07</v>
+        <v>-9.0892201845836736e-07</v>
       </c>
       <c r="K14" s="1">
-        <v>-1.6570918695660659e-07</v>
+        <v>-1.657091869507452e-07</v>
       </c>
       <c r="L14" s="1">
-        <v>1.0049198051697741e-07</v>
+        <v>1.0049198052331095e-07</v>
       </c>
       <c r="M14" s="1">
-        <v>6.5480984904726635e-07</v>
+        <v>6.5480984905363869e-07</v>
       </c>
       <c r="N14" s="1">
-        <v>3.7079688952230513e-07</v>
+        <v>3.7079688982295366e-07</v>
       </c>
       <c r="O14" s="1">
-        <v>1.6352234077747418e-06</v>
+        <v>1.6352234077873228e-06</v>
       </c>
       <c r="P14" s="1">
-        <v>-1.5139389560821337e-05</v>
+        <v>-1.5139389537806015e-05</v>
       </c>
       <c r="Q14" s="1">
-        <v>-8.4059927586099608e-05</v>
+        <v>-8.4059927564899309e-05</v>
       </c>
       <c r="R14" s="1">
-        <v>-4.8445813873396128e-05</v>
+        <v>-4.8445813850201466e-05</v>
       </c>
       <c r="S14" s="1">
-        <v>-4.3198331095163184e-05</v>
+        <v>-4.319833107221431e-05</v>
       </c>
       <c r="T14" s="1">
-        <v>-3.8602315152180822e-06</v>
+        <v>-3.8602315152414535e-06</v>
       </c>
       <c r="U14" s="1">
-        <v>-6.55254317598442e-06</v>
+        <v>-6.5525431760431363e-06</v>
       </c>
       <c r="V14" s="1">
-        <v>-3.1227122834257784e-05</v>
+        <v>-3.1227122834457589e-05</v>
       </c>
       <c r="W14" s="1">
-        <v>-2.8356771281659932e-05</v>
+        <v>-2.835677128185168e-05</v>
       </c>
       <c r="X14" s="1">
-        <v>0.00058826385054559587</v>
+        <v>0.00058826385057323446</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.00058849217651018757</v>
+        <v>0.00058849217653722833</v>
       </c>
       <c r="Z14" s="1">
-        <v>0.00058999178502670661</v>
+        <v>0.00058999178505500722</v>
       </c>
       <c r="AA14" s="1">
-        <v>-1.4428049344542317e-05</v>
+        <v>-1.4428049344474507e-05</v>
       </c>
       <c r="AB14" s="1">
-        <v>4.8488587665390797e-07</v>
+        <v>4.8488587670062692e-07</v>
       </c>
       <c r="AC14" s="1">
-        <v>-1.2061443910948397e-06</v>
+        <v>-1.2061443911462851e-06</v>
       </c>
       <c r="AD14" s="1">
-        <v>2.8649514887941415e-06</v>
+        <v>2.8649514888350329e-06</v>
       </c>
       <c r="AE14" s="1">
-        <v>-7.2317296396100757e-06</v>
+        <v>-7.231729639714647e-06</v>
       </c>
       <c r="AF14" s="1">
-        <v>5.903927805222598e-06</v>
+        <v>5.9039278053599935e-06</v>
       </c>
       <c r="AG14" s="1">
-        <v>2.6390617494967102e-06</v>
+        <v>2.6390617495283689e-06</v>
       </c>
       <c r="AH14" s="1">
-        <v>5.9570636788271419e-07</v>
+        <v>5.9570636789806921e-07</v>
       </c>
       <c r="AI14" s="1">
-        <v>9.9918855874772585e-07</v>
+        <v>9.9918855878092954e-07</v>
       </c>
       <c r="AJ14" s="1">
-        <v>3.7372028265341816e-07</v>
+        <v>3.7372028266762121e-07</v>
       </c>
       <c r="AK14" s="1">
-        <v>-2.4476669109535574e-07</v>
+        <v>-2.4476669109324832e-07</v>
       </c>
       <c r="AL14" s="1">
-        <v>-0.00055402555501665436</v>
+        <v>-0.00055402555504303734</v>
       </c>
     </row>
     <row r="15">
@@ -2208,115 +2208,115 @@
         <v>42</v>
       </c>
       <c r="B15" s="1">
-        <v>-1.6751169523391873</v>
+        <v>-1.6751169523393086</v>
       </c>
       <c r="C15" s="1">
-        <v>-9.7676588504064008e-05</v>
+        <v>-9.767658846916232e-05</v>
       </c>
       <c r="D15" s="1">
-        <v>6.2318194595786705e-05</v>
+        <v>6.2318194547055774e-05</v>
       </c>
       <c r="E15" s="1">
-        <v>-8.0795369675873505e-07</v>
+        <v>-8.0795369630638314e-07</v>
       </c>
       <c r="F15" s="1">
-        <v>0.017574894910762133</v>
+        <v>0.017574894911781849</v>
       </c>
       <c r="G15" s="1">
-        <v>-0.0025612762142994162</v>
+        <v>-0.0025612762139291569</v>
       </c>
       <c r="H15" s="1">
-        <v>0.0002508164567880926</v>
+        <v>0.00025081645717822042</v>
       </c>
       <c r="I15" s="1">
-        <v>5.4960952700438236e-05</v>
+        <v>5.4960952960800876e-05</v>
       </c>
       <c r="J15" s="1">
-        <v>-1.5890419950983993e-05</v>
+        <v>-1.5890419972119254e-05</v>
       </c>
       <c r="K15" s="1">
-        <v>0.00014075649255679398</v>
+        <v>0.00014075649256319777</v>
       </c>
       <c r="L15" s="1">
-        <v>-9.8777582017101756e-05</v>
+        <v>-9.8777582012711944e-05</v>
       </c>
       <c r="M15" s="1">
-        <v>-5.1659555183136688e-05</v>
+        <v>-5.1659555165668802e-05</v>
       </c>
       <c r="N15" s="1">
-        <v>-0.0069457326317082227</v>
+        <v>-0.0069457326312877127</v>
       </c>
       <c r="O15" s="1">
-        <v>-1.5139389560821337e-05</v>
+        <v>-1.5139389537806015e-05</v>
       </c>
       <c r="P15" s="1">
-        <v>1.1925475644160346</v>
+        <v>1.1925475644491119</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.69735317328628255</v>
+        <v>0.6973531733140943</v>
       </c>
       <c r="R15" s="1">
-        <v>0.71828501620928709</v>
+        <v>0.71828501624290464</v>
       </c>
       <c r="S15" s="1">
-        <v>0.71712320879553704</v>
+        <v>0.71712320882796809</v>
       </c>
       <c r="T15" s="1">
-        <v>-0.00017773248366899363</v>
+        <v>-0.00017773248370520078</v>
       </c>
       <c r="U15" s="1">
-        <v>-0.00051213708105161959</v>
+        <v>-0.00051213708114904166</v>
       </c>
       <c r="V15" s="1">
-        <v>0.0017198715456454294</v>
+        <v>0.0017198715452603902</v>
       </c>
       <c r="W15" s="1">
-        <v>0.0013638838286421755</v>
+        <v>0.0013638838282574658</v>
       </c>
       <c r="X15" s="1">
-        <v>0.7107605974445681</v>
+        <v>0.71076059748483811</v>
       </c>
       <c r="Y15" s="1">
-        <v>0.71029302499972713</v>
+        <v>0.71029302503801439</v>
       </c>
       <c r="Z15" s="1">
-        <v>0.71046833570272705</v>
+        <v>0.71046833574460666</v>
       </c>
       <c r="AA15" s="1">
-        <v>0.001296564401397575</v>
+        <v>0.001296564401674874</v>
       </c>
       <c r="AB15" s="1">
-        <v>-0.00041626977681320787</v>
+        <v>-0.00041626977675469912</v>
       </c>
       <c r="AC15" s="1">
-        <v>0.00027110308151009899</v>
+        <v>0.00027110308156277907</v>
       </c>
       <c r="AD15" s="1">
-        <v>-0.00073917780573091313</v>
+        <v>-0.00073917780563757807</v>
       </c>
       <c r="AE15" s="1">
-        <v>-8.1115652960289664e-05</v>
+        <v>-8.1115653112528996e-05</v>
       </c>
       <c r="AF15" s="1">
-        <v>0.0050593527678394201</v>
+        <v>0.0050593527681538353</v>
       </c>
       <c r="AG15" s="1">
-        <v>0.0010529188522405697</v>
+        <v>0.0010529188522705457</v>
       </c>
       <c r="AH15" s="1">
-        <v>0.00069204524251523236</v>
+        <v>0.00069204524253621558</v>
       </c>
       <c r="AI15" s="1">
-        <v>0.0010295202297375683</v>
+        <v>0.0010295202297798678</v>
       </c>
       <c r="AJ15" s="1">
-        <v>0.00055051196329386487</v>
+        <v>0.00055051196329469754</v>
       </c>
       <c r="AK15" s="1">
-        <v>-0.00011072448411314495</v>
+        <v>-0.00011072448410665015</v>
       </c>
       <c r="AL15" s="1">
-        <v>-0.7103001611195201</v>
+        <v>-0.71030016115773364</v>
       </c>
     </row>
     <row r="16">
@@ -2324,115 +2324,115 @@
         <v>43</v>
       </c>
       <c r="B16" s="1">
-        <v>-2.5834029997220451</v>
+        <v>-2.5834029997221655</v>
       </c>
       <c r="C16" s="1">
-        <v>-0.00026176895267021095</v>
+        <v>-0.00026176895263734824</v>
       </c>
       <c r="D16" s="1">
-        <v>0.00011241424737369268</v>
+        <v>0.00011241424731644372</v>
       </c>
       <c r="E16" s="1">
-        <v>-1.3437543377330105e-06</v>
+        <v>-1.3437543371949023e-06</v>
       </c>
       <c r="F16" s="1">
-        <v>0.017683304496518004</v>
+        <v>0.017683304497449783</v>
       </c>
       <c r="G16" s="1">
-        <v>0.00053931682966464425</v>
+        <v>0.00053931683002650659</v>
       </c>
       <c r="H16" s="1">
-        <v>-0.000956487523724678</v>
+        <v>-0.00095648752333873737</v>
       </c>
       <c r="I16" s="1">
-        <v>9.1946761603610666e-05</v>
+        <v>9.1946761864627785e-05</v>
       </c>
       <c r="J16" s="1">
-        <v>-2.6939425460752069e-05</v>
+        <v>-2.6939425480981272e-05</v>
       </c>
       <c r="K16" s="1">
-        <v>0.00012461942023962537</v>
+        <v>0.00012461942024397869</v>
       </c>
       <c r="L16" s="1">
-        <v>-8.3940790746369411e-05</v>
+        <v>-8.3940790739927624e-05</v>
       </c>
       <c r="M16" s="1">
-        <v>6.2091231300211879e-07</v>
+        <v>6.2091233054715269e-07</v>
       </c>
       <c r="N16" s="1">
-        <v>0.00097240469385634788</v>
+        <v>0.000972404694207318</v>
       </c>
       <c r="O16" s="1">
-        <v>-8.4059927586099608e-05</v>
+        <v>-8.4059927564899309e-05</v>
       </c>
       <c r="P16" s="1">
-        <v>0.69735317328628255</v>
+        <v>0.6973531733140943</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.92920510686910673</v>
+        <v>0.92920510689781566</v>
       </c>
       <c r="R16" s="1">
-        <v>0.7771974300237956</v>
+        <v>0.7771974300582476</v>
       </c>
       <c r="S16" s="1">
-        <v>0.77748462270037144</v>
+        <v>0.77748462273365204</v>
       </c>
       <c r="T16" s="1">
-        <v>-0.003377712372176378</v>
+        <v>-0.0033777123722130015</v>
       </c>
       <c r="U16" s="1">
-        <v>-0.0018787400429714218</v>
+        <v>-0.0018787400430696211</v>
       </c>
       <c r="V16" s="1">
-        <v>0.004388305253088115</v>
+        <v>0.0043883052527021738</v>
       </c>
       <c r="W16" s="1">
-        <v>0.0015343727605800685</v>
+        <v>0.0015343727601956209</v>
       </c>
       <c r="X16" s="1">
-        <v>0.74501406541298532</v>
+        <v>0.74501406545420545</v>
       </c>
       <c r="Y16" s="1">
-        <v>0.74519501111925612</v>
+        <v>0.74519501115852527</v>
       </c>
       <c r="Z16" s="1">
-        <v>0.74512419512729289</v>
+        <v>0.7451241951701002</v>
       </c>
       <c r="AA16" s="1">
-        <v>0.0015188009392918186</v>
+        <v>0.0015188009395610963</v>
       </c>
       <c r="AB16" s="1">
-        <v>-0.0007118042989207457</v>
+        <v>-0.00071180429886116836</v>
       </c>
       <c r="AC16" s="1">
-        <v>0.00033124076570051342</v>
+        <v>0.00033124076574492234</v>
       </c>
       <c r="AD16" s="1">
-        <v>-0.00084135438976470911</v>
+        <v>-0.00084135438967195691</v>
       </c>
       <c r="AE16" s="1">
-        <v>-0.00019410960052287929</v>
+        <v>-0.00019410960067781091</v>
       </c>
       <c r="AF16" s="1">
-        <v>0.0052413457905653438</v>
+        <v>0.0052413457908775385</v>
       </c>
       <c r="AG16" s="1">
-        <v>0.00093920988924389714</v>
+        <v>0.00093920988927542748</v>
       </c>
       <c r="AH16" s="1">
-        <v>0.00010790994071090132</v>
+        <v>0.00010790994073243965</v>
       </c>
       <c r="AI16" s="1">
-        <v>0.00088694936906263955</v>
+        <v>0.00088694936910682642</v>
       </c>
       <c r="AJ16" s="1">
-        <v>2.3207444428408053e-06</v>
+        <v>2.3207444451722736e-06</v>
       </c>
       <c r="AK16" s="1">
-        <v>-5.913572926505295e-05</v>
+        <v>-5.9135729258585901e-05</v>
       </c>
       <c r="AL16" s="1">
-        <v>-0.74643200119387354</v>
+        <v>-0.74643200123301234</v>
       </c>
     </row>
     <row r="17">
@@ -2440,115 +2440,115 @@
         <v>44</v>
       </c>
       <c r="B17" s="1">
-        <v>-2.6552858497548959</v>
+        <v>-2.6552858497550158</v>
       </c>
       <c r="C17" s="1">
-        <v>-7.0923232997222127e-05</v>
+        <v>-7.092323296223411e-05</v>
       </c>
       <c r="D17" s="1">
-        <v>3.2769385125475873e-05</v>
+        <v>3.2769385073399854e-05</v>
       </c>
       <c r="E17" s="1">
-        <v>-7.6459609355421659e-07</v>
+        <v>-7.6459609307119774e-07</v>
       </c>
       <c r="F17" s="1">
-        <v>0.018872890395427076</v>
+        <v>0.018872890396459945</v>
       </c>
       <c r="G17" s="1">
-        <v>0.0015151353853942943</v>
+        <v>0.0015151353857721314</v>
       </c>
       <c r="H17" s="1">
-        <v>0.0010384969413550734</v>
+        <v>0.0010384969417520169</v>
       </c>
       <c r="I17" s="1">
-        <v>-0.00076748884461731227</v>
+        <v>-0.00076748884435072875</v>
       </c>
       <c r="J17" s="1">
-        <v>-4.383433273796585e-05</v>
+        <v>-4.3834332758812042e-05</v>
       </c>
       <c r="K17" s="1">
-        <v>0.0001109763480569417</v>
+        <v>0.00011097634806405425</v>
       </c>
       <c r="L17" s="1">
-        <v>-5.9831030580844121e-05</v>
+        <v>-5.9831030576428112e-05</v>
       </c>
       <c r="M17" s="1">
-        <v>-6.0116844500292144e-05</v>
+        <v>-6.0116844483280171e-05</v>
       </c>
       <c r="N17" s="1">
-        <v>-0.0024947513191331538</v>
+        <v>-0.0024947513187056451</v>
       </c>
       <c r="O17" s="1">
-        <v>-4.8445813873396128e-05</v>
+        <v>-4.8445813850201466e-05</v>
       </c>
       <c r="P17" s="1">
-        <v>0.71828501620928709</v>
+        <v>0.71828501624290464</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.7771974300237956</v>
+        <v>0.7771974300582476</v>
       </c>
       <c r="R17" s="1">
-        <v>0.80552518921075189</v>
+        <v>0.80552518924580874</v>
       </c>
       <c r="S17" s="1">
-        <v>0.78083252381437895</v>
+        <v>0.78083252384825697</v>
       </c>
       <c r="T17" s="1">
-        <v>-0.0035348522809948851</v>
+        <v>-0.0035348522810321331</v>
       </c>
       <c r="U17" s="1">
-        <v>-0.00069984303912473678</v>
+        <v>-0.00069984303922458746</v>
       </c>
       <c r="V17" s="1">
-        <v>-0.00056514999423953882</v>
+        <v>-0.00056514999463086468</v>
       </c>
       <c r="W17" s="1">
-        <v>0.0025464546302981072</v>
+        <v>0.0025464546299083166</v>
       </c>
       <c r="X17" s="1">
-        <v>0.7573815291243835</v>
+        <v>0.75738152916632751</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.7579522975737949</v>
+        <v>0.75795229761376981</v>
       </c>
       <c r="Z17" s="1">
-        <v>0.75804593463615277</v>
+        <v>0.75804593467970283</v>
       </c>
       <c r="AA17" s="1">
-        <v>-0.00027090509826546705</v>
+        <v>-0.00027090509799336526</v>
       </c>
       <c r="AB17" s="1">
-        <v>-0.00093892551120024204</v>
+        <v>-0.00093892551113944345</v>
       </c>
       <c r="AC17" s="1">
-        <v>0.00010619393080438244</v>
+        <v>0.00010619393084773665</v>
       </c>
       <c r="AD17" s="1">
-        <v>-0.00045915250430560856</v>
+        <v>-0.00045915250421165593</v>
       </c>
       <c r="AE17" s="1">
-        <v>-0.00055054595536291329</v>
+        <v>-0.00055054595552034291</v>
       </c>
       <c r="AF17" s="1">
-        <v>0.0066392870316531738</v>
+        <v>0.0066392870319694763</v>
       </c>
       <c r="AG17" s="1">
-        <v>0.0012715818800942413</v>
+        <v>0.0012715818801266598</v>
       </c>
       <c r="AH17" s="1">
-        <v>0.000325715064898216</v>
+        <v>0.00032571506492011515</v>
       </c>
       <c r="AI17" s="1">
-        <v>0.0012773758690651782</v>
+        <v>0.0012773758691095871</v>
       </c>
       <c r="AJ17" s="1">
-        <v>0.00048494177400243421</v>
+        <v>0.00048494177400509875</v>
       </c>
       <c r="AK17" s="1">
-        <v>-3.0735105178106292e-05</v>
+        <v>-3.0735105171569854e-05</v>
       </c>
       <c r="AL17" s="1">
-        <v>-0.7579378004989481</v>
+        <v>-0.75793780053877657</v>
       </c>
     </row>
     <row r="18">
@@ -2556,115 +2556,115 @@
         <v>45</v>
       </c>
       <c r="B18" s="1">
-        <v>-2.6251549801627458</v>
+        <v>-2.6251549801628649</v>
       </c>
       <c r="C18" s="1">
-        <v>0.00014101263549054052</v>
+        <v>0.00014101263552363945</v>
       </c>
       <c r="D18" s="1">
-        <v>-8.5679708139436647e-05</v>
+        <v>-8.567970819804016e-05</v>
       </c>
       <c r="E18" s="1">
-        <v>1.6785511279013216e-07</v>
+        <v>1.6785511334203511e-07</v>
       </c>
       <c r="F18" s="1">
-        <v>0.022134298978477449</v>
+        <v>0.022134298979494614</v>
       </c>
       <c r="G18" s="1">
-        <v>0.0047959391956321719</v>
+        <v>0.0047959391960137147</v>
       </c>
       <c r="H18" s="1">
-        <v>0.0042723082330759429</v>
+        <v>0.0042723082334802714</v>
       </c>
       <c r="I18" s="1">
-        <v>0.0030241914464016265</v>
+        <v>0.003024191446676117</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.00014679834605191787</v>
+        <v>-0.00014679834607250172</v>
       </c>
       <c r="K18" s="1">
-        <v>0.00011726469664380053</v>
+        <v>0.00011726469664914079</v>
       </c>
       <c r="L18" s="1">
-        <v>-6.2384645609330974e-05</v>
+        <v>-6.2384645603126085e-05</v>
       </c>
       <c r="M18" s="1">
-        <v>4.0450632494849119e-05</v>
+        <v>4.0450632511859438e-05</v>
       </c>
       <c r="N18" s="1">
-        <v>-0.0029128041446057334</v>
+        <v>-0.0029128041441911917</v>
       </c>
       <c r="O18" s="1">
-        <v>-4.3198331095163184e-05</v>
+        <v>-4.319833107221431e-05</v>
       </c>
       <c r="P18" s="1">
-        <v>0.71712320879553704</v>
+        <v>0.71712320882796809</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.77748462270037144</v>
+        <v>0.77748462273365204</v>
       </c>
       <c r="R18" s="1">
-        <v>0.78083252381437895</v>
+        <v>0.78083252384825697</v>
       </c>
       <c r="S18" s="1">
-        <v>0.79808405482016798</v>
+        <v>0.79808405485437017</v>
       </c>
       <c r="T18" s="1">
-        <v>-0.0017023981006442507</v>
+        <v>-0.0017023981006818734</v>
       </c>
       <c r="U18" s="1">
-        <v>-0.0015937770749772373</v>
+        <v>-0.0015937770750780039</v>
       </c>
       <c r="V18" s="1">
-        <v>0.00091519242865562012</v>
+        <v>0.00091519242826196279</v>
       </c>
       <c r="W18" s="1">
-        <v>-0.0015527121524817489</v>
+        <v>-0.001552712152873629</v>
       </c>
       <c r="X18" s="1">
-        <v>0.76032256847687363</v>
+        <v>0.7603225685192021</v>
       </c>
       <c r="Y18" s="1">
-        <v>0.76080340546628056</v>
+        <v>0.76080340550664061</v>
       </c>
       <c r="Z18" s="1">
-        <v>0.76114881223271014</v>
+        <v>0.76114881227665465</v>
       </c>
       <c r="AA18" s="1">
-        <v>-0.00019385146589492863</v>
+        <v>-0.00019385146562196642</v>
       </c>
       <c r="AB18" s="1">
-        <v>-0.00079294441965360729</v>
+        <v>-0.00079294441959186501</v>
       </c>
       <c r="AC18" s="1">
-        <v>0.00020409748504182645</v>
+        <v>0.00020409748508373737</v>
       </c>
       <c r="AD18" s="1">
-        <v>-0.00040788370359221005</v>
+        <v>-0.00040788370349770231</v>
       </c>
       <c r="AE18" s="1">
-        <v>-0.00063580147632330553</v>
+        <v>-0.00063580147648203966</v>
       </c>
       <c r="AF18" s="1">
-        <v>0.0060795862446796356</v>
+        <v>0.0060795862449969373</v>
       </c>
       <c r="AG18" s="1">
-        <v>0.00076581954053656087</v>
+        <v>0.00076581954056964552</v>
       </c>
       <c r="AH18" s="1">
-        <v>0.00014665216587794738</v>
+        <v>0.00014665216590011021</v>
       </c>
       <c r="AI18" s="1">
-        <v>0.0012383312103790844</v>
+        <v>0.0012383312104244926</v>
       </c>
       <c r="AJ18" s="1">
-        <v>0.00032803400681530315</v>
+        <v>0.00032803400681852279</v>
       </c>
       <c r="AK18" s="1">
-        <v>-8.1882413260209175e-06</v>
+        <v>-8.1882413195677461e-06</v>
       </c>
       <c r="AL18" s="1">
-        <v>-0.76088718229212859</v>
+        <v>-0.76088718233232899</v>
       </c>
     </row>
     <row r="19">
@@ -2672,115 +2672,115 @@
         <v>46</v>
       </c>
       <c r="B19" s="1">
-        <v>0.16205891215897636</v>
+        <v>0.16205891215897664</v>
       </c>
       <c r="C19" s="1">
-        <v>9.5117774016051845e-06</v>
+        <v>9.5117774015979779e-06</v>
       </c>
       <c r="D19" s="1">
-        <v>-1.0907752677686043e-05</v>
+        <v>-1.0907752677580672e-05</v>
       </c>
       <c r="E19" s="1">
-        <v>1.1866416477474847e-07</v>
+        <v>1.1866416477374167e-07</v>
       </c>
       <c r="F19" s="1">
-        <v>0.00011030231493322539</v>
+        <v>0.00011030231493217024</v>
       </c>
       <c r="G19" s="1">
-        <v>6.0896170010413605e-05</v>
+        <v>6.0896170009967104e-05</v>
       </c>
       <c r="H19" s="1">
-        <v>7.2372875798721974e-05</v>
+        <v>7.237287579824651e-05</v>
       </c>
       <c r="I19" s="1">
-        <v>4.5561638979319116e-05</v>
+        <v>4.5561638978989261e-05</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.00017186141713062831</v>
+        <v>-0.00017186141713061039</v>
       </c>
       <c r="K19" s="1">
-        <v>-5.2278432530244372e-06</v>
+        <v>-5.2278432530070086e-06</v>
       </c>
       <c r="L19" s="1">
-        <v>1.5358442570351905e-06</v>
+        <v>1.5358442570040722e-06</v>
       </c>
       <c r="M19" s="1">
-        <v>8.4463579805249501e-05</v>
+        <v>8.4463579805232994e-05</v>
       </c>
       <c r="N19" s="1">
-        <v>-0.0015371183499032013</v>
+        <v>-0.0015371183499037031</v>
       </c>
       <c r="O19" s="1">
-        <v>-3.8602315152180822e-06</v>
+        <v>-3.8602315152414535e-06</v>
       </c>
       <c r="P19" s="1">
-        <v>-0.00017773248366899363</v>
+        <v>-0.00017773248370520078</v>
       </c>
       <c r="Q19" s="1">
-        <v>-0.003377712372176378</v>
+        <v>-0.0033777123722130015</v>
       </c>
       <c r="R19" s="1">
-        <v>-0.0035348522809948851</v>
+        <v>-0.0035348522810321331</v>
       </c>
       <c r="S19" s="1">
-        <v>-0.0017023981006442507</v>
+        <v>-0.0017023981006818734</v>
       </c>
       <c r="T19" s="1">
-        <v>0.0047636374305731789</v>
+        <v>0.0047636374305732171</v>
       </c>
       <c r="U19" s="1">
-        <v>0.00062378498272801306</v>
+        <v>0.00062378498272809644</v>
       </c>
       <c r="V19" s="1">
-        <v>-6.7817146290039156e-05</v>
+        <v>-6.7817146289645916e-05</v>
       </c>
       <c r="W19" s="1">
-        <v>-0.0028660391554443231</v>
+        <v>-0.0028660391554439567</v>
       </c>
       <c r="X19" s="1">
-        <v>-0.0016237481804599301</v>
+        <v>-0.0016237481805066764</v>
       </c>
       <c r="Y19" s="1">
-        <v>-0.0015414870030749171</v>
+        <v>-0.0015414870031196558</v>
       </c>
       <c r="Z19" s="1">
-        <v>-0.0015325373390287238</v>
+        <v>-0.0015325373390766162</v>
       </c>
       <c r="AA19" s="1">
-        <v>5.4064131018278633e-06</v>
+        <v>5.4064131018404265e-06</v>
       </c>
       <c r="AB19" s="1">
-        <v>3.3830239596436895e-05</v>
+        <v>3.3830239596416701e-05</v>
       </c>
       <c r="AC19" s="1">
-        <v>9.7562196655723321e-06</v>
+        <v>9.7562196656840862e-06</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.00011582145678657206</v>
+        <v>0.00011582145678651221</v>
       </c>
       <c r="AE19" s="1">
-        <v>-8.0669725409345449e-05</v>
+        <v>-8.0669725409119366e-05</v>
       </c>
       <c r="AF19" s="1">
-        <v>0.00026045608561864764</v>
+        <v>0.00026045608561842137</v>
       </c>
       <c r="AG19" s="1">
-        <v>-2.49759929468724e-05</v>
+        <v>-2.4975992946904601e-05</v>
       </c>
       <c r="AH19" s="1">
-        <v>3.0720548170659178e-05</v>
+        <v>3.0720548170634458e-05</v>
       </c>
       <c r="AI19" s="1">
-        <v>-5.6118017251381388e-05</v>
+        <v>-5.611801725143549e-05</v>
       </c>
       <c r="AJ19" s="1">
-        <v>2.4411847720227139e-06</v>
+        <v>2.4411847720130103e-06</v>
       </c>
       <c r="AK19" s="1">
-        <v>-3.4382167042515518e-06</v>
+        <v>-3.438216704255726e-06</v>
       </c>
       <c r="AL19" s="1">
-        <v>0.0018538329167746956</v>
+        <v>0.0018538329168189501</v>
       </c>
     </row>
     <row r="20">
@@ -2788,115 +2788,115 @@
         <v>47</v>
       </c>
       <c r="B20" s="1">
-        <v>0.17489851108118426</v>
+        <v>0.17489851108118529</v>
       </c>
       <c r="C20" s="1">
-        <v>-2.6929279263032234e-06</v>
+        <v>-2.6929279263089595e-06</v>
       </c>
       <c r="D20" s="1">
-        <v>-7.8494086436863185e-06</v>
+        <v>-7.8494086433453505e-06</v>
       </c>
       <c r="E20" s="1">
-        <v>6.7766432895908924e-08</v>
+        <v>6.776643289258469e-08</v>
       </c>
       <c r="F20" s="1">
-        <v>-8.6388543875278541e-05</v>
+        <v>-8.638854387795652e-05</v>
       </c>
       <c r="G20" s="1">
-        <v>4.914285960256896e-05</v>
+        <v>4.914285960145581e-05</v>
       </c>
       <c r="H20" s="1">
-        <v>2.9114204305561339e-05</v>
+        <v>2.9114204304326636e-05</v>
       </c>
       <c r="I20" s="1">
-        <v>3.4065995292866807e-05</v>
+        <v>3.4065995292014922e-05</v>
       </c>
       <c r="J20" s="1">
-        <v>3.2443636863720368e-06</v>
+        <v>3.2443636864150796e-06</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.00024917057608289992</v>
+        <v>-0.00024917057608288393</v>
       </c>
       <c r="L20" s="1">
-        <v>0.00016166096857994717</v>
+        <v>0.0001616609685798857</v>
       </c>
       <c r="M20" s="1">
-        <v>1.309822716670862e-05</v>
+        <v>1.3098227166670149e-05</v>
       </c>
       <c r="N20" s="1">
-        <v>-0.00052356174362737417</v>
+        <v>-0.00052356174362866925</v>
       </c>
       <c r="O20" s="1">
-        <v>-6.55254317598442e-06</v>
+        <v>-6.5525431760431363e-06</v>
       </c>
       <c r="P20" s="1">
-        <v>-0.00051213708105161959</v>
+        <v>-0.00051213708114904166</v>
       </c>
       <c r="Q20" s="1">
-        <v>-0.0018787400429714218</v>
+        <v>-0.0018787400430696211</v>
       </c>
       <c r="R20" s="1">
-        <v>-0.00069984303912473678</v>
+        <v>-0.00069984303922458746</v>
       </c>
       <c r="S20" s="1">
-        <v>-0.0015937770749772373</v>
+        <v>-0.0015937770750780039</v>
       </c>
       <c r="T20" s="1">
-        <v>0.00062378498272801306</v>
+        <v>0.00062378498272809644</v>
       </c>
       <c r="U20" s="1">
-        <v>0.0048462846487490737</v>
+        <v>0.0048462846487493027</v>
       </c>
       <c r="V20" s="1">
-        <v>-0.0020348727084594249</v>
+        <v>-0.0020348727084584916</v>
       </c>
       <c r="W20" s="1">
-        <v>-0.00038764175108789298</v>
+        <v>-0.00038764175108702562</v>
       </c>
       <c r="X20" s="1">
-        <v>-0.0024866414558549913</v>
+        <v>-0.0024866414559785686</v>
       </c>
       <c r="Y20" s="1">
-        <v>-0.0024105001740615277</v>
+        <v>-0.00241050017418367</v>
       </c>
       <c r="Z20" s="1">
-        <v>-0.0023848068546120402</v>
+        <v>-0.0023848068547387305</v>
       </c>
       <c r="AA20" s="1">
-        <v>-0.0003878449758052975</v>
+        <v>-0.00038784497580496134</v>
       </c>
       <c r="AB20" s="1">
-        <v>-0.00056022104608678301</v>
+        <v>-0.00056022104608685944</v>
       </c>
       <c r="AC20" s="1">
-        <v>-0.00058396406289003245</v>
+        <v>-0.00058396406288942009</v>
       </c>
       <c r="AD20" s="1">
-        <v>-1.0893057927756727e-05</v>
+        <v>-1.0893057927792397e-05</v>
       </c>
       <c r="AE20" s="1">
-        <v>3.7360694907531645e-06</v>
+        <v>3.7360694915483726e-06</v>
       </c>
       <c r="AF20" s="1">
-        <v>6.011640845755839e-05</v>
+        <v>6.0116408457154416e-05</v>
       </c>
       <c r="AG20" s="1">
-        <v>-5.7736549650522001e-05</v>
+        <v>-5.7736549650572958e-05</v>
       </c>
       <c r="AH20" s="1">
-        <v>-1.8571938081750404e-06</v>
+        <v>-1.8571938082011697e-06</v>
       </c>
       <c r="AI20" s="1">
-        <v>-3.954522552119589e-05</v>
+        <v>-3.9545225521284361e-05</v>
       </c>
       <c r="AJ20" s="1">
-        <v>-2.6652271197614551e-05</v>
+        <v>-2.6652271197591566e-05</v>
       </c>
       <c r="AK20" s="1">
-        <v>-4.5443419750162734e-06</v>
+        <v>-4.5443419750242423e-06</v>
       </c>
       <c r="AL20" s="1">
-        <v>0.0032987591985131665</v>
+        <v>0.0032987591986270454</v>
       </c>
     </row>
     <row r="21">
@@ -2904,115 +2904,115 @@
         <v>48</v>
       </c>
       <c r="B21" s="1">
-        <v>0.075569581627067742</v>
+        <v>0.075569581627067312</v>
       </c>
       <c r="C21" s="1">
-        <v>-2.0068735687118123e-05</v>
+        <v>-2.0068735687166926e-05</v>
       </c>
       <c r="D21" s="1">
-        <v>1.6185001188869622e-05</v>
+        <v>1.6185001189615004e-05</v>
       </c>
       <c r="E21" s="1">
-        <v>-1.5440898339794633e-07</v>
+        <v>-1.5440898340530281e-07</v>
       </c>
       <c r="F21" s="1">
-        <v>0.00015029657207344359</v>
+        <v>0.00015029657206438746</v>
       </c>
       <c r="G21" s="1">
-        <v>2.4179731639195287e-05</v>
+        <v>2.4179731636134964e-05</v>
       </c>
       <c r="H21" s="1">
-        <v>5.1972346467689482e-05</v>
+        <v>5.1972346464425003e-05</v>
       </c>
       <c r="I21" s="1">
-        <v>0.00011033036714415255</v>
+        <v>0.00011033036714183992</v>
       </c>
       <c r="J21" s="1">
-        <v>1.663675364706994e-05</v>
+        <v>1.663675364717527e-05</v>
       </c>
       <c r="K21" s="1">
-        <v>0.00015006452857256277</v>
+        <v>0.00015006452857250298</v>
       </c>
       <c r="L21" s="1">
-        <v>-0.00017213043765208462</v>
+        <v>-0.00017213043765222413</v>
       </c>
       <c r="M21" s="1">
-        <v>-1.7453580828604919e-05</v>
+        <v>-1.7453580828694193e-05</v>
       </c>
       <c r="N21" s="1">
-        <v>0.00051330786188360654</v>
+        <v>0.00051330786187834447</v>
       </c>
       <c r="O21" s="1">
-        <v>-3.1227122834257784e-05</v>
+        <v>-3.1227122834457589e-05</v>
       </c>
       <c r="P21" s="1">
-        <v>0.0017198715456454294</v>
+        <v>0.0017198715452603902</v>
       </c>
       <c r="Q21" s="1">
-        <v>0.004388305253088115</v>
+        <v>0.0043883052527021738</v>
       </c>
       <c r="R21" s="1">
-        <v>-0.00056514999423953882</v>
+        <v>-0.00056514999463086468</v>
       </c>
       <c r="S21" s="1">
-        <v>0.00091519242865562012</v>
+        <v>0.00091519242826196279</v>
       </c>
       <c r="T21" s="1">
-        <v>-6.7817146290039156e-05</v>
+        <v>-6.7817146289645916e-05</v>
       </c>
       <c r="U21" s="1">
-        <v>-0.0020348727084594249</v>
+        <v>-0.0020348727084584916</v>
       </c>
       <c r="V21" s="1">
-        <v>0.005843576799743194</v>
+        <v>0.0058435767997463183</v>
       </c>
       <c r="W21" s="1">
-        <v>-9.9118373177880045e-05</v>
+        <v>-9.9118373174929524e-05</v>
       </c>
       <c r="X21" s="1">
-        <v>-0.011018821103718679</v>
+        <v>-0.01101882110419552</v>
       </c>
       <c r="Y21" s="1">
-        <v>-0.010999918461554866</v>
+        <v>-0.010999918462022303</v>
       </c>
       <c r="Z21" s="1">
-        <v>-0.010977962044143029</v>
+        <v>-0.010977962044628857</v>
       </c>
       <c r="AA21" s="1">
-        <v>0.00022822329330723963</v>
+        <v>0.00022822329330622661</v>
       </c>
       <c r="AB21" s="1">
-        <v>4.0772771981555512e-06</v>
+        <v>4.0772771973962845e-06</v>
       </c>
       <c r="AC21" s="1">
-        <v>-1.9137050595889691e-05</v>
+        <v>-1.913705059491933e-05</v>
       </c>
       <c r="AD21" s="1">
-        <v>-3.592245507663287e-06</v>
+        <v>-3.5922455083543304e-06</v>
       </c>
       <c r="AE21" s="1">
-        <v>5.4820369696419874e-05</v>
+        <v>5.4820369697939166e-05</v>
       </c>
       <c r="AF21" s="1">
-        <v>-0.00030547754276210063</v>
+        <v>-0.00030547754276424649</v>
       </c>
       <c r="AG21" s="1">
-        <v>-8.4769767593244338e-05</v>
+        <v>-8.4769767593858864e-05</v>
       </c>
       <c r="AH21" s="1">
-        <v>-0.00016451525623779385</v>
+        <v>-0.00016451525623809141</v>
       </c>
       <c r="AI21" s="1">
-        <v>-0.00013496827790804257</v>
+        <v>-0.0001349682779086701</v>
       </c>
       <c r="AJ21" s="1">
-        <v>-7.408986158921908e-05</v>
+        <v>-7.4089861589561688e-05</v>
       </c>
       <c r="AK21" s="1">
-        <v>8.9084164345785153e-06</v>
+        <v>8.9084164345541207e-06</v>
       </c>
       <c r="AL21" s="1">
-        <v>0.010562799687303313</v>
+        <v>0.010562799687762508</v>
       </c>
     </row>
     <row r="22">
@@ -3020,115 +3020,115 @@
         <v>49</v>
       </c>
       <c r="B22" s="1">
-        <v>-0.035616729557472158</v>
+        <v>-0.035616729557471798</v>
       </c>
       <c r="C22" s="1">
-        <v>-2.5432879730762264e-05</v>
+        <v>-2.5432879730769972e-05</v>
       </c>
       <c r="D22" s="1">
-        <v>6.4068447314234521e-06</v>
+        <v>6.4068447322269229e-06</v>
       </c>
       <c r="E22" s="1">
-        <v>-5.0671466925641377e-08</v>
+        <v>-5.0671466933557257e-08</v>
       </c>
       <c r="F22" s="1">
-        <v>-3.6740018577273594e-05</v>
+        <v>-3.6740018586093023e-05</v>
       </c>
       <c r="G22" s="1">
-        <v>-4.5906057484904285e-05</v>
+        <v>-4.5906057487950534e-05</v>
       </c>
       <c r="H22" s="1">
-        <v>-4.9845849220843882e-05</v>
+        <v>-4.9845849224094022e-05</v>
       </c>
       <c r="I22" s="1">
-        <v>-5.2430592832602031e-05</v>
+        <v>-5.2430592834899699e-05</v>
       </c>
       <c r="J22" s="1">
-        <v>0.0001326808006227672</v>
+        <v>0.00013268080062286484</v>
       </c>
       <c r="K22" s="1">
-        <v>1.82916784940932e-05</v>
+        <v>1.8291678494074247e-05</v>
       </c>
       <c r="L22" s="1">
-        <v>-1.5859190370739438e-05</v>
+        <v>-1.5859190370915997e-05</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.00023490384988515743</v>
+        <v>-0.00023490384988524314</v>
       </c>
       <c r="N22" s="1">
-        <v>-0.00058533840420309713</v>
+        <v>-0.00058533840420834336</v>
       </c>
       <c r="O22" s="1">
-        <v>-2.8356771281659932e-05</v>
+        <v>-2.835677128185168e-05</v>
       </c>
       <c r="P22" s="1">
-        <v>0.0013638838286421755</v>
+        <v>0.0013638838282574658</v>
       </c>
       <c r="Q22" s="1">
-        <v>0.0015343727605800685</v>
+        <v>0.0015343727601956209</v>
       </c>
       <c r="R22" s="1">
-        <v>0.0025464546302981072</v>
+        <v>0.0025464546299083166</v>
       </c>
       <c r="S22" s="1">
-        <v>-0.0015527121524817489</v>
+        <v>-0.001552712152873629</v>
       </c>
       <c r="T22" s="1">
-        <v>-0.0028660391554443231</v>
+        <v>-0.0028660391554439567</v>
       </c>
       <c r="U22" s="1">
-        <v>-0.00038764175108789298</v>
+        <v>-0.00038764175108702562</v>
       </c>
       <c r="V22" s="1">
-        <v>-9.9118373177880045e-05</v>
+        <v>-9.9118373174929524e-05</v>
       </c>
       <c r="W22" s="1">
-        <v>0.0085686142552429817</v>
+        <v>0.0085686142552456879</v>
       </c>
       <c r="X22" s="1">
-        <v>-0.010723971978390612</v>
+        <v>-0.010723971978856004</v>
       </c>
       <c r="Y22" s="1">
-        <v>-0.010601878337376037</v>
+        <v>-0.010601878337834117</v>
       </c>
       <c r="Z22" s="1">
-        <v>-0.010673570833174353</v>
+        <v>-0.010673570833647002</v>
       </c>
       <c r="AA22" s="1">
-        <v>-3.9623458379323291e-05</v>
+        <v>-3.9623458380004875e-05</v>
       </c>
       <c r="AB22" s="1">
-        <v>-1.7837023743604019e-05</v>
+        <v>-1.7837023744276116e-05</v>
       </c>
       <c r="AC22" s="1">
-        <v>-5.1028335180497235e-05</v>
+        <v>-5.1028335179397421e-05</v>
       </c>
       <c r="AD22" s="1">
-        <v>-1.7141068717212073e-06</v>
+        <v>-1.7141068722926632e-06</v>
       </c>
       <c r="AE22" s="1">
-        <v>0.00010217752358129644</v>
+        <v>0.0001021775235828308</v>
       </c>
       <c r="AF22" s="1">
-        <v>-5.6455914824453998e-05</v>
+        <v>-5.6455914826340076e-05</v>
       </c>
       <c r="AG22" s="1">
-        <v>-0.00012380109557395781</v>
+        <v>-0.00012380109557450641</v>
       </c>
       <c r="AH22" s="1">
-        <v>-2.7603420272297825e-05</v>
+        <v>-2.7603420272569634e-05</v>
       </c>
       <c r="AI22" s="1">
-        <v>2.9601765706782895e-05</v>
+        <v>2.9601765706200461e-05</v>
       </c>
       <c r="AJ22" s="1">
-        <v>-8.5639203866032547e-05</v>
+        <v>-8.5639203866329835e-05</v>
       </c>
       <c r="AK22" s="1">
-        <v>3.3498287454496374e-06</v>
+        <v>3.3498287454164066e-06</v>
       </c>
       <c r="AL22" s="1">
-        <v>0.01055815120471231</v>
+        <v>0.010558151205160115</v>
       </c>
     </row>
     <row r="23">
@@ -3136,115 +3136,115 @@
         <v>50</v>
       </c>
       <c r="B23" s="1">
-        <v>-2.8026033842805047</v>
+        <v>-2.8026033842806295</v>
       </c>
       <c r="C23" s="1">
-        <v>-0.00026348219367271301</v>
+        <v>-0.00026348219363690772</v>
       </c>
       <c r="D23" s="1">
-        <v>-0.00055454691565844983</v>
+        <v>-0.00055454691573372523</v>
       </c>
       <c r="E23" s="1">
-        <v>4.6713630258071757e-06</v>
+        <v>4.6713630265179465e-06</v>
       </c>
       <c r="F23" s="1">
-        <v>0.020882061654932102</v>
+        <v>0.0208820616561626</v>
       </c>
       <c r="G23" s="1">
-        <v>0.0034251536520370548</v>
+        <v>0.0034251536524958284</v>
       </c>
       <c r="H23" s="1">
-        <v>0.0031460719514642089</v>
+        <v>0.0031460719519514468</v>
       </c>
       <c r="I23" s="1">
-        <v>0.001180147778312262</v>
+        <v>0.001180147778641697</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.00042837014297512205</v>
+        <v>-0.00042837014299954311</v>
       </c>
       <c r="K23" s="1">
-        <v>6.8672731479027979e-05</v>
+        <v>6.8672731485651086e-05</v>
       </c>
       <c r="L23" s="1">
-        <v>1.5649191214688145e-05</v>
+        <v>1.5649191223885873e-05</v>
       </c>
       <c r="M23" s="1">
-        <v>0.00019164360641002139</v>
+        <v>0.00019164360643084133</v>
       </c>
       <c r="N23" s="1">
-        <v>0.01129787240271835</v>
+        <v>0.011297872403237246</v>
       </c>
       <c r="O23" s="1">
-        <v>0.00058826385054559587</v>
+        <v>0.00058826385057323446</v>
       </c>
       <c r="P23" s="1">
-        <v>0.7107605974445681</v>
+        <v>0.71076059748483811</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.74501406541298532</v>
+        <v>0.74501406545420545</v>
       </c>
       <c r="R23" s="1">
-        <v>0.7573815291243835</v>
+        <v>0.75738152916632751</v>
       </c>
       <c r="S23" s="1">
-        <v>0.76032256847687363</v>
+        <v>0.7603225685192021</v>
       </c>
       <c r="T23" s="1">
-        <v>-0.0016237481804599301</v>
+        <v>-0.0016237481805066764</v>
       </c>
       <c r="U23" s="1">
-        <v>-0.0024866414558549913</v>
+        <v>-0.0024866414559785686</v>
       </c>
       <c r="V23" s="1">
-        <v>-0.011018821103718679</v>
+        <v>-0.01101882110419552</v>
       </c>
       <c r="W23" s="1">
-        <v>-0.010723971978390612</v>
+        <v>-0.010723971978856004</v>
       </c>
       <c r="X23" s="1">
-        <v>1.0023275196660451</v>
+        <v>1.0023275197195951</v>
       </c>
       <c r="Y23" s="1">
-        <v>1.0013715707139523</v>
+        <v>1.0013715707652691</v>
       </c>
       <c r="Z23" s="1">
-        <v>1.001589077645276</v>
+        <v>1.0015890777007193</v>
       </c>
       <c r="AA23" s="1">
-        <v>0.0042157656143863437</v>
+        <v>0.0042157656146895456</v>
       </c>
       <c r="AB23" s="1">
-        <v>-0.00063177520790938524</v>
+        <v>-0.00063177520782889407</v>
       </c>
       <c r="AC23" s="1">
-        <v>-0.00022561678770854909</v>
+        <v>-0.00022561678768534543</v>
       </c>
       <c r="AD23" s="1">
-        <v>0.00047976145122928526</v>
+        <v>0.00047976145134089737</v>
       </c>
       <c r="AE23" s="1">
-        <v>-0.0034962861787465882</v>
+        <v>-0.0034962861789477606</v>
       </c>
       <c r="AF23" s="1">
-        <v>0.007131210748180683</v>
+        <v>0.0071312107485558274</v>
       </c>
       <c r="AG23" s="1">
-        <v>0.0017716829033989079</v>
+        <v>0.001771682903444538</v>
       </c>
       <c r="AH23" s="1">
-        <v>0.00012953566858178722</v>
+        <v>0.00012953566861018118</v>
       </c>
       <c r="AI23" s="1">
-        <v>0.0011656447634584843</v>
+        <v>0.0011656447635169931</v>
       </c>
       <c r="AJ23" s="1">
-        <v>0.00037738879194731956</v>
+        <v>0.00037738879195553521</v>
       </c>
       <c r="AK23" s="1">
-        <v>-0.00010738827251124961</v>
+        <v>-0.00010738827250383887</v>
       </c>
       <c r="AL23" s="1">
-        <v>-0.98716862852262643</v>
+        <v>-0.9871686285735366</v>
       </c>
     </row>
     <row r="24">
@@ -3252,115 +3252,115 @@
         <v>51</v>
       </c>
       <c r="B24" s="1">
-        <v>-2.9689314210940645</v>
+        <v>-2.968931421094188</v>
       </c>
       <c r="C24" s="1">
-        <v>-0.00027818846895300491</v>
+        <v>-0.00027818846891748499</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.00065869397070566159</v>
+        <v>-0.0006586939707827102</v>
       </c>
       <c r="E24" s="1">
-        <v>5.9549460063740453e-06</v>
+        <v>5.9549460071057547e-06</v>
       </c>
       <c r="F24" s="1">
-        <v>0.021477836863667273</v>
+        <v>0.021477836864862616</v>
       </c>
       <c r="G24" s="1">
-        <v>0.0041698235072124478</v>
+        <v>0.0041698235076642462</v>
       </c>
       <c r="H24" s="1">
-        <v>0.0036037377633782266</v>
+        <v>0.0036037377638609047</v>
       </c>
       <c r="I24" s="1">
-        <v>0.0013848364760086923</v>
+        <v>0.0013848364763364685</v>
       </c>
       <c r="J24" s="1">
-        <v>-0.00046011995418190796</v>
+        <v>-0.00046011995420648649</v>
       </c>
       <c r="K24" s="1">
-        <v>1.1433355032000357e-05</v>
+        <v>1.1433355040772746e-05</v>
       </c>
       <c r="L24" s="1">
-        <v>5.4963951685436705e-06</v>
+        <v>5.4963951757263616e-06</v>
       </c>
       <c r="M24" s="1">
-        <v>0.00017868822374644635</v>
+        <v>0.00017868822376718846</v>
       </c>
       <c r="N24" s="1">
-        <v>0.011419740148282218</v>
+        <v>0.011419740148772829</v>
       </c>
       <c r="O24" s="1">
-        <v>0.00058849217651018757</v>
+        <v>0.00058849217653722833</v>
       </c>
       <c r="P24" s="1">
-        <v>0.71029302499972713</v>
+        <v>0.71029302503801439</v>
       </c>
       <c r="Q24" s="1">
-        <v>0.74519501111925612</v>
+        <v>0.74519501115852527</v>
       </c>
       <c r="R24" s="1">
-        <v>0.7579522975737949</v>
+        <v>0.75795229761376981</v>
       </c>
       <c r="S24" s="1">
-        <v>0.76080340546628056</v>
+        <v>0.76080340550664061</v>
       </c>
       <c r="T24" s="1">
-        <v>-0.0015414870030749171</v>
+        <v>-0.0015414870031196558</v>
       </c>
       <c r="U24" s="1">
-        <v>-0.0024105001740615277</v>
+        <v>-0.00241050017418367</v>
       </c>
       <c r="V24" s="1">
-        <v>-0.010999918461554866</v>
+        <v>-0.010999918462022303</v>
       </c>
       <c r="W24" s="1">
-        <v>-0.010601878337376037</v>
+        <v>-0.010601878337834117</v>
       </c>
       <c r="X24" s="1">
-        <v>1.0013715707139523</v>
+        <v>1.0013715707652691</v>
       </c>
       <c r="Y24" s="1">
-        <v>1.0041090232899514</v>
+        <v>1.0041090233414969</v>
       </c>
       <c r="Z24" s="1">
-        <v>1.0038505718475377</v>
+        <v>1.0038505719032162</v>
       </c>
       <c r="AA24" s="1">
-        <v>0.0051865838041601359</v>
+        <v>0.0051865838044634696</v>
       </c>
       <c r="AB24" s="1">
-        <v>-0.00090789380157650645</v>
+        <v>-0.00090789380149501608</v>
       </c>
       <c r="AC24" s="1">
-        <v>-0.00070938165043382684</v>
+        <v>-0.00070938165041145584</v>
       </c>
       <c r="AD24" s="1">
-        <v>0.00076230956988051352</v>
+        <v>0.00076230956999237542</v>
       </c>
       <c r="AE24" s="1">
-        <v>-0.0035126614777413745</v>
+        <v>-0.0035126614779439069</v>
       </c>
       <c r="AF24" s="1">
-        <v>0.007338299402368853</v>
+        <v>0.0073382994027448856</v>
       </c>
       <c r="AG24" s="1">
-        <v>0.0017926964249775912</v>
+        <v>0.0017926964250237765</v>
       </c>
       <c r="AH24" s="1">
-        <v>4.866613503076711e-05</v>
+        <v>4.8666135059355353e-05</v>
       </c>
       <c r="AI24" s="1">
-        <v>0.0011997182148691943</v>
+        <v>0.0011997182149282581</v>
       </c>
       <c r="AJ24" s="1">
-        <v>0.0004472020362410456</v>
+        <v>0.00044720203624998289</v>
       </c>
       <c r="AK24" s="1">
-        <v>-0.00011844307143032973</v>
+        <v>-0.0001184430714229745</v>
       </c>
       <c r="AL24" s="1">
-        <v>-0.98731696874896324</v>
+        <v>-0.98731696880008479</v>
       </c>
     </row>
     <row r="25">
@@ -3368,115 +3368,115 @@
         <v>52</v>
       </c>
       <c r="B25" s="1">
-        <v>-2.8408637394526415</v>
+        <v>-2.8408637394527663</v>
       </c>
       <c r="C25" s="1">
-        <v>0.00010511101503655053</v>
+        <v>0.00010511101507029488</v>
       </c>
       <c r="D25" s="1">
-        <v>-0.0006313664102661087</v>
+        <v>-0.00063136641034565043</v>
       </c>
       <c r="E25" s="1">
-        <v>5.7235865045181206e-06</v>
+        <v>5.7235865052717335e-06</v>
       </c>
       <c r="F25" s="1">
-        <v>0.021653582213319655</v>
+        <v>0.02165358221458355</v>
       </c>
       <c r="G25" s="1">
-        <v>0.0043141288214769494</v>
+        <v>0.0043141288219489538</v>
       </c>
       <c r="H25" s="1">
-        <v>0.0040077533179542092</v>
+        <v>0.0040077533184546873</v>
       </c>
       <c r="I25" s="1">
-        <v>0.0016107494537340469</v>
+        <v>0.0016107494540751374</v>
       </c>
       <c r="J25" s="1">
-        <v>-0.00049233701362342674</v>
+        <v>-0.00049233701364818645</v>
       </c>
       <c r="K25" s="1">
-        <v>-1.8126425720113047e-05</v>
+        <v>-1.8126425713237498e-05</v>
       </c>
       <c r="L25" s="1">
-        <v>-8.3347339625704391e-05</v>
+        <v>-8.3347339615637777e-05</v>
       </c>
       <c r="M25" s="1">
-        <v>0.00024096496135118069</v>
+        <v>0.00024096496137166151</v>
       </c>
       <c r="N25" s="1">
-        <v>0.011054692434949444</v>
+        <v>0.011054692435492584</v>
       </c>
       <c r="O25" s="1">
-        <v>0.00058999178502670661</v>
+        <v>0.00058999178505500722</v>
       </c>
       <c r="P25" s="1">
-        <v>0.71046833570272705</v>
+        <v>0.71046833574460666</v>
       </c>
       <c r="Q25" s="1">
-        <v>0.74512419512729289</v>
+        <v>0.7451241951701002</v>
       </c>
       <c r="R25" s="1">
-        <v>0.75804593463615277</v>
+        <v>0.75804593467970283</v>
       </c>
       <c r="S25" s="1">
-        <v>0.76114881223271014</v>
+        <v>0.76114881227665465</v>
       </c>
       <c r="T25" s="1">
-        <v>-0.0015325373390287238</v>
+        <v>-0.0015325373390766162</v>
       </c>
       <c r="U25" s="1">
-        <v>-0.0023848068546120402</v>
+        <v>-0.0023848068547387305</v>
       </c>
       <c r="V25" s="1">
-        <v>-0.010977962044143029</v>
+        <v>-0.010977962044628857</v>
       </c>
       <c r="W25" s="1">
-        <v>-0.010673570833174353</v>
+        <v>-0.010673570833647002</v>
       </c>
       <c r="X25" s="1">
-        <v>1.001589077645276</v>
+        <v>1.0015890777007193</v>
       </c>
       <c r="Y25" s="1">
-        <v>1.0038505718475377</v>
+        <v>1.0038505719032162</v>
       </c>
       <c r="Z25" s="1">
-        <v>1.0063746809608507</v>
+        <v>1.0063746810165293</v>
       </c>
       <c r="AA25" s="1">
-        <v>0.0050377664607648212</v>
+        <v>0.0050377664610681272</v>
       </c>
       <c r="AB25" s="1">
-        <v>-0.00075682703402024654</v>
+        <v>-0.00075682703393890882</v>
       </c>
       <c r="AC25" s="1">
-        <v>-0.00095327411143908414</v>
+        <v>-0.00095327411141671314</v>
       </c>
       <c r="AD25" s="1">
-        <v>0.00073541950839775549</v>
+        <v>0.00073541950850958965</v>
       </c>
       <c r="AE25" s="1">
-        <v>-0.003632651613509591</v>
+        <v>-0.0036326516137119291</v>
       </c>
       <c r="AF25" s="1">
-        <v>0.0073981019450310992</v>
+        <v>0.0073981019454069097</v>
       </c>
       <c r="AG25" s="1">
-        <v>0.0019831191463941522</v>
+        <v>0.0019831191464402265</v>
       </c>
       <c r="AH25" s="1">
-        <v>0.00016706629061344347</v>
+        <v>0.00016706629064208722</v>
       </c>
       <c r="AI25" s="1">
-        <v>0.0013326437124387969</v>
+        <v>0.0013326437124978607</v>
       </c>
       <c r="AJ25" s="1">
-        <v>0.00049649066349660709</v>
+        <v>0.00049649066350537785</v>
       </c>
       <c r="AK25" s="1">
-        <v>-0.00014733381017947855</v>
+        <v>-0.00014733381017209557</v>
       </c>
       <c r="AL25" s="1">
-        <v>-0.98801862919393391</v>
+        <v>-0.98801862924506056</v>
       </c>
     </row>
     <row r="26">
@@ -3484,115 +3484,115 @@
         <v>53</v>
       </c>
       <c r="B26" s="1">
-        <v>0.80818453660195444</v>
+        <v>0.80818453660194567</v>
       </c>
       <c r="C26" s="1">
-        <v>-0.00015603137491062381</v>
+        <v>-0.00015603137491074513</v>
       </c>
       <c r="D26" s="1">
-        <v>0.00030664793768514015</v>
+        <v>0.00030664793768516319</v>
       </c>
       <c r="E26" s="1">
-        <v>-2.3734237045282386e-06</v>
+        <v>-2.3734237045292631e-06</v>
       </c>
       <c r="F26" s="1">
-        <v>0.00054615923700245233</v>
+        <v>0.00054615923700768176</v>
       </c>
       <c r="G26" s="1">
-        <v>0.0004572597289908171</v>
+        <v>0.00045725972899315036</v>
       </c>
       <c r="H26" s="1">
-        <v>0.00025443491395772092</v>
+        <v>0.00025443491395967232</v>
       </c>
       <c r="I26" s="1">
-        <v>0.00061202778242823647</v>
+        <v>0.00061202778242956885</v>
       </c>
       <c r="J26" s="1">
-        <v>1.9075395905195623e-05</v>
+        <v>1.9075395905088165e-05</v>
       </c>
       <c r="K26" s="1">
-        <v>0.00064985580312339664</v>
+        <v>0.00064985580312263845</v>
       </c>
       <c r="L26" s="1">
-        <v>-4.1163920117300018e-05</v>
+        <v>-4.1163920116798466e-05</v>
       </c>
       <c r="M26" s="1">
-        <v>5.2703957415744592e-05</v>
+        <v>5.2703957415865108e-05</v>
       </c>
       <c r="N26" s="1">
-        <v>0.001502875202934737</v>
+        <v>0.0015028752029381265</v>
       </c>
       <c r="O26" s="1">
-        <v>-1.4428049344542317e-05</v>
+        <v>-1.4428049344474507e-05</v>
       </c>
       <c r="P26" s="1">
-        <v>0.001296564401397575</v>
+        <v>0.001296564401674874</v>
       </c>
       <c r="Q26" s="1">
-        <v>0.0015188009392918186</v>
+        <v>0.0015188009395610963</v>
       </c>
       <c r="R26" s="1">
-        <v>-0.00027090509826546705</v>
+        <v>-0.00027090509799336526</v>
       </c>
       <c r="S26" s="1">
-        <v>-0.00019385146589492863</v>
+        <v>-0.00019385146562196642</v>
       </c>
       <c r="T26" s="1">
-        <v>5.4064131018278633e-06</v>
+        <v>5.4064131018404265e-06</v>
       </c>
       <c r="U26" s="1">
-        <v>-0.0003878449758052975</v>
+        <v>-0.00038784497580496134</v>
       </c>
       <c r="V26" s="1">
-        <v>0.00022822329330723963</v>
+        <v>0.00022822329330622661</v>
       </c>
       <c r="W26" s="1">
-        <v>-3.9623458379323291e-05</v>
+        <v>-3.9623458380004875e-05</v>
       </c>
       <c r="X26" s="1">
-        <v>0.0042157656143863437</v>
+        <v>0.0042157656146895456</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.0051865838041601359</v>
+        <v>0.0051865838044634696</v>
       </c>
       <c r="Z26" s="1">
-        <v>0.0050377664607648212</v>
+        <v>0.0050377664610681272</v>
       </c>
       <c r="AA26" s="1">
-        <v>0.018308020987471311</v>
+        <v>0.018308020987470551</v>
       </c>
       <c r="AB26" s="1">
-        <v>0.0044298373167322418</v>
+        <v>0.0044298373167304412</v>
       </c>
       <c r="AC26" s="1">
-        <v>0.0040346017827897415</v>
+        <v>0.0040346017827896513</v>
       </c>
       <c r="AD26" s="1">
-        <v>0.00094585274078719955</v>
+        <v>0.00094585274078687917</v>
       </c>
       <c r="AE26" s="1">
-        <v>0.00011999192595958815</v>
+        <v>0.00011999192595928696</v>
       </c>
       <c r="AF26" s="1">
-        <v>-0.00027015504543707013</v>
+        <v>-0.00027015504543695477</v>
       </c>
       <c r="AG26" s="1">
-        <v>2.5849422305353545e-05</v>
+        <v>2.5849422304897313e-05</v>
       </c>
       <c r="AH26" s="1">
-        <v>-0.0004890947590466758</v>
+        <v>-0.0004890947590465212</v>
       </c>
       <c r="AI26" s="1">
-        <v>-0.00010432961155413308</v>
+        <v>-0.00010432961155393793</v>
       </c>
       <c r="AJ26" s="1">
-        <v>0.00010121899882894114</v>
+        <v>0.00010121899882867963</v>
       </c>
       <c r="AK26" s="1">
-        <v>-3.4520621058288905e-05</v>
+        <v>-3.4520621058144272e-05</v>
       </c>
       <c r="AL26" s="1">
-        <v>-0.018580896456864827</v>
+        <v>-0.018580896457169357</v>
       </c>
     </row>
     <row r="27">
@@ -3600,115 +3600,115 @@
         <v>54</v>
       </c>
       <c r="B27" s="1">
-        <v>0.22807197713055322</v>
+        <v>0.22807197713055102</v>
       </c>
       <c r="C27" s="1">
-        <v>0.00017693113481951663</v>
+        <v>0.00017693113481946662</v>
       </c>
       <c r="D27" s="1">
-        <v>1.6471746527999335e-05</v>
+        <v>1.6471746527498543e-05</v>
       </c>
       <c r="E27" s="1">
-        <v>-1.4200885892225273e-07</v>
+        <v>-1.4200885891730547e-07</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.00080010563935088144</v>
+        <v>-0.00080010563934895438</v>
       </c>
       <c r="G27" s="1">
-        <v>-0.00052467239634628468</v>
+        <v>-0.00052467239634531356</v>
       </c>
       <c r="H27" s="1">
-        <v>-0.00017760195287848854</v>
+        <v>-0.00017760195287728657</v>
       </c>
       <c r="I27" s="1">
-        <v>0.00015327152039843053</v>
+        <v>0.00015327152039929483</v>
       </c>
       <c r="J27" s="1">
-        <v>-2.3870307439553413e-05</v>
+        <v>-2.3870307439601826e-05</v>
       </c>
       <c r="K27" s="1">
-        <v>0.00055637960424016948</v>
+        <v>0.00055637960424009087</v>
       </c>
       <c r="L27" s="1">
-        <v>-1.9375510236418637e-05</v>
+        <v>-1.9375510236351711e-05</v>
       </c>
       <c r="M27" s="1">
-        <v>2.7363902590949198e-05</v>
+        <v>2.7363902590985183e-05</v>
       </c>
       <c r="N27" s="1">
-        <v>-0.00018758123733207666</v>
+        <v>-0.00018758123733128562</v>
       </c>
       <c r="O27" s="1">
-        <v>4.8488587665390797e-07</v>
+        <v>4.8488587670062692e-07</v>
       </c>
       <c r="P27" s="1">
-        <v>-0.00041626977681320787</v>
+        <v>-0.00041626977675469912</v>
       </c>
       <c r="Q27" s="1">
-        <v>-0.0007118042989207457</v>
+        <v>-0.00071180429886116836</v>
       </c>
       <c r="R27" s="1">
-        <v>-0.00093892551120024204</v>
+        <v>-0.00093892551113944345</v>
       </c>
       <c r="S27" s="1">
-        <v>-0.00079294441965360729</v>
+        <v>-0.00079294441959186501</v>
       </c>
       <c r="T27" s="1">
-        <v>3.3830239596436895e-05</v>
+        <v>3.3830239596416701e-05</v>
       </c>
       <c r="U27" s="1">
-        <v>-0.00056022104608678301</v>
+        <v>-0.00056022104608685944</v>
       </c>
       <c r="V27" s="1">
-        <v>4.0772771981555512e-06</v>
+        <v>4.0772771973962845e-06</v>
       </c>
       <c r="W27" s="1">
-        <v>-1.7837023743604019e-05</v>
+        <v>-1.7837023744276116e-05</v>
       </c>
       <c r="X27" s="1">
-        <v>-0.00063177520790938524</v>
+        <v>-0.00063177520782889407</v>
       </c>
       <c r="Y27" s="1">
-        <v>-0.00090789380157650645</v>
+        <v>-0.00090789380149501608</v>
       </c>
       <c r="Z27" s="1">
-        <v>-0.00075682703402024654</v>
+        <v>-0.00075682703393890882</v>
       </c>
       <c r="AA27" s="1">
-        <v>0.0044298373167322418</v>
+        <v>0.0044298373167304412</v>
       </c>
       <c r="AB27" s="1">
-        <v>0.0058637729808378673</v>
+        <v>0.005863772980837483</v>
       </c>
       <c r="AC27" s="1">
-        <v>0.0044388045090924498</v>
+        <v>0.0044388045090908391</v>
       </c>
       <c r="AD27" s="1">
-        <v>0.00012943797811064832</v>
+        <v>0.00012943797811038445</v>
       </c>
       <c r="AE27" s="1">
-        <v>-6.2113828647474023e-05</v>
+        <v>-6.2113828648736576e-05</v>
       </c>
       <c r="AF27" s="1">
-        <v>5.8512797779614652e-05</v>
+        <v>5.8512797779488018e-05</v>
       </c>
       <c r="AG27" s="1">
-        <v>0.00016829653166048003</v>
+        <v>0.00016829653166041433</v>
       </c>
       <c r="AH27" s="1">
-        <v>7.1377680461136349e-05</v>
+        <v>7.1377680461084226e-05</v>
       </c>
       <c r="AI27" s="1">
-        <v>0.00012302914600908588</v>
+        <v>0.00012302914600906094</v>
       </c>
       <c r="AJ27" s="1">
-        <v>0.00030856015825745167</v>
+        <v>0.00030856015825733068</v>
       </c>
       <c r="AK27" s="1">
-        <v>-2.0108878353096546e-05</v>
+        <v>-2.0108878353166531e-05</v>
       </c>
       <c r="AL27" s="1">
-        <v>-0.0039542442136659235</v>
+        <v>-0.0039542442137415973</v>
       </c>
     </row>
     <row r="28">
@@ -3716,115 +3716,115 @@
         <v>55</v>
       </c>
       <c r="B28" s="1">
-        <v>-0.029831920626588425</v>
+        <v>-0.029831920626595336</v>
       </c>
       <c r="C28" s="1">
-        <v>0.00019335639665853918</v>
+        <v>0.00019335639665834001</v>
       </c>
       <c r="D28" s="1">
-        <v>0.00015400732713688288</v>
+        <v>0.00015400732713753294</v>
       </c>
       <c r="E28" s="1">
-        <v>-2.4700097629126476e-06</v>
+        <v>-2.4700097629193896e-06</v>
       </c>
       <c r="F28" s="1">
-        <v>-8.0399581780699232e-06</v>
+        <v>-8.0399581794976006e-06</v>
       </c>
       <c r="G28" s="1">
-        <v>-3.7187003444040675e-05</v>
+        <v>-3.7187003445085195e-05</v>
       </c>
       <c r="H28" s="1">
-        <v>-0.00016060390037165104</v>
+        <v>-0.00016060390037307161</v>
       </c>
       <c r="I28" s="1">
-        <v>0.00011185002130279813</v>
+        <v>0.00011185002130178554</v>
       </c>
       <c r="J28" s="1">
-        <v>-1.3817399271839829e-05</v>
+        <v>-1.3817399271830618e-05</v>
       </c>
       <c r="K28" s="1">
-        <v>0.00058622495876161176</v>
+        <v>0.00058622495876110934</v>
       </c>
       <c r="L28" s="1">
-        <v>2.1611608991420687e-05</v>
+        <v>2.1611608991628807e-05</v>
       </c>
       <c r="M28" s="1">
-        <v>5.2723457177004285e-05</v>
+        <v>5.2723457176985115e-05</v>
       </c>
       <c r="N28" s="1">
-        <v>-0.00017570613249802284</v>
+        <v>-0.00017570613249740397</v>
       </c>
       <c r="O28" s="1">
-        <v>-1.2061443910948397e-06</v>
+        <v>-1.2061443911462851e-06</v>
       </c>
       <c r="P28" s="1">
-        <v>0.00027110308151009899</v>
+        <v>0.00027110308156277907</v>
       </c>
       <c r="Q28" s="1">
-        <v>0.00033124076570051342</v>
+        <v>0.00033124076574492234</v>
       </c>
       <c r="R28" s="1">
-        <v>0.00010619393080438244</v>
+        <v>0.00010619393084773665</v>
       </c>
       <c r="S28" s="1">
-        <v>0.00020409748504182645</v>
+        <v>0.00020409748508373737</v>
       </c>
       <c r="T28" s="1">
-        <v>9.7562196655723321e-06</v>
+        <v>9.7562196656840862e-06</v>
       </c>
       <c r="U28" s="1">
-        <v>-0.00058396406289003245</v>
+        <v>-0.00058396406288942009</v>
       </c>
       <c r="V28" s="1">
-        <v>-1.9137050595889691e-05</v>
+        <v>-1.913705059491933e-05</v>
       </c>
       <c r="W28" s="1">
-        <v>-5.1028335180497235e-05</v>
+        <v>-5.1028335179397421e-05</v>
       </c>
       <c r="X28" s="1">
-        <v>-0.00022561678770854909</v>
+        <v>-0.00022561678768534543</v>
       </c>
       <c r="Y28" s="1">
-        <v>-0.00070938165043382684</v>
+        <v>-0.00070938165041145584</v>
       </c>
       <c r="Z28" s="1">
-        <v>-0.00095327411143908414</v>
+        <v>-0.00095327411141671314</v>
       </c>
       <c r="AA28" s="1">
-        <v>0.0040346017827897415</v>
+        <v>0.0040346017827896513</v>
       </c>
       <c r="AB28" s="1">
-        <v>0.0044388045090924498</v>
+        <v>0.0044388045090908391</v>
       </c>
       <c r="AC28" s="1">
-        <v>0.009586899507133928</v>
+        <v>0.0095868995071346184</v>
       </c>
       <c r="AD28" s="1">
-        <v>0.00018306343056292092</v>
+        <v>0.00018306343056265044</v>
       </c>
       <c r="AE28" s="1">
-        <v>0.00023816590274408167</v>
+        <v>0.00023816590274545611</v>
       </c>
       <c r="AF28" s="1">
-        <v>0.00047684693733723816</v>
+        <v>0.00047684693733672729</v>
       </c>
       <c r="AG28" s="1">
-        <v>0.00026916140660062119</v>
+        <v>0.0002691614066002981</v>
       </c>
       <c r="AH28" s="1">
-        <v>6.8252774330585691e-05</v>
+        <v>6.8252774330598701e-05</v>
       </c>
       <c r="AI28" s="1">
-        <v>0.00027991961301195934</v>
+        <v>0.00027991961301197972</v>
       </c>
       <c r="AJ28" s="1">
-        <v>0.00039095289926541687</v>
+        <v>0.00039095289926532526</v>
       </c>
       <c r="AK28" s="1">
-        <v>-3.5030027346993561e-05</v>
+        <v>-3.5030027346988249e-05</v>
       </c>
       <c r="AL28" s="1">
-        <v>-0.0058035607550259828</v>
+        <v>-0.0058035607550810282</v>
       </c>
     </row>
     <row r="29">
@@ -3832,115 +3832,115 @@
         <v>56</v>
       </c>
       <c r="B29" s="1">
-        <v>0.14928150830030706</v>
+        <v>0.14928150830030806</v>
       </c>
       <c r="C29" s="1">
-        <v>0.00022658984800174789</v>
+        <v>0.00022658984800173011</v>
       </c>
       <c r="D29" s="1">
-        <v>6.862649303486748e-05</v>
+        <v>6.8626493034722088e-05</v>
       </c>
       <c r="E29" s="1">
-        <v>-3.4190658259346549e-07</v>
+        <v>-3.4190658259218621e-07</v>
       </c>
       <c r="F29" s="1">
-        <v>-2.4706411334543565e-05</v>
+        <v>-2.4706411332341008e-05</v>
       </c>
       <c r="G29" s="1">
-        <v>3.2536224191486354e-05</v>
+        <v>3.2536224192396786e-05</v>
       </c>
       <c r="H29" s="1">
-        <v>0.00025297884207914323</v>
+        <v>0.00025297884207999992</v>
       </c>
       <c r="I29" s="1">
-        <v>3.9091697350303129e-05</v>
+        <v>3.9091697350918088e-05</v>
       </c>
       <c r="J29" s="1">
-        <v>-1.5691099153444037e-05</v>
+        <v>-1.5691099153479379e-05</v>
       </c>
       <c r="K29" s="1">
-        <v>1.170422956090962e-05</v>
+        <v>1.1704229560753207e-05</v>
       </c>
       <c r="L29" s="1">
-        <v>-5.084441346616486e-05</v>
+        <v>-5.0844413466025743e-05</v>
       </c>
       <c r="M29" s="1">
-        <v>-1.6370943141980253e-05</v>
+        <v>-1.6370943141943552e-05</v>
       </c>
       <c r="N29" s="1">
-        <v>-0.00026076025471245378</v>
+        <v>-0.00026076025471121259</v>
       </c>
       <c r="O29" s="1">
-        <v>2.8649514887941415e-06</v>
+        <v>2.8649514888350329e-06</v>
       </c>
       <c r="P29" s="1">
-        <v>-0.00073917780573091313</v>
+        <v>-0.00073917780563757807</v>
       </c>
       <c r="Q29" s="1">
-        <v>-0.00084135438976470911</v>
+        <v>-0.00084135438967195691</v>
       </c>
       <c r="R29" s="1">
-        <v>-0.00045915250430560856</v>
+        <v>-0.00045915250421165593</v>
       </c>
       <c r="S29" s="1">
-        <v>-0.00040788370359221005</v>
+        <v>-0.00040788370349770231</v>
       </c>
       <c r="T29" s="1">
-        <v>0.00011582145678657206</v>
+        <v>0.00011582145678651221</v>
       </c>
       <c r="U29" s="1">
-        <v>-1.0893057927756727e-05</v>
+        <v>-1.0893057927792397e-05</v>
       </c>
       <c r="V29" s="1">
-        <v>-3.592245507663287e-06</v>
+        <v>-3.5922455083543304e-06</v>
       </c>
       <c r="W29" s="1">
-        <v>-1.7141068717212073e-06</v>
+        <v>-1.7141068722926632e-06</v>
       </c>
       <c r="X29" s="1">
-        <v>0.00047976145122928526</v>
+        <v>0.00047976145134089737</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.00076230956988051352</v>
+        <v>0.00076230956999237542</v>
       </c>
       <c r="Z29" s="1">
-        <v>0.00073541950839775549</v>
+        <v>0.00073541950850958965</v>
       </c>
       <c r="AA29" s="1">
-        <v>0.00094585274078719955</v>
+        <v>0.00094585274078687917</v>
       </c>
       <c r="AB29" s="1">
-        <v>0.00012943797811064832</v>
+        <v>0.00012943797811038445</v>
       </c>
       <c r="AC29" s="1">
-        <v>0.00018306343056292092</v>
+        <v>0.00018306343056265044</v>
       </c>
       <c r="AD29" s="1">
-        <v>0.0031859807130528899</v>
+        <v>0.0031859807130528396</v>
       </c>
       <c r="AE29" s="1">
-        <v>0.0014908262198285744</v>
+        <v>0.0014908262198282281</v>
       </c>
       <c r="AF29" s="1">
-        <v>0.0020111327053972715</v>
+        <v>0.0020111327053975781</v>
       </c>
       <c r="AG29" s="1">
-        <v>-1.4742999941962879e-05</v>
+        <v>-1.4742999941963313e-05</v>
       </c>
       <c r="AH29" s="1">
-        <v>-8.5426834694512718e-05</v>
+        <v>-8.5426834694473904e-05</v>
       </c>
       <c r="AI29" s="1">
-        <v>-2.1950547072984751e-05</v>
+        <v>-2.195054707288327e-05</v>
       </c>
       <c r="AJ29" s="1">
-        <v>1.5381095965998461e-05</v>
+        <v>1.5381095965978728e-05</v>
       </c>
       <c r="AK29" s="1">
-        <v>8.8045301172197128e-06</v>
+        <v>8.8045301172522388e-06</v>
       </c>
       <c r="AL29" s="1">
-        <v>-0.0049030518989783556</v>
+        <v>-0.0049030518990928161</v>
       </c>
     </row>
     <row r="30">
@@ -3948,115 +3948,115 @@
         <v>57</v>
       </c>
       <c r="B30" s="1">
-        <v>-0.121673970333832</v>
+        <v>-0.1216739703338339</v>
       </c>
       <c r="C30" s="1">
-        <v>0.00011484912744162687</v>
+        <v>0.00011484912744158963</v>
       </c>
       <c r="D30" s="1">
-        <v>0.00017306963129176239</v>
+        <v>0.00017306963129245666</v>
       </c>
       <c r="E30" s="1">
-        <v>-1.5425722565011119e-06</v>
+        <v>-1.5425722565083636e-06</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.0004986110511323691</v>
+        <v>-0.00049861105113622193</v>
       </c>
       <c r="G30" s="1">
-        <v>-0.00028498321159713981</v>
+        <v>-0.00028498321159828478</v>
       </c>
       <c r="H30" s="1">
-        <v>-5.3935154648180754e-05</v>
+        <v>-5.3935154649732573e-05</v>
       </c>
       <c r="I30" s="1">
-        <v>-1.0296938046014587e-05</v>
+        <v>-1.0296938047119281e-05</v>
       </c>
       <c r="J30" s="1">
-        <v>-2.4093106921045247e-05</v>
+        <v>-2.4093106921026318e-05</v>
       </c>
       <c r="K30" s="1">
-        <v>-3.647673240879665e-06</v>
+        <v>-3.6476732412744502e-06</v>
       </c>
       <c r="L30" s="1">
-        <v>2.0457992734635474e-05</v>
+        <v>2.0457992734769983e-05</v>
       </c>
       <c r="M30" s="1">
-        <v>-5.7529476346296735e-05</v>
+        <v>-5.7529476346300591e-05</v>
       </c>
       <c r="N30" s="1">
-        <v>1.9673136917242734e-05</v>
+        <v>1.9673136915017084e-05</v>
       </c>
       <c r="O30" s="1">
-        <v>-7.2317296396100757e-06</v>
+        <v>-7.231729639714647e-06</v>
       </c>
       <c r="P30" s="1">
-        <v>-8.1115652960289664e-05</v>
+        <v>-8.1115653112528996e-05</v>
       </c>
       <c r="Q30" s="1">
-        <v>-0.00019410960052287929</v>
+        <v>-0.00019410960067781091</v>
       </c>
       <c r="R30" s="1">
-        <v>-0.00055054595536291329</v>
+        <v>-0.00055054595552034291</v>
       </c>
       <c r="S30" s="1">
-        <v>-0.00063580147632330553</v>
+        <v>-0.00063580147648203966</v>
       </c>
       <c r="T30" s="1">
-        <v>-8.0669725409345449e-05</v>
+        <v>-8.0669725409119366e-05</v>
       </c>
       <c r="U30" s="1">
-        <v>3.7360694907531645e-06</v>
+        <v>3.7360694915483726e-06</v>
       </c>
       <c r="V30" s="1">
-        <v>5.4820369696419874e-05</v>
+        <v>5.4820369697939166e-05</v>
       </c>
       <c r="W30" s="1">
-        <v>0.00010217752358129644</v>
+        <v>0.0001021775235828308</v>
       </c>
       <c r="X30" s="1">
-        <v>-0.0034962861787465882</v>
+        <v>-0.0034962861789477606</v>
       </c>
       <c r="Y30" s="1">
-        <v>-0.0035126614777413745</v>
+        <v>-0.0035126614779439069</v>
       </c>
       <c r="Z30" s="1">
-        <v>-0.003632651613509591</v>
+        <v>-0.0036326516137119291</v>
       </c>
       <c r="AA30" s="1">
-        <v>0.00011999192595958815</v>
+        <v>0.00011999192595928696</v>
       </c>
       <c r="AB30" s="1">
-        <v>-6.2113828647474023e-05</v>
+        <v>-6.2113828648736576e-05</v>
       </c>
       <c r="AC30" s="1">
-        <v>0.00023816590274408167</v>
+        <v>0.00023816590274545611</v>
       </c>
       <c r="AD30" s="1">
-        <v>0.0014908262198285744</v>
+        <v>0.0014908262198282281</v>
       </c>
       <c r="AE30" s="1">
-        <v>0.0030727594197681998</v>
+        <v>0.0030727594197695806</v>
       </c>
       <c r="AF30" s="1">
-        <v>0.0017228631701784927</v>
+        <v>0.0017228631701775468</v>
       </c>
       <c r="AG30" s="1">
-        <v>-7.2216747102718396e-05</v>
+        <v>-7.2216747103245318e-05</v>
       </c>
       <c r="AH30" s="1">
-        <v>-0.00020604640822179536</v>
+        <v>-0.0002060464082218883</v>
       </c>
       <c r="AI30" s="1">
-        <v>-0.00020751997725205226</v>
+        <v>-0.00020751997725231204</v>
       </c>
       <c r="AJ30" s="1">
-        <v>-8.6036790780880069e-05</v>
+        <v>-8.6036790781136266e-05</v>
       </c>
       <c r="AK30" s="1">
-        <v>5.0424984362906647e-06</v>
+        <v>5.0424984363391014e-06</v>
       </c>
       <c r="AL30" s="1">
-        <v>-0.0021953742565006011</v>
+        <v>-0.0021953742563166571</v>
       </c>
     </row>
     <row r="31">
@@ -4064,115 +4064,115 @@
         <v>58</v>
       </c>
       <c r="B31" s="1">
-        <v>1.3152481146656907</v>
+        <v>1.3152481146656896</v>
       </c>
       <c r="C31" s="1">
-        <v>0.00069630728065239126</v>
+        <v>0.00069630728065236643</v>
       </c>
       <c r="D31" s="1">
-        <v>0.00010611991847014912</v>
+        <v>0.00010611991846971224</v>
       </c>
       <c r="E31" s="1">
-        <v>-6.770993893134014e-07</v>
+        <v>-6.7709938930937333e-07</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.00075115552716347248</v>
+        <v>-0.00075115552715650062</v>
       </c>
       <c r="G31" s="1">
-        <v>-0.00044609028407857697</v>
+        <v>-0.00044609028407598431</v>
       </c>
       <c r="H31" s="1">
-        <v>-0.00045170735578779417</v>
+        <v>-0.00045170735578525302</v>
       </c>
       <c r="I31" s="1">
-        <v>-0.00046364917288914913</v>
+        <v>-0.00046364917288734366</v>
       </c>
       <c r="J31" s="1">
-        <v>-4.300288743538768e-05</v>
+        <v>-4.3002887435480278e-05</v>
       </c>
       <c r="K31" s="1">
-        <v>-5.47726219558427e-06</v>
+        <v>-5.477262195828595e-06</v>
       </c>
       <c r="L31" s="1">
-        <v>1.0531096945841482e-05</v>
+        <v>1.0531096946118869e-05</v>
       </c>
       <c r="M31" s="1">
-        <v>-4.9955903661385066e-05</v>
+        <v>-4.9955903661294074e-05</v>
       </c>
       <c r="N31" s="1">
-        <v>-0.00096376385235637761</v>
+        <v>-0.00096376385235219259</v>
       </c>
       <c r="O31" s="1">
-        <v>5.903927805222598e-06</v>
+        <v>5.9039278053599935e-06</v>
       </c>
       <c r="P31" s="1">
-        <v>0.0050593527678394201</v>
+        <v>0.0050593527681538353</v>
       </c>
       <c r="Q31" s="1">
-        <v>0.0052413457905653438</v>
+        <v>0.0052413457908775385</v>
       </c>
       <c r="R31" s="1">
-        <v>0.0066392870316531738</v>
+        <v>0.0066392870319694763</v>
       </c>
       <c r="S31" s="1">
-        <v>0.0060795862446796356</v>
+        <v>0.0060795862449969373</v>
       </c>
       <c r="T31" s="1">
-        <v>0.00026045608561864764</v>
+        <v>0.00026045608561842137</v>
       </c>
       <c r="U31" s="1">
-        <v>6.011640845755839e-05</v>
+        <v>6.0116408457154416e-05</v>
       </c>
       <c r="V31" s="1">
-        <v>-0.00030547754276210063</v>
+        <v>-0.00030547754276424649</v>
       </c>
       <c r="W31" s="1">
-        <v>-5.6455914824453998e-05</v>
+        <v>-5.6455914826340076e-05</v>
       </c>
       <c r="X31" s="1">
-        <v>0.007131210748180683</v>
+        <v>0.0071312107485558274</v>
       </c>
       <c r="Y31" s="1">
-        <v>0.007338299402368853</v>
+        <v>0.0073382994027448856</v>
       </c>
       <c r="Z31" s="1">
-        <v>0.0073981019450310992</v>
+        <v>0.0073981019454069097</v>
       </c>
       <c r="AA31" s="1">
-        <v>-0.00027015504543707013</v>
+        <v>-0.00027015504543695477</v>
       </c>
       <c r="AB31" s="1">
-        <v>5.8512797779614652e-05</v>
+        <v>5.8512797779488018e-05</v>
       </c>
       <c r="AC31" s="1">
-        <v>0.00047684693733723816</v>
+        <v>0.00047684693733672729</v>
       </c>
       <c r="AD31" s="1">
-        <v>0.0020111327053972715</v>
+        <v>0.0020111327053975781</v>
       </c>
       <c r="AE31" s="1">
-        <v>0.0017228631701784927</v>
+        <v>0.0017228631701775468</v>
       </c>
       <c r="AF31" s="1">
-        <v>0.016981341980383168</v>
+        <v>0.016981341980384375</v>
       </c>
       <c r="AG31" s="1">
-        <v>-0.00011643673564320361</v>
+        <v>-0.0001164367356430128</v>
       </c>
       <c r="AH31" s="1">
-        <v>-0.00016076873320673073</v>
+        <v>-0.00016076873320652364</v>
       </c>
       <c r="AI31" s="1">
-        <v>6.4106848321297295e-05</v>
+        <v>6.4106848321708858e-05</v>
       </c>
       <c r="AJ31" s="1">
-        <v>-0.0002827201068666828</v>
+        <v>-0.00028272010686658001</v>
       </c>
       <c r="AK31" s="1">
-        <v>3.6855282286160185e-05</v>
+        <v>3.6855282286234561e-05</v>
       </c>
       <c r="AL31" s="1">
-        <v>-0.012742749750243199</v>
+        <v>-0.012742749750605511</v>
       </c>
     </row>
     <row r="32">
@@ -4180,115 +4180,115 @@
         <v>59</v>
       </c>
       <c r="B32" s="1">
-        <v>-0.073262504569937228</v>
+        <v>-0.073262504569937284</v>
       </c>
       <c r="C32" s="1">
-        <v>-9.5444803732204248e-06</v>
+        <v>-9.5444803732092575e-06</v>
       </c>
       <c r="D32" s="1">
-        <v>2.8935186044736372e-05</v>
+        <v>2.8935186044526796e-05</v>
       </c>
       <c r="E32" s="1">
-        <v>-2.9554011974343353e-07</v>
+        <v>-2.9554011974143877e-07</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.00016332808938981751</v>
+        <v>-0.0001633280893883985</v>
       </c>
       <c r="G32" s="1">
-        <v>-0.00020161923183942753</v>
+        <v>-0.00020161923183867596</v>
       </c>
       <c r="H32" s="1">
-        <v>-0.00022568533869324423</v>
+        <v>-0.00022568533869240506</v>
       </c>
       <c r="I32" s="1">
-        <v>-0.00018088263239688859</v>
+        <v>-0.00018088263239628621</v>
       </c>
       <c r="J32" s="1">
-        <v>-4.7552776869514134e-05</v>
+        <v>-4.7552776869551302e-05</v>
       </c>
       <c r="K32" s="1">
-        <v>3.6931049345794055e-05</v>
+        <v>3.693104934573109e-05</v>
       </c>
       <c r="L32" s="1">
-        <v>-2.3570093689754078e-05</v>
+        <v>-2.3570093689684537e-05</v>
       </c>
       <c r="M32" s="1">
-        <v>1.9182932206294718e-05</v>
+        <v>1.9182932206328806e-05</v>
       </c>
       <c r="N32" s="1">
-        <v>0.00048838442078575836</v>
+        <v>0.00048838442078615214</v>
       </c>
       <c r="O32" s="1">
-        <v>2.6390617494967102e-06</v>
+        <v>2.6390617495283689e-06</v>
       </c>
       <c r="P32" s="1">
-        <v>0.0010529188522405697</v>
+        <v>0.0010529188522705457</v>
       </c>
       <c r="Q32" s="1">
-        <v>0.00093920988924389714</v>
+        <v>0.00093920988927542748</v>
       </c>
       <c r="R32" s="1">
-        <v>0.0012715818800942413</v>
+        <v>0.0012715818801266598</v>
       </c>
       <c r="S32" s="1">
-        <v>0.00076581954053656087</v>
+        <v>0.00076581954056964552</v>
       </c>
       <c r="T32" s="1">
-        <v>-2.49759929468724e-05</v>
+        <v>-2.4975992946904601e-05</v>
       </c>
       <c r="U32" s="1">
-        <v>-5.7736549650522001e-05</v>
+        <v>-5.7736549650572958e-05</v>
       </c>
       <c r="V32" s="1">
-        <v>-8.4769767593244338e-05</v>
+        <v>-8.4769767593858864e-05</v>
       </c>
       <c r="W32" s="1">
-        <v>-0.00012380109557395781</v>
+        <v>-0.00012380109557450641</v>
       </c>
       <c r="X32" s="1">
-        <v>0.0017716829033989079</v>
+        <v>0.001771682903444538</v>
       </c>
       <c r="Y32" s="1">
-        <v>0.0017926964249775912</v>
+        <v>0.0017926964250237765</v>
       </c>
       <c r="Z32" s="1">
-        <v>0.0019831191463941522</v>
+        <v>0.0019831191464402265</v>
       </c>
       <c r="AA32" s="1">
-        <v>2.5849422305353545e-05</v>
+        <v>2.5849422304897313e-05</v>
       </c>
       <c r="AB32" s="1">
-        <v>0.00016829653166048003</v>
+        <v>0.00016829653166041433</v>
       </c>
       <c r="AC32" s="1">
-        <v>0.00026916140660062119</v>
+        <v>0.0002691614066002981</v>
       </c>
       <c r="AD32" s="1">
-        <v>-1.4742999941962879e-05</v>
+        <v>-1.4742999941963313e-05</v>
       </c>
       <c r="AE32" s="1">
-        <v>-7.2216747102718396e-05</v>
+        <v>-7.2216747103245318e-05</v>
       </c>
       <c r="AF32" s="1">
-        <v>-0.00011643673564320361</v>
+        <v>-0.0001164367356430128</v>
       </c>
       <c r="AG32" s="1">
-        <v>0.0043989486713171492</v>
+        <v>0.0043989486713172073</v>
       </c>
       <c r="AH32" s="1">
-        <v>0.0023408544370360452</v>
+        <v>0.0023408544370360973</v>
       </c>
       <c r="AI32" s="1">
-        <v>0.0023504390555683027</v>
+        <v>0.0023504390555683678</v>
       </c>
       <c r="AJ32" s="1">
-        <v>0.002354234421637682</v>
+        <v>0.0023542344216376915</v>
       </c>
       <c r="AK32" s="1">
-        <v>-8.5569978473513714e-05</v>
+        <v>-8.5569978473530898e-05</v>
       </c>
       <c r="AL32" s="1">
-        <v>-0.0032903127539880167</v>
+        <v>-0.0032903127540297224</v>
       </c>
     </row>
     <row r="33">
@@ -4296,115 +4296,115 @@
         <v>60</v>
       </c>
       <c r="B33" s="1">
-        <v>0.23572181237567036</v>
+        <v>0.23572181237567011</v>
       </c>
       <c r="C33" s="1">
-        <v>3.3924509545058812e-05</v>
+        <v>3.3924509545089589e-05</v>
       </c>
       <c r="D33" s="1">
-        <v>6.9042561322281524e-07</v>
+        <v>6.9042561320218829e-07</v>
       </c>
       <c r="E33" s="1">
-        <v>-7.1685799009015749e-08</v>
+        <v>-7.168579900884126e-08</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.00021652712268065838</v>
+        <v>-0.00021652712268000482</v>
       </c>
       <c r="G33" s="1">
-        <v>-0.00029782438912136146</v>
+        <v>-0.00029782438912112679</v>
       </c>
       <c r="H33" s="1">
-        <v>-0.00020708557683970252</v>
+        <v>-0.00020708557683944619</v>
       </c>
       <c r="I33" s="1">
-        <v>-0.00019226002972683905</v>
+        <v>-0.00019226002972664934</v>
       </c>
       <c r="J33" s="1">
-        <v>-3.6164875914466468e-05</v>
+        <v>-3.6164875914483172e-05</v>
       </c>
       <c r="K33" s="1">
-        <v>-8.8976663517633994e-06</v>
+        <v>-8.8976663518011432e-06</v>
       </c>
       <c r="L33" s="1">
-        <v>-7.9239280543692123e-06</v>
+        <v>-7.9239280543415652e-06</v>
       </c>
       <c r="M33" s="1">
-        <v>2.9254598987517492e-05</v>
+        <v>2.9254598987531018e-05</v>
       </c>
       <c r="N33" s="1">
-        <v>0.00012528393140078214</v>
+        <v>0.00012528393140102826</v>
       </c>
       <c r="O33" s="1">
-        <v>5.9570636788271419e-07</v>
+        <v>5.9570636789806921e-07</v>
       </c>
       <c r="P33" s="1">
-        <v>0.00069204524251523236</v>
+        <v>0.00069204524253621558</v>
       </c>
       <c r="Q33" s="1">
-        <v>0.00010790994071090132</v>
+        <v>0.00010790994073243965</v>
       </c>
       <c r="R33" s="1">
-        <v>0.000325715064898216</v>
+        <v>0.00032571506492011515</v>
       </c>
       <c r="S33" s="1">
-        <v>0.00014665216587794738</v>
+        <v>0.00014665216590011021</v>
       </c>
       <c r="T33" s="1">
-        <v>3.0720548170659178e-05</v>
+        <v>3.0720548170634458e-05</v>
       </c>
       <c r="U33" s="1">
-        <v>-1.8571938081750404e-06</v>
+        <v>-1.8571938082011697e-06</v>
       </c>
       <c r="V33" s="1">
-        <v>-0.00016451525623779385</v>
+        <v>-0.00016451525623809141</v>
       </c>
       <c r="W33" s="1">
-        <v>-2.7603420272297825e-05</v>
+        <v>-2.7603420272569634e-05</v>
       </c>
       <c r="X33" s="1">
-        <v>0.00012953566858178722</v>
+        <v>0.00012953566861018118</v>
       </c>
       <c r="Y33" s="1">
-        <v>4.866613503076711e-05</v>
+        <v>4.8666135059355353e-05</v>
       </c>
       <c r="Z33" s="1">
-        <v>0.00016706629061344347</v>
+        <v>0.00016706629064208722</v>
       </c>
       <c r="AA33" s="1">
-        <v>-0.0004890947590466758</v>
+        <v>-0.0004890947590465212</v>
       </c>
       <c r="AB33" s="1">
-        <v>7.1377680461136349e-05</v>
+        <v>7.1377680461084226e-05</v>
       </c>
       <c r="AC33" s="1">
-        <v>6.8252774330585691e-05</v>
+        <v>6.8252774330598701e-05</v>
       </c>
       <c r="AD33" s="1">
-        <v>-8.5426834694512718e-05</v>
+        <v>-8.5426834694473904e-05</v>
       </c>
       <c r="AE33" s="1">
-        <v>-0.00020604640822179536</v>
+        <v>-0.0002060464082218883</v>
       </c>
       <c r="AF33" s="1">
-        <v>-0.00016076873320673073</v>
+        <v>-0.00016076873320652364</v>
       </c>
       <c r="AG33" s="1">
-        <v>0.0023408544370360452</v>
+        <v>0.0023408544370360973</v>
       </c>
       <c r="AH33" s="1">
-        <v>0.0059061962244863911</v>
+        <v>0.0059061962244864553</v>
       </c>
       <c r="AI33" s="1">
-        <v>0.0023477485281411751</v>
+        <v>0.0023477485281412328</v>
       </c>
       <c r="AJ33" s="1">
-        <v>0.0023678818852201204</v>
+        <v>0.0023678818852201559</v>
       </c>
       <c r="AK33" s="1">
-        <v>-0.00010208833617727578</v>
+        <v>-0.00010208833617728416</v>
       </c>
       <c r="AL33" s="1">
-        <v>-0.00026376012085281564</v>
+        <v>-0.00026376012088027848</v>
       </c>
     </row>
     <row r="34">
@@ -4412,115 +4412,115 @@
         <v>61</v>
       </c>
       <c r="B34" s="1">
-        <v>-0.032410225954086221</v>
+        <v>-0.032410225954086901</v>
       </c>
       <c r="C34" s="1">
-        <v>1.9318954850772527e-05</v>
+        <v>1.9318954850809688e-05</v>
       </c>
       <c r="D34" s="1">
-        <v>1.7512065808804116e-05</v>
+        <v>1.7512065808717326e-05</v>
       </c>
       <c r="E34" s="1">
-        <v>-2.1051976594319231e-07</v>
+        <v>-2.1051976594240415e-07</v>
       </c>
       <c r="F34" s="1">
-        <v>8.4793944348940734e-05</v>
+        <v>8.4793944350403105e-05</v>
       </c>
       <c r="G34" s="1">
-        <v>-0.00020969143890345841</v>
+        <v>-0.00020969143890286947</v>
       </c>
       <c r="H34" s="1">
-        <v>-9.8553689358878279e-05</v>
+        <v>-9.8553689358255731e-05</v>
       </c>
       <c r="I34" s="1">
-        <v>-5.3451448485928232e-05</v>
+        <v>-5.3451448485485661e-05</v>
       </c>
       <c r="J34" s="1">
-        <v>-5.690446433278891e-05</v>
+        <v>-5.6904464332823001e-05</v>
       </c>
       <c r="K34" s="1">
-        <v>1.3443650714663468e-05</v>
+        <v>1.3443650714617443e-05</v>
       </c>
       <c r="L34" s="1">
-        <v>-1.9093120517715411e-05</v>
+        <v>-1.9093120517670003e-05</v>
       </c>
       <c r="M34" s="1">
-        <v>-4.2924420730634032e-06</v>
+        <v>-4.2924420730354342e-06</v>
       </c>
       <c r="N34" s="1">
-        <v>0.00012258185353706055</v>
+        <v>0.0001225818535376122</v>
       </c>
       <c r="O34" s="1">
-        <v>9.9918855874772585e-07</v>
+        <v>9.9918855878092954e-07</v>
       </c>
       <c r="P34" s="1">
-        <v>0.0010295202297375683</v>
+        <v>0.0010295202297798678</v>
       </c>
       <c r="Q34" s="1">
-        <v>0.00088694936906263955</v>
+        <v>0.00088694936910682642</v>
       </c>
       <c r="R34" s="1">
-        <v>0.0012773758690651782</v>
+        <v>0.0012773758691095871</v>
       </c>
       <c r="S34" s="1">
-        <v>0.0012383312103790844</v>
+        <v>0.0012383312104244926</v>
       </c>
       <c r="T34" s="1">
-        <v>-5.6118017251381388e-05</v>
+        <v>-5.611801725143549e-05</v>
       </c>
       <c r="U34" s="1">
-        <v>-3.954522552119589e-05</v>
+        <v>-3.9545225521284361e-05</v>
       </c>
       <c r="V34" s="1">
-        <v>-0.00013496827790804257</v>
+        <v>-0.0001349682779086701</v>
       </c>
       <c r="W34" s="1">
-        <v>2.9601765706782895e-05</v>
+        <v>2.9601765706200461e-05</v>
       </c>
       <c r="X34" s="1">
-        <v>0.0011656447634584843</v>
+        <v>0.0011656447635169931</v>
       </c>
       <c r="Y34" s="1">
-        <v>0.0011997182148691943</v>
+        <v>0.0011997182149282581</v>
       </c>
       <c r="Z34" s="1">
-        <v>0.0013326437124387969</v>
+        <v>0.0013326437124978607</v>
       </c>
       <c r="AA34" s="1">
-        <v>-0.00010432961155413308</v>
+        <v>-0.00010432961155393793</v>
       </c>
       <c r="AB34" s="1">
-        <v>0.00012302914600908588</v>
+        <v>0.00012302914600906094</v>
       </c>
       <c r="AC34" s="1">
-        <v>0.00027991961301195934</v>
+        <v>0.00027991961301197972</v>
       </c>
       <c r="AD34" s="1">
-        <v>-2.1950547072984751e-05</v>
+        <v>-2.195054707288327e-05</v>
       </c>
       <c r="AE34" s="1">
-        <v>-0.00020751997725205226</v>
+        <v>-0.00020751997725231204</v>
       </c>
       <c r="AF34" s="1">
-        <v>6.4106848321297295e-05</v>
+        <v>6.4106848321708858e-05</v>
       </c>
       <c r="AG34" s="1">
-        <v>0.0023504390555683027</v>
+        <v>0.0023504390555683678</v>
       </c>
       <c r="AH34" s="1">
-        <v>0.0023477485281411751</v>
+        <v>0.0023477485281412328</v>
       </c>
       <c r="AI34" s="1">
-        <v>0.0043853127266970642</v>
+        <v>0.0043853127266971492</v>
       </c>
       <c r="AJ34" s="1">
-        <v>0.0023581048797810819</v>
+        <v>0.0023581048797811084</v>
       </c>
       <c r="AK34" s="1">
-        <v>-9.0465745287152653e-05</v>
+        <v>-9.0465745287162438e-05</v>
       </c>
       <c r="AL34" s="1">
-        <v>-0.0022294365284480041</v>
+        <v>-0.0022294365285050787</v>
       </c>
     </row>
     <row r="35">
@@ -4528,115 +4528,115 @@
         <v>62</v>
       </c>
       <c r="B35" s="1">
-        <v>-0.0087635410619564934</v>
+        <v>-0.0087635410619569948</v>
       </c>
       <c r="C35" s="1">
-        <v>2.5770834566505603e-05</v>
+        <v>2.5770834566524956e-05</v>
       </c>
       <c r="D35" s="1">
-        <v>2.3881238001463383e-05</v>
+        <v>2.3881238001379845e-05</v>
       </c>
       <c r="E35" s="1">
-        <v>-2.8661483694152515e-07</v>
+        <v>-2.8661483694076981e-07</v>
       </c>
       <c r="F35" s="1">
-        <v>7.8321520189435917e-05</v>
+        <v>7.8321520190037866e-05</v>
       </c>
       <c r="G35" s="1">
-        <v>-5.8569217146796056e-05</v>
+        <v>-5.8569217146417236e-05</v>
       </c>
       <c r="H35" s="1">
-        <v>-1.340793102954296e-05</v>
+        <v>-1.3407931029119254e-05</v>
       </c>
       <c r="I35" s="1">
-        <v>-7.5919483127538494e-05</v>
+        <v>-7.5919483127230526e-05</v>
       </c>
       <c r="J35" s="1">
-        <v>-2.2005824852954966e-05</v>
+        <v>-2.2005824852979811e-05</v>
       </c>
       <c r="K35" s="1">
-        <v>2.1756948892418958e-05</v>
+        <v>2.1756948892352821e-05</v>
       </c>
       <c r="L35" s="1">
-        <v>-1.5979458165976204e-06</v>
+        <v>-1.5979458165457956e-06</v>
       </c>
       <c r="M35" s="1">
-        <v>2.2279585569666447e-05</v>
+        <v>2.2279585569689317e-05</v>
       </c>
       <c r="N35" s="1">
-        <v>0.00015561236279167372</v>
+        <v>0.00015561236279166678</v>
       </c>
       <c r="O35" s="1">
-        <v>3.7372028265341816e-07</v>
+        <v>3.7372028266762121e-07</v>
       </c>
       <c r="P35" s="1">
-        <v>0.00055051196329386487</v>
+        <v>0.00055051196329469754</v>
       </c>
       <c r="Q35" s="1">
-        <v>2.3207444428408053e-06</v>
+        <v>2.3207444451722736e-06</v>
       </c>
       <c r="R35" s="1">
-        <v>0.00048494177400243421</v>
+        <v>0.00048494177400509875</v>
       </c>
       <c r="S35" s="1">
-        <v>0.00032803400681530315</v>
+        <v>0.00032803400681852279</v>
       </c>
       <c r="T35" s="1">
-        <v>2.4411847720227139e-06</v>
+        <v>2.4411847720130103e-06</v>
       </c>
       <c r="U35" s="1">
-        <v>-2.6652271197614551e-05</v>
+        <v>-2.6652271197591566e-05</v>
       </c>
       <c r="V35" s="1">
-        <v>-7.408986158921908e-05</v>
+        <v>-7.4089861589561688e-05</v>
       </c>
       <c r="W35" s="1">
-        <v>-8.5639203866032547e-05</v>
+        <v>-8.5639203866329835e-05</v>
       </c>
       <c r="X35" s="1">
-        <v>0.00037738879194731956</v>
+        <v>0.00037738879195553521</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.0004472020362410456</v>
+        <v>0.00044720203624998289</v>
       </c>
       <c r="Z35" s="1">
-        <v>0.00049649066349660709</v>
+        <v>0.00049649066350537785</v>
       </c>
       <c r="AA35" s="1">
-        <v>0.00010121899882894114</v>
+        <v>0.00010121899882867963</v>
       </c>
       <c r="AB35" s="1">
-        <v>0.00030856015825745167</v>
+        <v>0.00030856015825733068</v>
       </c>
       <c r="AC35" s="1">
-        <v>0.00039095289926541687</v>
+        <v>0.00039095289926532526</v>
       </c>
       <c r="AD35" s="1">
-        <v>1.5381095965998461e-05</v>
+        <v>1.5381095965978728e-05</v>
       </c>
       <c r="AE35" s="1">
-        <v>-8.6036790780880069e-05</v>
+        <v>-8.6036790781136266e-05</v>
       </c>
       <c r="AF35" s="1">
-        <v>-0.0002827201068666828</v>
+        <v>-0.00028272010686658001</v>
       </c>
       <c r="AG35" s="1">
-        <v>0.002354234421637682</v>
+        <v>0.0023542344216376915</v>
       </c>
       <c r="AH35" s="1">
-        <v>0.0023678818852201204</v>
+        <v>0.0023678818852201559</v>
       </c>
       <c r="AI35" s="1">
-        <v>0.0023581048797810819</v>
+        <v>0.0023581048797811084</v>
       </c>
       <c r="AJ35" s="1">
-        <v>0.0033575340326914547</v>
+        <v>0.0033575340326914564</v>
       </c>
       <c r="AK35" s="1">
-        <v>-9.2886693069488659e-05</v>
+        <v>-9.2886693069505816e-05</v>
       </c>
       <c r="AL35" s="1">
-        <v>-0.0018279633341968262</v>
+        <v>-0.0018279633342038917</v>
       </c>
     </row>
     <row r="36">
@@ -4644,115 +4644,115 @@
         <v>63</v>
       </c>
       <c r="B36" s="1">
-        <v>-0.032345553487005692</v>
+        <v>-0.032345553487005199</v>
       </c>
       <c r="C36" s="1">
-        <v>-3.994819555932575e-06</v>
+        <v>-3.9948195559330154e-06</v>
       </c>
       <c r="D36" s="1">
-        <v>-2.3471768138907142e-06</v>
+        <v>-2.3471768138588251e-06</v>
       </c>
       <c r="E36" s="1">
-        <v>1.9677432665468871e-08</v>
+        <v>1.9677432665158857e-08</v>
       </c>
       <c r="F36" s="1">
-        <v>2.6047144065958778e-05</v>
+        <v>2.604714406604443e-05</v>
       </c>
       <c r="G36" s="1">
-        <v>2.6997927960038088e-05</v>
+        <v>2.6997927960021554e-05</v>
       </c>
       <c r="H36" s="1">
-        <v>8.5736453995748215e-06</v>
+        <v>8.5736453995497223e-06</v>
       </c>
       <c r="I36" s="1">
-        <v>-3.7075244263497958e-06</v>
+        <v>-3.7075244263599602e-06</v>
       </c>
       <c r="J36" s="1">
-        <v>3.841588999009404e-06</v>
+        <v>3.841588999006552e-06</v>
       </c>
       <c r="K36" s="1">
-        <v>-4.1396484164253931e-07</v>
+        <v>-4.1396484164695066e-07</v>
       </c>
       <c r="L36" s="1">
-        <v>-1.0857226890041353e-06</v>
+        <v>-1.0857226890158006e-06</v>
       </c>
       <c r="M36" s="1">
-        <v>-1.6762621207695698e-06</v>
+        <v>-1.6762621207704787e-06</v>
       </c>
       <c r="N36" s="1">
-        <v>2.5852452685503268e-05</v>
+        <v>2.585245268558415e-05</v>
       </c>
       <c r="O36" s="1">
-        <v>-2.4476669109535574e-07</v>
+        <v>-2.4476669109324832e-07</v>
       </c>
       <c r="P36" s="1">
-        <v>-0.00011072448411314495</v>
+        <v>-0.00011072448410665015</v>
       </c>
       <c r="Q36" s="1">
-        <v>-5.913572926505295e-05</v>
+        <v>-5.9135729258585901e-05</v>
       </c>
       <c r="R36" s="1">
-        <v>-3.0735105178106292e-05</v>
+        <v>-3.0735105171569854e-05</v>
       </c>
       <c r="S36" s="1">
-        <v>-8.1882413260209175e-06</v>
+        <v>-8.1882413195677461e-06</v>
       </c>
       <c r="T36" s="1">
-        <v>-3.4382167042515518e-06</v>
+        <v>-3.438216704255726e-06</v>
       </c>
       <c r="U36" s="1">
-        <v>-4.5443419750162734e-06</v>
+        <v>-4.5443419750242423e-06</v>
       </c>
       <c r="V36" s="1">
-        <v>8.9084164345785153e-06</v>
+        <v>8.9084164345541207e-06</v>
       </c>
       <c r="W36" s="1">
-        <v>3.3498287454496374e-06</v>
+        <v>3.3498287454164066e-06</v>
       </c>
       <c r="X36" s="1">
-        <v>-0.00010738827251124961</v>
+        <v>-0.00010738827250383887</v>
       </c>
       <c r="Y36" s="1">
-        <v>-0.00011844307143032973</v>
+        <v>-0.0001184430714229745</v>
       </c>
       <c r="Z36" s="1">
-        <v>-0.00014733381017947855</v>
+        <v>-0.00014733381017209557</v>
       </c>
       <c r="AA36" s="1">
-        <v>-3.4520621058288905e-05</v>
+        <v>-3.4520621058144272e-05</v>
       </c>
       <c r="AB36" s="1">
-        <v>-2.0108878353096546e-05</v>
+        <v>-2.0108878353166531e-05</v>
       </c>
       <c r="AC36" s="1">
-        <v>-3.5030027346993561e-05</v>
+        <v>-3.5030027346988249e-05</v>
       </c>
       <c r="AD36" s="1">
-        <v>8.8045301172197128e-06</v>
+        <v>8.8045301172522388e-06</v>
       </c>
       <c r="AE36" s="1">
-        <v>5.0424984362906647e-06</v>
+        <v>5.0424984363391014e-06</v>
       </c>
       <c r="AF36" s="1">
-        <v>3.6855282286160185e-05</v>
+        <v>3.6855282286234561e-05</v>
       </c>
       <c r="AG36" s="1">
-        <v>-8.5569978473513714e-05</v>
+        <v>-8.5569978473530898e-05</v>
       </c>
       <c r="AH36" s="1">
-        <v>-0.00010208833617727578</v>
+        <v>-0.00010208833617728416</v>
       </c>
       <c r="AI36" s="1">
-        <v>-9.0465745287152653e-05</v>
+        <v>-9.0465745287162438e-05</v>
       </c>
       <c r="AJ36" s="1">
-        <v>-9.2886693069488659e-05</v>
+        <v>-9.2886693069505816e-05</v>
       </c>
       <c r="AK36" s="1">
-        <v>3.9107079700350679e-05</v>
+        <v>3.9107079700345705e-05</v>
       </c>
       <c r="AL36" s="1">
-        <v>-0.00036329550898849173</v>
+        <v>-0.00036329550899599024</v>
       </c>
     </row>
     <row r="37">
@@ -4760,115 +4760,115 @@
         <v>64</v>
       </c>
       <c r="B37" s="1">
-        <v>0.18562505920785816</v>
+        <v>0.18562505920800637</v>
       </c>
       <c r="C37" s="1">
-        <v>-0.00084948509481593416</v>
+        <v>-0.00084948509485140329</v>
       </c>
       <c r="D37" s="1">
-        <v>-0.00097243503089864184</v>
+        <v>-0.00097243503083369661</v>
       </c>
       <c r="E37" s="1">
-        <v>9.1336556548105908e-06</v>
+        <v>9.1336556542037442e-06</v>
       </c>
       <c r="F37" s="1">
-        <v>-0.021192789809307333</v>
+        <v>-0.021192789810487105</v>
       </c>
       <c r="G37" s="1">
-        <v>-0.0034340330730213246</v>
+        <v>-0.0034340330734633265</v>
       </c>
       <c r="H37" s="1">
-        <v>-0.0024502434910213941</v>
+        <v>-0.0024502434914878378</v>
       </c>
       <c r="I37" s="1">
-        <v>-0.0014014341750661827</v>
+        <v>-0.0014014341753842178</v>
       </c>
       <c r="J37" s="1">
-        <v>0.00034126079343411921</v>
+        <v>0.00034126079345844106</v>
       </c>
       <c r="K37" s="1">
-        <v>-0.00087113916615671398</v>
+        <v>-0.00087113916615868452</v>
       </c>
       <c r="L37" s="1">
-        <v>0.0003177250207875166</v>
+        <v>0.00031772502077733654</v>
       </c>
       <c r="M37" s="1">
-        <v>-0.00014310115244555363</v>
+        <v>-0.00014310115246613799</v>
       </c>
       <c r="N37" s="1">
-        <v>-0.011519716844985336</v>
+        <v>-0.011519716845475822</v>
       </c>
       <c r="O37" s="1">
-        <v>-0.00055402555501665436</v>
+        <v>-0.00055402555504303734</v>
       </c>
       <c r="P37" s="1">
-        <v>-0.7103001611195201</v>
+        <v>-0.71030016115773364</v>
       </c>
       <c r="Q37" s="1">
-        <v>-0.74643200119387354</v>
+        <v>-0.74643200123301234</v>
       </c>
       <c r="R37" s="1">
-        <v>-0.7579378004989481</v>
+        <v>-0.75793780053877657</v>
       </c>
       <c r="S37" s="1">
-        <v>-0.76088718229212859</v>
+        <v>-0.76088718233232899</v>
       </c>
       <c r="T37" s="1">
-        <v>0.0018538329167746956</v>
+        <v>0.0018538329168189501</v>
       </c>
       <c r="U37" s="1">
-        <v>0.0032987591985131665</v>
+        <v>0.0032987591986270454</v>
       </c>
       <c r="V37" s="1">
-        <v>0.010562799687303313</v>
+        <v>0.010562799687762508</v>
       </c>
       <c r="W37" s="1">
-        <v>0.01055815120471231</v>
+        <v>0.010558151205160115</v>
       </c>
       <c r="X37" s="1">
-        <v>-0.98716862852262643</v>
+        <v>-0.9871686285735366</v>
       </c>
       <c r="Y37" s="1">
-        <v>-0.98731696874896324</v>
+        <v>-0.98731696880008479</v>
       </c>
       <c r="Z37" s="1">
-        <v>-0.98801862919393391</v>
+        <v>-0.98801862924506056</v>
       </c>
       <c r="AA37" s="1">
-        <v>-0.018580896456864827</v>
+        <v>-0.018580896457169357</v>
       </c>
       <c r="AB37" s="1">
-        <v>-0.0039542442136659235</v>
+        <v>-0.0039542442137415973</v>
       </c>
       <c r="AC37" s="1">
-        <v>-0.0058035607550259828</v>
+        <v>-0.0058035607550810282</v>
       </c>
       <c r="AD37" s="1">
-        <v>-0.0049030518989783556</v>
+        <v>-0.0049030518990928161</v>
       </c>
       <c r="AE37" s="1">
-        <v>-0.0021953742565006011</v>
+        <v>-0.0021953742563166571</v>
       </c>
       <c r="AF37" s="1">
-        <v>-0.012742749750243199</v>
+        <v>-0.012742749750605511</v>
       </c>
       <c r="AG37" s="1">
-        <v>-0.0032903127539880167</v>
+        <v>-0.0032903127540297224</v>
       </c>
       <c r="AH37" s="1">
-        <v>-0.00026376012085281564</v>
+        <v>-0.00026376012088027848</v>
       </c>
       <c r="AI37" s="1">
-        <v>-0.0022294365284480041</v>
+        <v>-0.0022294365285050787</v>
       </c>
       <c r="AJ37" s="1">
-        <v>-0.0018279633341968262</v>
+        <v>-0.0018279633342038917</v>
       </c>
       <c r="AK37" s="1">
-        <v>-0.00036329550898849173</v>
+        <v>-0.00036329550899599024</v>
       </c>
       <c r="AL37" s="1">
-        <v>1.0278093986727803</v>
+        <v>1.0278093987229118</v>
       </c>
     </row>
   </sheetData>
@@ -4986,100 +4986,100 @@
         <v>29</v>
       </c>
       <c r="B2" s="1">
-        <v>-0.025240222299580787</v>
+        <v>-0.025240222299579521</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0010650484860845377</v>
+        <v>0.0010650484860845364</v>
       </c>
       <c r="D2" s="1">
-        <v>1.6339053799013771e-05</v>
+        <v>1.633905379901373e-05</v>
       </c>
       <c r="E2" s="1">
-        <v>-1.8275689700715978e-07</v>
+        <v>-1.8275689700713021e-07</v>
       </c>
       <c r="F2" s="1">
-        <v>0.00051462991022414146</v>
+        <v>0.00051462991022417789</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00059217330766195416</v>
+        <v>0.00059217330766197888</v>
       </c>
       <c r="H2" s="1">
-        <v>0.0004801353360134468</v>
+        <v>0.00048013533601350957</v>
       </c>
       <c r="I2" s="1">
-        <v>0.00044515300783601786</v>
+        <v>0.00044515300783605309</v>
       </c>
       <c r="J2" s="1">
-        <v>3.2869397362727805e-05</v>
+        <v>3.2869397362727209e-05</v>
       </c>
       <c r="K2" s="1">
-        <v>-4.170690682898532e-05</v>
+        <v>-4.1706906828986899e-05</v>
       </c>
       <c r="L2" s="1">
-        <v>-1.5834087445028352e-05</v>
+        <v>-1.5834087445026112e-05</v>
       </c>
       <c r="M2" s="1">
-        <v>-1.7647373021457746e-05</v>
+        <v>-1.7647373021460213e-05</v>
       </c>
       <c r="N2" s="1">
-        <v>-0.0010487097153188856</v>
+        <v>-0.0010487097153188841</v>
       </c>
       <c r="O2" s="1">
-        <v>-4.1581387441835214e-05</v>
+        <v>-4.1581387441793472e-05</v>
       </c>
       <c r="P2" s="1">
-        <v>3.3393533150383268e-05</v>
+        <v>3.3393533150399592e-05</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.1208301938427276e-06</v>
+        <v>1.120830193841169e-06</v>
       </c>
       <c r="R2" s="1">
-        <v>3.9492816686277437e-05</v>
+        <v>3.9492816686296139e-05</v>
       </c>
       <c r="S2" s="1">
-        <v>-0.00037926386093542551</v>
+        <v>-0.00037926386093509239</v>
       </c>
       <c r="T2" s="1">
-        <v>-0.00033569246695577489</v>
+        <v>-0.0003356924669555232</v>
       </c>
       <c r="U2" s="1">
-        <v>-0.00015267774938342125</v>
+        <v>-0.00015267774938319633</v>
       </c>
       <c r="V2" s="1">
-        <v>-7.8433900262784784e-05</v>
+        <v>-7.8433900262733406e-05</v>
       </c>
       <c r="W2" s="1">
-        <v>-4.4622951285627718e-05</v>
+        <v>-4.462295128562704e-05</v>
       </c>
       <c r="X2" s="1">
-        <v>0.00011364653780756125</v>
+        <v>0.00011364653780754092</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.00012476702225810968</v>
+        <v>0.00012476702225811261</v>
       </c>
       <c r="Z2" s="1">
-        <v>0.00024688383600290296</v>
+        <v>0.00024688383600290366</v>
       </c>
       <c r="AA2" s="1">
-        <v>0.00059012301569078961</v>
+        <v>0.00059012301569079568</v>
       </c>
       <c r="AB2" s="1">
-        <v>-5.2426104394325814e-05</v>
+        <v>-5.2426104394323809e-05</v>
       </c>
       <c r="AC2" s="1">
-        <v>-4.9085181256343033e-05</v>
+        <v>-4.9085181256342978e-05</v>
       </c>
       <c r="AD2" s="1">
-        <v>7.2811379269905498e-05</v>
+        <v>7.2811379269905918e-05</v>
       </c>
       <c r="AE2" s="1">
-        <v>-8.0574579766557602e-05</v>
+        <v>-8.057457976655706e-05</v>
       </c>
       <c r="AF2" s="1">
-        <v>9.89090529956304e-06</v>
+        <v>9.8909052995635076e-06</v>
       </c>
       <c r="AG2" s="1">
-        <v>-0.0010837478335164194</v>
+        <v>-0.0010837478335165916</v>
       </c>
     </row>
     <row r="3">
@@ -5087,100 +5087,100 @@
         <v>30</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.0075908600924569584</v>
+        <v>-0.0075908600924573617</v>
       </c>
       <c r="C3" s="1">
-        <v>1.6339053799013771e-05</v>
+        <v>1.633905379901373e-05</v>
       </c>
       <c r="D3" s="1">
-        <v>4.6194688529338218e-05</v>
+        <v>4.6194688529333359e-05</v>
       </c>
       <c r="E3" s="1">
-        <v>-4.8138575042672359e-07</v>
+        <v>-4.8138575042660628e-07</v>
       </c>
       <c r="F3" s="1">
-        <v>0.00017982489712795643</v>
+        <v>0.0001798248971279844</v>
       </c>
       <c r="G3" s="1">
-        <v>0.00016569792537115863</v>
+        <v>0.00016569792537122065</v>
       </c>
       <c r="H3" s="1">
-        <v>0.0001751391426013495</v>
+        <v>0.00017513914260144795</v>
       </c>
       <c r="I3" s="1">
-        <v>0.00021282494787349163</v>
+        <v>0.00021282494787352546</v>
       </c>
       <c r="J3" s="1">
-        <v>-2.221987789413312e-06</v>
+        <v>-2.2219877894042047e-06</v>
       </c>
       <c r="K3" s="1">
-        <v>5.4187203834057087e-06</v>
+        <v>5.4187203834020521e-06</v>
       </c>
       <c r="L3" s="1">
-        <v>-1.0164290925030153e-05</v>
+        <v>-1.0164290925023854e-05</v>
       </c>
       <c r="M3" s="1">
-        <v>-8.0905793299225069e-06</v>
+        <v>-8.0905793299309095e-06</v>
       </c>
       <c r="N3" s="1">
-        <v>-2.4869131880844795e-05</v>
+        <v>-2.4869131880823328e-05</v>
       </c>
       <c r="O3" s="1">
-        <v>6.4843019309966578e-06</v>
+        <v>6.4843019310249555e-06</v>
       </c>
       <c r="P3" s="1">
-        <v>-2.9850549362174939e-06</v>
+        <v>-2.9850549361984391e-06</v>
       </c>
       <c r="Q3" s="1">
-        <v>8.2391666210945396e-06</v>
+        <v>8.2391666210911786e-06</v>
       </c>
       <c r="R3" s="1">
-        <v>1.0251132452634222e-05</v>
+        <v>1.0251132452651678e-05</v>
       </c>
       <c r="S3" s="1">
-        <v>3.9347954577622583e-05</v>
+        <v>3.9347954578175743e-05</v>
       </c>
       <c r="T3" s="1">
-        <v>2.3081702616830051e-05</v>
+        <v>2.3081702616858891e-05</v>
       </c>
       <c r="U3" s="1">
-        <v>4.8338837890395505e-05</v>
+        <v>4.8338837890562472e-05</v>
       </c>
       <c r="V3" s="1">
-        <v>0.00013305191093106471</v>
+        <v>0.00013305191093110965</v>
       </c>
       <c r="W3" s="1">
-        <v>2.0399969914487043e-05</v>
+        <v>2.0399969914492572e-05</v>
       </c>
       <c r="X3" s="1">
-        <v>0.00017097207127786355</v>
+        <v>0.00017097207127780292</v>
       </c>
       <c r="Y3" s="1">
-        <v>1.1153319499612009e-05</v>
+        <v>1.1153319499621007e-05</v>
       </c>
       <c r="Z3" s="1">
-        <v>0.00010018497687356532</v>
+        <v>0.0001001849768735624</v>
       </c>
       <c r="AA3" s="1">
-        <v>1.7828568744848315e-05</v>
+        <v>1.7828568744855037e-05</v>
       </c>
       <c r="AB3" s="1">
-        <v>-3.1417369092205422e-05</v>
+        <v>-3.141736909219317e-05</v>
       </c>
       <c r="AC3" s="1">
-        <v>-7.0612681292189393e-05</v>
+        <v>-7.0612681292175894e-05</v>
       </c>
       <c r="AD3" s="1">
-        <v>-1.5371687661805888e-05</v>
+        <v>-1.5371687661801822e-05</v>
       </c>
       <c r="AE3" s="1">
-        <v>-3.1569579549181603e-05</v>
+        <v>-3.1569579549175423e-05</v>
       </c>
       <c r="AF3" s="1">
-        <v>-8.9254441796526943e-07</v>
+        <v>-8.925444179634534e-07</v>
       </c>
       <c r="AG3" s="1">
-        <v>-0.0011764663930049425</v>
+        <v>-0.0011764663930050575</v>
       </c>
     </row>
     <row r="4">
@@ -5188,100 +5188,100 @@
         <v>31</v>
       </c>
       <c r="B4" s="1">
-        <v>7.1253495956572838e-05</v>
+        <v>7.1253495956577893e-05</v>
       </c>
       <c r="C4" s="1">
-        <v>-1.8275689700715978e-07</v>
+        <v>-1.8275689700713021e-07</v>
       </c>
       <c r="D4" s="1">
-        <v>-4.8138575042672359e-07</v>
+        <v>-4.8138575042660628e-07</v>
       </c>
       <c r="E4" s="1">
-        <v>5.2493160584280359e-09</v>
+        <v>5.2493160584267472e-09</v>
       </c>
       <c r="F4" s="1">
-        <v>-2.0791176929912898e-06</v>
+        <v>-2.0791176929914541e-06</v>
       </c>
       <c r="G4" s="1">
-        <v>-1.8053921857879368e-06</v>
+        <v>-1.8053921857884585e-06</v>
       </c>
       <c r="H4" s="1">
-        <v>-1.7888626944414222e-06</v>
+        <v>-1.7888626944423116e-06</v>
       </c>
       <c r="I4" s="1">
-        <v>-2.1070382446626522e-06</v>
+        <v>-2.1070382446628996e-06</v>
       </c>
       <c r="J4" s="1">
-        <v>2.7222561358544733e-08</v>
+        <v>2.7222561358457912e-08</v>
       </c>
       <c r="K4" s="1">
-        <v>-2.987382838636382e-08</v>
+        <v>-2.9873828386326412e-08</v>
       </c>
       <c r="L4" s="1">
-        <v>8.3945306509481477e-08</v>
+        <v>8.3945306509415435e-08</v>
       </c>
       <c r="M4" s="1">
-        <v>7.8449751780093324e-08</v>
+        <v>7.8449751780175486e-08</v>
       </c>
       <c r="N4" s="1">
-        <v>2.5099687305187632e-07</v>
+        <v>2.5099687305165228e-07</v>
       </c>
       <c r="O4" s="1">
-        <v>-4.3636033771014753e-08</v>
+        <v>-4.3636033771295121e-08</v>
       </c>
       <c r="P4" s="1">
-        <v>1.617104642311154e-08</v>
+        <v>1.6171046422917781e-08</v>
       </c>
       <c r="Q4" s="1">
-        <v>-7.1675315913851051e-08</v>
+        <v>-7.1675315913814311e-08</v>
       </c>
       <c r="R4" s="1">
-        <v>-1.327694325121753e-07</v>
+        <v>-1.3276943251235148e-07</v>
       </c>
       <c r="S4" s="1">
-        <v>-5.3557068817196715e-07</v>
+        <v>-5.3557068817756773e-07</v>
       </c>
       <c r="T4" s="1">
-        <v>-3.0657499079046117e-07</v>
+        <v>-3.0657499079080507e-07</v>
       </c>
       <c r="U4" s="1">
-        <v>-5.8882490348818363e-07</v>
+        <v>-5.8882490348993529e-07</v>
       </c>
       <c r="V4" s="1">
-        <v>-1.0832780701910347e-06</v>
+        <v>-1.0832780701914478e-06</v>
       </c>
       <c r="W4" s="1">
-        <v>-1.4705250733446665e-07</v>
+        <v>-1.4705250733452425e-07</v>
       </c>
       <c r="X4" s="1">
-        <v>-2.2301552036290766e-06</v>
+        <v>-2.2301552036284142e-06</v>
       </c>
       <c r="Y4" s="1">
-        <v>1.854832317286762e-07</v>
+        <v>1.8548323172858048e-07</v>
       </c>
       <c r="Z4" s="1">
-        <v>-8.7686144722127035e-07</v>
+        <v>-8.7686144722122758e-07</v>
       </c>
       <c r="AA4" s="1">
-        <v>7.3412141061194641e-08</v>
+        <v>7.3412141061128572e-08</v>
       </c>
       <c r="AB4" s="1">
-        <v>2.8972752488738926e-07</v>
+        <v>2.8972752488727152e-07</v>
       </c>
       <c r="AC4" s="1">
-        <v>6.1016131946174865e-07</v>
+        <v>6.1016131946160762e-07</v>
       </c>
       <c r="AD4" s="1">
-        <v>6.7560590059206306e-08</v>
+        <v>6.7560590059174966e-08</v>
       </c>
       <c r="AE4" s="1">
-        <v>3.1820888235853339e-07</v>
+        <v>3.1820888235846901e-07</v>
       </c>
       <c r="AF4" s="1">
-        <v>5.6514015506191151e-09</v>
+        <v>5.6514015506019098e-09</v>
       </c>
       <c r="AG4" s="1">
-        <v>1.173248343135216e-05</v>
+        <v>1.1732483431352887e-05</v>
       </c>
     </row>
     <row r="5">
@@ -5289,100 +5289,100 @@
         <v>33</v>
       </c>
       <c r="B5" s="1">
-        <v>0.37643857076040921</v>
+        <v>0.37643857076042864</v>
       </c>
       <c r="C5" s="1">
-        <v>0.00051462991022414146</v>
+        <v>0.00051462991022417789</v>
       </c>
       <c r="D5" s="1">
-        <v>0.00017982489712795643</v>
+        <v>0.0001798248971279844</v>
       </c>
       <c r="E5" s="1">
-        <v>-2.0791176929912898e-06</v>
+        <v>-2.0791176929914541e-06</v>
       </c>
       <c r="F5" s="1">
-        <v>0.031846589658508132</v>
+        <v>0.031846589658514224</v>
       </c>
       <c r="G5" s="1">
-        <v>0.030153444820767414</v>
+        <v>0.030153444820773249</v>
       </c>
       <c r="H5" s="1">
-        <v>0.030041835636406382</v>
+        <v>0.030041835636412745</v>
       </c>
       <c r="I5" s="1">
-        <v>0.030120242133651054</v>
+        <v>0.030120242133657341</v>
       </c>
       <c r="J5" s="1">
-        <v>-5.3237864431543089e-05</v>
+        <v>-5.3237864431543956e-05</v>
       </c>
       <c r="K5" s="1">
-        <v>1.4617450913782196e-05</v>
+        <v>1.4617450913776647e-05</v>
       </c>
       <c r="L5" s="1">
-        <v>-8.6919554873058226e-05</v>
+        <v>-8.691955487307579e-05</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.00018742302000795703</v>
+        <v>-0.00018742302000795876</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.00047713329546585038</v>
+        <v>-0.00047713329546572114</v>
       </c>
       <c r="O5" s="1">
-        <v>4.355909649232919e-05</v>
+        <v>4.3559096494347541e-05</v>
       </c>
       <c r="P5" s="1">
-        <v>-2.5897101901336313e-05</v>
+        <v>-2.5897101900995223e-05</v>
       </c>
       <c r="Q5" s="1">
-        <v>2.9223457779913465e-05</v>
+        <v>2.9223457779938185e-05</v>
       </c>
       <c r="R5" s="1">
-        <v>0.00020374946334861255</v>
+        <v>0.00020374946334810774</v>
       </c>
       <c r="S5" s="1">
-        <v>-3.7378172552256575e-05</v>
+        <v>-3.7378172544236948e-05</v>
       </c>
       <c r="T5" s="1">
-        <v>0.00058181669874420895</v>
+        <v>0.00058181669874880944</v>
       </c>
       <c r="U5" s="1">
-        <v>0.00083011177811210743</v>
+        <v>0.0008301117781180159</v>
       </c>
       <c r="V5" s="1">
-        <v>0.00059543285392457245</v>
+        <v>0.00059543285392597237</v>
       </c>
       <c r="W5" s="1">
-        <v>0.00037935257794391138</v>
+        <v>0.00037935257794403715</v>
       </c>
       <c r="X5" s="1">
-        <v>0.0010848267231048044</v>
+        <v>0.0010848267231050269</v>
       </c>
       <c r="Y5" s="1">
-        <v>-0.00054617911183649833</v>
+        <v>-0.00054617911183637777</v>
       </c>
       <c r="Z5" s="1">
-        <v>-0.00050637629835039604</v>
+        <v>-0.00050637629835017465</v>
       </c>
       <c r="AA5" s="1">
-        <v>-2.03152316665383e-05</v>
+        <v>-2.0315231666286765e-05</v>
       </c>
       <c r="AB5" s="1">
-        <v>-4.4001561505363149e-05</v>
+        <v>-4.4001561505269474e-05</v>
       </c>
       <c r="AC5" s="1">
-        <v>5.3047019707930243e-05</v>
+        <v>5.3047019707982285e-05</v>
       </c>
       <c r="AD5" s="1">
-        <v>8.6293782535488105e-05</v>
+        <v>8.629378253557831e-05</v>
       </c>
       <c r="AE5" s="1">
-        <v>-0.00058485491823510524</v>
+        <v>-0.000584854918235048</v>
       </c>
       <c r="AF5" s="1">
-        <v>1.0700395052566278e-05</v>
+        <v>1.0700395052582975e-05</v>
       </c>
       <c r="AG5" s="1">
-        <v>-0.033051009480211661</v>
+        <v>-0.033051009480229057</v>
       </c>
     </row>
     <row r="6">
@@ -5390,100 +5390,100 @@
         <v>34</v>
       </c>
       <c r="B6" s="1">
-        <v>0.28621202230464804</v>
+        <v>0.2862120223046673</v>
       </c>
       <c r="C6" s="1">
-        <v>0.00059217330766195416</v>
+        <v>0.00059217330766197888</v>
       </c>
       <c r="D6" s="1">
-        <v>0.00016569792537115863</v>
+        <v>0.00016569792537122065</v>
       </c>
       <c r="E6" s="1">
-        <v>-1.8053921857879368e-06</v>
+        <v>-1.8053921857884585e-06</v>
       </c>
       <c r="F6" s="1">
-        <v>0.030153444820767414</v>
+        <v>0.030153444820773249</v>
       </c>
       <c r="G6" s="1">
-        <v>0.030598478825414506</v>
+        <v>0.030598478825420428</v>
       </c>
       <c r="H6" s="1">
-        <v>0.030000345709758923</v>
+        <v>0.03000034570976538</v>
       </c>
       <c r="I6" s="1">
-        <v>0.030100219118045463</v>
+        <v>0.030100219118051851</v>
       </c>
       <c r="J6" s="1">
-        <v>6.6625413003546137e-05</v>
+        <v>6.66254130035418e-05</v>
       </c>
       <c r="K6" s="1">
-        <v>1.1116685437575974e-05</v>
+        <v>1.1116685437571163e-05</v>
       </c>
       <c r="L6" s="1">
-        <v>-9.2327766520229517e-05</v>
+        <v>-9.2327766520249955e-05</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.00022912510777679893</v>
+        <v>-0.00022912510777679806</v>
       </c>
       <c r="N6" s="1">
-        <v>-0.00053813168660061562</v>
+        <v>-0.00053813168660048682</v>
       </c>
       <c r="O6" s="1">
-        <v>-0.00015645210835998642</v>
+        <v>-0.00015645210835797847</v>
       </c>
       <c r="P6" s="1">
-        <v>-4.2072508834227126e-05</v>
+        <v>-4.2072508833879748e-05</v>
       </c>
       <c r="Q6" s="1">
-        <v>8.5612408542838766e-05</v>
+        <v>8.5612408542866088e-05</v>
       </c>
       <c r="R6" s="1">
-        <v>0.00036416345112393923</v>
+        <v>0.0003641634511234778</v>
       </c>
       <c r="S6" s="1">
-        <v>-0.00013662097313786245</v>
+        <v>-0.00013662097312982027</v>
       </c>
       <c r="T6" s="1">
-        <v>0.00040105339158538755</v>
+        <v>0.00040105339159015284</v>
       </c>
       <c r="U6" s="1">
-        <v>0.00063016810357386169</v>
+        <v>0.00063016810357987077</v>
       </c>
       <c r="V6" s="1">
-        <v>0.00051982459422149048</v>
+        <v>0.00051982459422294808</v>
       </c>
       <c r="W6" s="1">
-        <v>0.00059815619062157654</v>
+        <v>0.00059815619062170101</v>
       </c>
       <c r="X6" s="1">
-        <v>0.00080420689596160657</v>
+        <v>0.00080420689596189497</v>
       </c>
       <c r="Y6" s="1">
-        <v>-0.00041204696778012178</v>
+        <v>-0.00041204696777999861</v>
       </c>
       <c r="Z6" s="1">
-        <v>-0.00023712980616433666</v>
+        <v>-0.00023712980616409532</v>
       </c>
       <c r="AA6" s="1">
-        <v>0.00010897237140907942</v>
+        <v>0.00010897237140933963</v>
       </c>
       <c r="AB6" s="1">
-        <v>-3.637764454469429e-05</v>
+        <v>-3.637764454460235e-05</v>
       </c>
       <c r="AC6" s="1">
-        <v>0.00019794183094271577</v>
+        <v>0.00019794183094276694</v>
       </c>
       <c r="AD6" s="1">
-        <v>8.5265824404513572e-05</v>
+        <v>8.5265824404611584e-05</v>
       </c>
       <c r="AE6" s="1">
-        <v>-0.00051547561696388411</v>
+        <v>-0.00051547561696382339</v>
       </c>
       <c r="AF6" s="1">
-        <v>-3.2454133608501336e-08</v>
+        <v>-3.2454133591045681e-08</v>
       </c>
       <c r="AG6" s="1">
-        <v>-0.033092621769745006</v>
+        <v>-0.033092621769763061</v>
       </c>
     </row>
     <row r="7">
@@ -5491,100 +5491,100 @@
         <v>35</v>
       </c>
       <c r="B7" s="1">
-        <v>0.24453092929973877</v>
+        <v>0.24453092929975878</v>
       </c>
       <c r="C7" s="1">
-        <v>0.0004801353360134468</v>
+        <v>0.00048013533601350957</v>
       </c>
       <c r="D7" s="1">
-        <v>0.0001751391426013495</v>
+        <v>0.00017513914260144795</v>
       </c>
       <c r="E7" s="1">
-        <v>-1.7888626944414222e-06</v>
+        <v>-1.7888626944423116e-06</v>
       </c>
       <c r="F7" s="1">
-        <v>0.030041835636406382</v>
+        <v>0.030041835636412745</v>
       </c>
       <c r="G7" s="1">
-        <v>0.030000345709758923</v>
+        <v>0.03000034570976538</v>
       </c>
       <c r="H7" s="1">
-        <v>0.030476263964323704</v>
+        <v>0.0304762639643303</v>
       </c>
       <c r="I7" s="1">
-        <v>0.030315912087219277</v>
+        <v>0.030315912087225803</v>
       </c>
       <c r="J7" s="1">
-        <v>4.890727726150363e-05</v>
+        <v>4.8907277261499293e-05</v>
       </c>
       <c r="K7" s="1">
-        <v>3.1222242740447033e-05</v>
+        <v>3.1222242740439349e-05</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.00011909782198354875</v>
+        <v>-0.00011909782198356658</v>
       </c>
       <c r="M7" s="1">
-        <v>-0.00018076371066552428</v>
+        <v>-0.00018076371066552861</v>
       </c>
       <c r="N7" s="1">
-        <v>-0.00047688667528550822</v>
+        <v>-0.00047688667528537421</v>
       </c>
       <c r="O7" s="1">
-        <v>-1.5872029004725813e-05</v>
+        <v>-1.5872029002626797e-05</v>
       </c>
       <c r="P7" s="1">
-        <v>6.2178382513808361e-06</v>
+        <v>6.2178382517403576e-06</v>
       </c>
       <c r="Q7" s="1">
-        <v>-2.3833388394394351e-05</v>
+        <v>-2.3833388394365728e-05</v>
       </c>
       <c r="R7" s="1">
-        <v>0.00012952114987662203</v>
+        <v>0.00012952114987611375</v>
       </c>
       <c r="S7" s="1">
-        <v>-0.00034091509378690599</v>
+        <v>-0.00034091509377851686</v>
       </c>
       <c r="T7" s="1">
-        <v>0.00013625166984911063</v>
+        <v>0.00013625166985390541</v>
       </c>
       <c r="U7" s="1">
-        <v>0.00029468384770915332</v>
+        <v>0.00029468384771534281</v>
       </c>
       <c r="V7" s="1">
-        <v>0.00061289258271415067</v>
+        <v>0.00061289258271565511</v>
       </c>
       <c r="W7" s="1">
-        <v>0.00057387449215265136</v>
+        <v>0.00057387449215277799</v>
       </c>
       <c r="X7" s="1">
-        <v>0.00073044439893198056</v>
+        <v>0.00073044439893226549</v>
       </c>
       <c r="Y7" s="1">
-        <v>-0.00034433282744365454</v>
+        <v>-0.00034433282744353397</v>
       </c>
       <c r="Z7" s="1">
-        <v>-0.00025737027065190392</v>
+        <v>-0.00025737027065165586</v>
       </c>
       <c r="AA7" s="1">
-        <v>9.7252410781074883e-06</v>
+        <v>9.7252410783676968e-06</v>
       </c>
       <c r="AB7" s="1">
-        <v>-1.7812746486356099e-05</v>
+        <v>-1.7812746486260689e-05</v>
       </c>
       <c r="AC7" s="1">
-        <v>-5.6172368746205611e-05</v>
+        <v>-5.6172368746156172e-05</v>
       </c>
       <c r="AD7" s="1">
-        <v>8.3251848522579788e-05</v>
+        <v>8.3251848522678668e-05</v>
       </c>
       <c r="AE7" s="1">
-        <v>-0.00044234699128296515</v>
+        <v>-0.00044234699128291137</v>
       </c>
       <c r="AF7" s="1">
-        <v>-1.3813260429492097e-06</v>
+        <v>-1.3813260429306699e-06</v>
       </c>
       <c r="AG7" s="1">
-        <v>-0.03337167446689631</v>
+        <v>-0.033371674466914698</v>
       </c>
     </row>
     <row r="8">
@@ -5592,100 +5592,100 @@
         <v>66</v>
       </c>
       <c r="B8" s="1">
-        <v>0.15650125941729837</v>
+        <v>0.15650125941731946</v>
       </c>
       <c r="C8" s="1">
-        <v>0.00044515300783601786</v>
+        <v>0.00044515300783605309</v>
       </c>
       <c r="D8" s="1">
-        <v>0.00021282494787349163</v>
+        <v>0.00021282494787352546</v>
       </c>
       <c r="E8" s="1">
-        <v>-2.1070382446626522e-06</v>
+        <v>-2.1070382446628996e-06</v>
       </c>
       <c r="F8" s="1">
-        <v>0.030120242133651054</v>
+        <v>0.030120242133657341</v>
       </c>
       <c r="G8" s="1">
-        <v>0.030100219118045463</v>
+        <v>0.030100219118051851</v>
       </c>
       <c r="H8" s="1">
-        <v>0.030315912087219277</v>
+        <v>0.030315912087225803</v>
       </c>
       <c r="I8" s="1">
-        <v>0.03188292339187361</v>
+        <v>0.031882923391880272</v>
       </c>
       <c r="J8" s="1">
-        <v>0.00028637087697440042</v>
+        <v>0.00028637087697440736</v>
       </c>
       <c r="K8" s="1">
-        <v>5.5638948474395972e-05</v>
+        <v>5.5638948474384832e-05</v>
       </c>
       <c r="L8" s="1">
-        <v>-0.00015701015398063859</v>
+        <v>-0.00015701015398065095</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.00039145055066626931</v>
+        <v>-0.00039145055066627972</v>
       </c>
       <c r="N8" s="1">
-        <v>-0.00054301100353047749</v>
+        <v>-0.00054301100353031269</v>
       </c>
       <c r="O8" s="1">
-        <v>-0.00012635719190649385</v>
+        <v>-0.00012635719190429943</v>
       </c>
       <c r="P8" s="1">
-        <v>-0.00010002853302654591</v>
+        <v>-0.00010002853302616124</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.00024116965178574176</v>
+        <v>0.00024116965178577385</v>
       </c>
       <c r="R8" s="1">
-        <v>0.00015327081139388833</v>
+        <v>0.00015327081139335057</v>
       </c>
       <c r="S8" s="1">
-        <v>-0.00024618869464664017</v>
+        <v>-0.00024618869463750859</v>
       </c>
       <c r="T8" s="1">
-        <v>6.3804789174243953e-05</v>
+        <v>6.380478917915669e-05</v>
       </c>
       <c r="U8" s="1">
-        <v>8.8121677255866004e-05</v>
+        <v>8.8121677262270603e-05</v>
       </c>
       <c r="V8" s="1">
-        <v>0.00067060269035464776</v>
+        <v>0.00067060269035624544</v>
       </c>
       <c r="W8" s="1">
-        <v>0.0005796951234975649</v>
+        <v>0.00057969512349770064</v>
       </c>
       <c r="X8" s="1">
-        <v>0.00078024845565661778</v>
+        <v>0.00078024845565685457</v>
       </c>
       <c r="Y8" s="1">
-        <v>-0.0002378797457067176</v>
+        <v>-0.00023787974570658663</v>
       </c>
       <c r="Z8" s="1">
-        <v>-0.00023278988812432404</v>
+        <v>-0.0002327898881240686</v>
       </c>
       <c r="AA8" s="1">
-        <v>5.9047850961783249e-05</v>
+        <v>5.9047850962053866e-05</v>
       </c>
       <c r="AB8" s="1">
-        <v>-0.00025231755418881133</v>
+        <v>-0.0002523175541887003</v>
       </c>
       <c r="AC8" s="1">
-        <v>-0.00018564509010019197</v>
+        <v>-0.00018564509010013386</v>
       </c>
       <c r="AD8" s="1">
-        <v>5.8868803333590736e-05</v>
+        <v>5.8868803333695686e-05</v>
       </c>
       <c r="AE8" s="1">
-        <v>-0.00061322226182228268</v>
+        <v>-0.00061322226182221502</v>
       </c>
       <c r="AF8" s="1">
-        <v>1.5350562552556317e-05</v>
+        <v>1.5350562552577784e-05</v>
       </c>
       <c r="AG8" s="1">
-        <v>-0.034700470401991756</v>
+        <v>-0.034700470402010679</v>
       </c>
     </row>
     <row r="9">
@@ -5693,100 +5693,100 @@
         <v>67</v>
       </c>
       <c r="B9" s="1">
-        <v>0.53021884635435024</v>
+        <v>0.53021884635434968</v>
       </c>
       <c r="C9" s="1">
-        <v>3.2869397362727805e-05</v>
+        <v>3.2869397362727209e-05</v>
       </c>
       <c r="D9" s="1">
-        <v>-2.221987789413312e-06</v>
+        <v>-2.2219877894042047e-06</v>
       </c>
       <c r="E9" s="1">
-        <v>2.7222561358544733e-08</v>
+        <v>2.7222561358457912e-08</v>
       </c>
       <c r="F9" s="1">
-        <v>-5.3237864431543089e-05</v>
+        <v>-5.3237864431543956e-05</v>
       </c>
       <c r="G9" s="1">
-        <v>6.6625413003546137e-05</v>
+        <v>6.66254130035418e-05</v>
       </c>
       <c r="H9" s="1">
-        <v>4.890727726150363e-05</v>
+        <v>4.8907277261499293e-05</v>
       </c>
       <c r="I9" s="1">
-        <v>0.00028637087697440042</v>
+        <v>0.00028637087697440736</v>
       </c>
       <c r="J9" s="1">
-        <v>0.00069452697541769735</v>
+        <v>0.00069452697541768705</v>
       </c>
       <c r="K9" s="1">
-        <v>-1.6491982501190782e-05</v>
+        <v>-1.6491982501189942e-05</v>
       </c>
       <c r="L9" s="1">
-        <v>4.9357738275415491e-06</v>
+        <v>4.9357738275405284e-06</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.00055549749087112832</v>
+        <v>-0.00055549749087112257</v>
       </c>
       <c r="N9" s="1">
-        <v>-3.9117611478588133e-05</v>
+        <v>-3.9117611478586324e-05</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.00068775951304060774</v>
+        <v>-0.00068775951304064797</v>
       </c>
       <c r="P9" s="1">
-        <v>1.5278947759053148e-05</v>
+        <v>1.5278947759054822e-05</v>
       </c>
       <c r="Q9" s="1">
-        <v>1.6232317453289116e-05</v>
+        <v>1.6232317453300876e-05</v>
       </c>
       <c r="R9" s="1">
-        <v>0.00052935085347081685</v>
+        <v>0.0005293508534709411</v>
       </c>
       <c r="S9" s="1">
-        <v>-0.00067037853362483509</v>
+        <v>-0.00067037853362436769</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.0006149110339232378</v>
+        <v>-0.00061491103392287004</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.00069023195821488691</v>
+        <v>-0.00069023195821456208</v>
       </c>
       <c r="V9" s="1">
-        <v>-0.00019163649912793895</v>
+        <v>-0.00019163649912788542</v>
       </c>
       <c r="W9" s="1">
-        <v>4.9908737465546154e-06</v>
+        <v>4.9908737465598432e-06</v>
       </c>
       <c r="X9" s="1">
-        <v>2.0432189783391473e-05</v>
+        <v>2.0432189783422739e-05</v>
       </c>
       <c r="Y9" s="1">
-        <v>-0.00014730311223573405</v>
+        <v>-0.00014730311223572478</v>
       </c>
       <c r="Z9" s="1">
-        <v>-0.00013186125767753601</v>
+        <v>-0.00013186125767750544</v>
       </c>
       <c r="AA9" s="1">
-        <v>-0.00010442613433339955</v>
+        <v>-0.00010442613433339297</v>
       </c>
       <c r="AB9" s="1">
-        <v>-7.1902526847598226e-05</v>
+        <v>-7.1902526847595082e-05</v>
       </c>
       <c r="AC9" s="1">
-        <v>0.00027047740389852685</v>
+        <v>0.0002704774038985236</v>
       </c>
       <c r="AD9" s="1">
-        <v>1.4781715064882692e-05</v>
+        <v>1.478171506488688e-05</v>
       </c>
       <c r="AE9" s="1">
-        <v>-4.9240939010911653e-05</v>
+        <v>-4.9240939010910745e-05</v>
       </c>
       <c r="AF9" s="1">
-        <v>-2.5883664685689507e-07</v>
+        <v>-2.5883664685555507e-07</v>
       </c>
       <c r="AG9" s="1">
-        <v>0.00027740404537670107</v>
+        <v>0.00027740404537594516</v>
       </c>
     </row>
     <row r="10">
@@ -5794,100 +5794,100 @@
         <v>37</v>
       </c>
       <c r="B10" s="1">
-        <v>0.010681391711612578</v>
+        <v>0.010681391711612686</v>
       </c>
       <c r="C10" s="1">
-        <v>-4.170690682898532e-05</v>
+        <v>-4.1706906828986899e-05</v>
       </c>
       <c r="D10" s="1">
-        <v>5.4187203834057087e-06</v>
+        <v>5.4187203834020521e-06</v>
       </c>
       <c r="E10" s="1">
-        <v>-2.987382838636382e-08</v>
+        <v>-2.9873828386326412e-08</v>
       </c>
       <c r="F10" s="1">
-        <v>1.4617450913782196e-05</v>
+        <v>1.4617450913776647e-05</v>
       </c>
       <c r="G10" s="1">
-        <v>1.1116685437575974e-05</v>
+        <v>1.1116685437571163e-05</v>
       </c>
       <c r="H10" s="1">
-        <v>3.1222242740447033e-05</v>
+        <v>3.1222242740439349e-05</v>
       </c>
       <c r="I10" s="1">
-        <v>5.5638948474395972e-05</v>
+        <v>5.5638948474384832e-05</v>
       </c>
       <c r="J10" s="1">
-        <v>-1.6491982501190782e-05</v>
+        <v>-1.6491982501189942e-05</v>
       </c>
       <c r="K10" s="1">
-        <v>0.00013255213281719192</v>
+        <v>0.00013255213281719051</v>
       </c>
       <c r="L10" s="1">
-        <v>-8.8716962177340104e-05</v>
+        <v>-8.8716962177337149e-05</v>
       </c>
       <c r="M10" s="1">
-        <v>-1.0934245310610733e-05</v>
+        <v>-1.0934245310612495e-05</v>
       </c>
       <c r="N10" s="1">
-        <v>4.6890565772495958e-05</v>
+        <v>4.689056577250106e-05</v>
       </c>
       <c r="O10" s="1">
-        <v>1.4851878975627903e-05</v>
+        <v>1.4851878975625572e-05</v>
       </c>
       <c r="P10" s="1">
-        <v>-0.00012512041329979854</v>
+        <v>-0.00012512041329979518</v>
       </c>
       <c r="Q10" s="1">
-        <v>8.6989218858997186e-05</v>
+        <v>8.6989218858992822e-05</v>
       </c>
       <c r="R10" s="1">
-        <v>9.4517759596569092e-06</v>
+        <v>9.4517759596644715e-06</v>
       </c>
       <c r="S10" s="1">
-        <v>7.3199712313382759e-05</v>
+        <v>7.3199712313419513e-05</v>
       </c>
       <c r="T10" s="1">
-        <v>6.6851448943402352e-05</v>
+        <v>6.6851448943539747e-05</v>
       </c>
       <c r="U10" s="1">
-        <v>5.7559850174592072e-05</v>
+        <v>5.7559850174702173e-05</v>
       </c>
       <c r="V10" s="1">
-        <v>0.00033282341580277545</v>
+        <v>0.00033282341580277426</v>
       </c>
       <c r="W10" s="1">
-        <v>0.00030158211493842954</v>
+        <v>0.00030158211493843502</v>
       </c>
       <c r="X10" s="1">
-        <v>0.00022573448386252403</v>
+        <v>0.00022573448386251581</v>
       </c>
       <c r="Y10" s="1">
-        <v>3.7400048449972076e-06</v>
+        <v>3.7400048450002434e-06</v>
       </c>
       <c r="Z10" s="1">
-        <v>-1.1603075409240806e-05</v>
+        <v>-1.1603075409238841e-05</v>
       </c>
       <c r="AA10" s="1">
-        <v>-3.5498178598404638e-05</v>
+        <v>-3.5498178598402348e-05</v>
       </c>
       <c r="AB10" s="1">
-        <v>-8.0131796173866306e-06</v>
+        <v>-8.0131796173842995e-06</v>
       </c>
       <c r="AC10" s="1">
-        <v>-1.4635770227950231e-05</v>
+        <v>-1.4635770227949615e-05</v>
       </c>
       <c r="AD10" s="1">
-        <v>5.1264264244140677e-06</v>
+        <v>5.1264264244125566e-06</v>
       </c>
       <c r="AE10" s="1">
-        <v>9.6330986387519997e-06</v>
+        <v>9.6330986387510511e-06</v>
       </c>
       <c r="AF10" s="1">
-        <v>-4.2959753302346994e-08</v>
+        <v>-4.2959753301461845e-08</v>
       </c>
       <c r="AG10" s="1">
-        <v>-0.00045771073886345453</v>
+        <v>-0.00045771073886348532</v>
       </c>
     </row>
     <row r="11">
@@ -5895,100 +5895,100 @@
         <v>38</v>
       </c>
       <c r="B11" s="1">
-        <v>-0.00089500422187153495</v>
+        <v>-0.00089500422187167286</v>
       </c>
       <c r="C11" s="1">
-        <v>-1.5834087445028352e-05</v>
+        <v>-1.5834087445026112e-05</v>
       </c>
       <c r="D11" s="1">
-        <v>-1.0164290925030153e-05</v>
+        <v>-1.0164290925023854e-05</v>
       </c>
       <c r="E11" s="1">
-        <v>8.3945306509481477e-08</v>
+        <v>8.3945306509415435e-08</v>
       </c>
       <c r="F11" s="1">
-        <v>-8.6919554873058226e-05</v>
+        <v>-8.691955487307579e-05</v>
       </c>
       <c r="G11" s="1">
-        <v>-9.2327766520229517e-05</v>
+        <v>-9.2327766520249955e-05</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.00011909782198354875</v>
+        <v>-0.00011909782198356658</v>
       </c>
       <c r="I11" s="1">
-        <v>-0.00015701015398063859</v>
+        <v>-0.00015701015398065095</v>
       </c>
       <c r="J11" s="1">
-        <v>4.9357738275415491e-06</v>
+        <v>4.9357738275405284e-06</v>
       </c>
       <c r="K11" s="1">
-        <v>-8.8716962177340104e-05</v>
+        <v>-8.8716962177337149e-05</v>
       </c>
       <c r="L11" s="1">
-        <v>9.8719398795702517e-05</v>
+        <v>9.8719398795698017e-05</v>
       </c>
       <c r="M11" s="1">
-        <v>3.7463394122614607e-06</v>
+        <v>3.7463394122637714e-06</v>
       </c>
       <c r="N11" s="1">
-        <v>6.2373832497835236e-06</v>
+        <v>6.2373832497774893e-06</v>
       </c>
       <c r="O11" s="1">
-        <v>-2.9249647700473134e-06</v>
+        <v>-2.9249647700422177e-06</v>
       </c>
       <c r="P11" s="1">
-        <v>7.9964195053160251e-05</v>
+        <v>7.9964195053154301e-05</v>
       </c>
       <c r="Q11" s="1">
-        <v>-9.3108601017310576e-05</v>
+        <v>-9.310860101730502e-05</v>
       </c>
       <c r="R11" s="1">
-        <v>-1.8742266801432527e-06</v>
+        <v>-1.8742266801471627e-06</v>
       </c>
       <c r="S11" s="1">
-        <v>-6.3373557136240467e-06</v>
+        <v>-6.3373557136822277e-06</v>
       </c>
       <c r="T11" s="1">
-        <v>-8.4988893052374544e-07</v>
+        <v>-8.4988893064356333e-07</v>
       </c>
       <c r="U11" s="1">
-        <v>-5.4263575489451482e-06</v>
+        <v>-5.4263575490151605e-06</v>
       </c>
       <c r="V11" s="1">
-        <v>-4.4825854992801742e-05</v>
+        <v>-4.4825854992802731e-05</v>
       </c>
       <c r="W11" s="1">
-        <v>-2.0644865361526364e-05</v>
+        <v>-2.064486536153044e-05</v>
       </c>
       <c r="X11" s="1">
-        <v>1.3075094486275733e-05</v>
+        <v>1.307509448629636e-05</v>
       </c>
       <c r="Y11" s="1">
-        <v>-2.0825242689456352e-05</v>
+        <v>-2.0825242689459029e-05</v>
       </c>
       <c r="Z11" s="1">
-        <v>8.3168958492756631e-06</v>
+        <v>8.3168958492761374e-06</v>
       </c>
       <c r="AA11" s="1">
-        <v>-2.1930698282460739e-05</v>
+        <v>-2.1930698282462467e-05</v>
       </c>
       <c r="AB11" s="1">
-        <v>-8.8423774420776411e-06</v>
+        <v>-8.8423774420809208e-06</v>
       </c>
       <c r="AC11" s="1">
-        <v>9.7004977714089765e-06</v>
+        <v>9.7004977714067878e-06</v>
       </c>
       <c r="AD11" s="1">
-        <v>-3.8721753493472041e-05</v>
+        <v>-3.8721753493470333e-05</v>
       </c>
       <c r="AE11" s="1">
-        <v>-9.5503911746879462e-06</v>
+        <v>-9.55039117468777e-06</v>
       </c>
       <c r="AF11" s="1">
-        <v>-1.9952545385008703e-06</v>
+        <v>-1.9952545385016068e-06</v>
       </c>
       <c r="AG11" s="1">
-        <v>0.00038421640520633853</v>
+        <v>0.0003842164052062757</v>
       </c>
     </row>
     <row r="12">
@@ -5996,100 +5996,100 @@
         <v>68</v>
       </c>
       <c r="B12" s="1">
-        <v>0.18999195648812162</v>
+        <v>0.18999195648812298</v>
       </c>
       <c r="C12" s="1">
-        <v>-1.7647373021457746e-05</v>
+        <v>-1.7647373021460213e-05</v>
       </c>
       <c r="D12" s="1">
-        <v>-8.0905793299225069e-06</v>
+        <v>-8.0905793299309095e-06</v>
       </c>
       <c r="E12" s="1">
-        <v>7.8449751780093324e-08</v>
+        <v>7.8449751780175486e-08</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.00018742302000795703</v>
+        <v>-0.00018742302000795876</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.00022912510777679893</v>
+        <v>-0.00022912510777679806</v>
       </c>
       <c r="H12" s="1">
-        <v>-0.00018076371066552428</v>
+        <v>-0.00018076371066552861</v>
       </c>
       <c r="I12" s="1">
-        <v>-0.00039145055066626931</v>
+        <v>-0.00039145055066627972</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.00055549749087112832</v>
+        <v>-0.00055549749087112257</v>
       </c>
       <c r="K12" s="1">
-        <v>-1.0934245310610733e-05</v>
+        <v>-1.0934245310612495e-05</v>
       </c>
       <c r="L12" s="1">
-        <v>3.7463394122614607e-06</v>
+        <v>3.7463394122637714e-06</v>
       </c>
       <c r="M12" s="1">
-        <v>0.00069260867974513132</v>
+        <v>0.0006926086797451272</v>
       </c>
       <c r="N12" s="1">
-        <v>2.8341870140294276e-05</v>
+        <v>2.8341870140295604e-05</v>
       </c>
       <c r="O12" s="1">
-        <v>0.00056407952063137503</v>
+        <v>0.00056407952063151424</v>
       </c>
       <c r="P12" s="1">
-        <v>1.8239794488046403e-05</v>
+        <v>1.8239794488060938e-05</v>
       </c>
       <c r="Q12" s="1">
-        <v>-2.7446660152643326e-05</v>
+        <v>-2.7446660152654541e-05</v>
       </c>
       <c r="R12" s="1">
-        <v>-0.00068014145471993477</v>
+        <v>-0.00068014145472006108</v>
       </c>
       <c r="S12" s="1">
-        <v>-0.00025015859317760415</v>
+        <v>-0.00025015859317772558</v>
       </c>
       <c r="T12" s="1">
-        <v>-0.00031603665453426355</v>
+        <v>-0.0003160366545341522</v>
       </c>
       <c r="U12" s="1">
-        <v>-0.00046582455830870145</v>
+        <v>-0.00046582455830861808</v>
       </c>
       <c r="V12" s="1">
-        <v>2.036360918105083e-05</v>
+        <v>2.0363609181036386e-05</v>
       </c>
       <c r="W12" s="1">
-        <v>-0.00011948310861770831</v>
+        <v>-0.0001194831086177157</v>
       </c>
       <c r="X12" s="1">
-        <v>-9.1053974870151453e-05</v>
+        <v>-9.1053974870172527e-05</v>
       </c>
       <c r="Y12" s="1">
-        <v>0.00014312581436422687</v>
+        <v>0.00014312581436421709</v>
       </c>
       <c r="Z12" s="1">
-        <v>8.6301910462069112e-05</v>
+        <v>8.6301910462051291e-05</v>
       </c>
       <c r="AA12" s="1">
-        <v>1.3517519335680308e-05</v>
+        <v>1.3517519335672692e-05</v>
       </c>
       <c r="AB12" s="1">
-        <v>0.00012000097798650625</v>
+        <v>0.00012000097798650466</v>
       </c>
       <c r="AC12" s="1">
-        <v>-0.00031407113203542239</v>
+        <v>-0.00031407113203542249</v>
       </c>
       <c r="AD12" s="1">
-        <v>-1.031219847218427e-05</v>
+        <v>-1.0312198472184744e-05</v>
       </c>
       <c r="AE12" s="1">
-        <v>7.8934588127470092e-05</v>
+        <v>7.8934588127470268e-05</v>
       </c>
       <c r="AF12" s="1">
-        <v>-9.3031498793091866e-06</v>
+        <v>-9.3031498793098626e-06</v>
       </c>
       <c r="AG12" s="1">
-        <v>0.00036637251601717285</v>
+        <v>0.00036637251601745642</v>
       </c>
     </row>
     <row r="13">
@@ -6097,100 +6097,100 @@
         <v>40</v>
       </c>
       <c r="B13" s="1">
-        <v>0.070095318796993739</v>
+        <v>0.070095318796987827</v>
       </c>
       <c r="C13" s="1">
-        <v>-0.0010487097153188856</v>
+        <v>-0.0010487097153188841</v>
       </c>
       <c r="D13" s="1">
-        <v>-2.4869131880844795e-05</v>
+        <v>-2.4869131880823328e-05</v>
       </c>
       <c r="E13" s="1">
-        <v>2.5099687305187632e-07</v>
+        <v>2.5099687305165228e-07</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.00047713329546585038</v>
+        <v>-0.00047713329546572114</v>
       </c>
       <c r="G13" s="1">
-        <v>-0.00053813168660061562</v>
+        <v>-0.00053813168660048682</v>
       </c>
       <c r="H13" s="1">
-        <v>-0.00047688667528550822</v>
+        <v>-0.00047688667528537421</v>
       </c>
       <c r="I13" s="1">
-        <v>-0.00054301100353047749</v>
+        <v>-0.00054301100353031269</v>
       </c>
       <c r="J13" s="1">
-        <v>-3.9117611478588133e-05</v>
+        <v>-3.9117611478586324e-05</v>
       </c>
       <c r="K13" s="1">
-        <v>4.6890565772495958e-05</v>
+        <v>4.689056577250106e-05</v>
       </c>
       <c r="L13" s="1">
-        <v>6.2373832497835236e-06</v>
+        <v>6.2373832497774893e-06</v>
       </c>
       <c r="M13" s="1">
-        <v>2.8341870140294276e-05</v>
+        <v>2.8341870140295604e-05</v>
       </c>
       <c r="N13" s="1">
-        <v>0.0072502240123255143</v>
+        <v>0.0072502240123254605</v>
       </c>
       <c r="O13" s="1">
-        <v>-0.0002601629112278134</v>
+        <v>-0.00026016291122745854</v>
       </c>
       <c r="P13" s="1">
-        <v>4.0239170956307276e-05</v>
+        <v>4.023917095641018e-05</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.00027724624148147743</v>
+        <v>0.00027724624148138283</v>
       </c>
       <c r="R13" s="1">
-        <v>-0.00091199988763497608</v>
+        <v>-0.00091199988763510879</v>
       </c>
       <c r="S13" s="1">
-        <v>-0.0015780207153636061</v>
+        <v>-0.0015780207153625208</v>
       </c>
       <c r="T13" s="1">
-        <v>-0.0015964963793665334</v>
+        <v>-0.0015964963793656619</v>
       </c>
       <c r="U13" s="1">
-        <v>-0.0017584352693106751</v>
+        <v>-0.0017584352693096788</v>
       </c>
       <c r="V13" s="1">
-        <v>-8.3912013857698144e-05</v>
+        <v>-8.3912013857624906e-05</v>
       </c>
       <c r="W13" s="1">
-        <v>4.2871151026074964e-05</v>
+        <v>4.2871151026082662e-05</v>
       </c>
       <c r="X13" s="1">
-        <v>-0.00012679262648712487</v>
+        <v>-0.00012679262648706679</v>
       </c>
       <c r="Y13" s="1">
-        <v>-0.00012423568623270184</v>
+        <v>-0.00012423568623269989</v>
       </c>
       <c r="Z13" s="1">
-        <v>-0.00025185269242975188</v>
+        <v>-0.00025185269242975042</v>
       </c>
       <c r="AA13" s="1">
-        <v>-0.00055524597503499296</v>
+        <v>-0.00055524597503498732</v>
       </c>
       <c r="AB13" s="1">
-        <v>0.00038495303918796174</v>
+        <v>0.00038495303918797063</v>
       </c>
       <c r="AC13" s="1">
-        <v>0.00031350607108254482</v>
+        <v>0.00031350607108254823</v>
       </c>
       <c r="AD13" s="1">
-        <v>0.00029237774965709483</v>
+        <v>0.0002923777496571002</v>
       </c>
       <c r="AE13" s="1">
-        <v>0.0002841986396675875</v>
+        <v>0.00028419863966759628</v>
       </c>
       <c r="AF13" s="1">
-        <v>-1.7544922723330289e-05</v>
+        <v>-1.7544922723328605e-05</v>
       </c>
       <c r="AG13" s="1">
-        <v>0.0031175344859868813</v>
+        <v>0.0031175344859850824</v>
       </c>
     </row>
     <row r="14">
@@ -6198,100 +6198,100 @@
         <v>69</v>
       </c>
       <c r="B14" s="1">
-        <v>0.20487099966735658</v>
+        <v>0.20487099966738059</v>
       </c>
       <c r="C14" s="1">
-        <v>-4.1581387441835214e-05</v>
+        <v>-4.1581387441793472e-05</v>
       </c>
       <c r="D14" s="1">
-        <v>6.4843019309966578e-06</v>
+        <v>6.4843019310249555e-06</v>
       </c>
       <c r="E14" s="1">
-        <v>-4.3636033771014753e-08</v>
+        <v>-4.3636033771295121e-08</v>
       </c>
       <c r="F14" s="1">
-        <v>4.355909649232919e-05</v>
+        <v>4.3559096494347541e-05</v>
       </c>
       <c r="G14" s="1">
-        <v>-0.00015645210835998642</v>
+        <v>-0.00015645210835797847</v>
       </c>
       <c r="H14" s="1">
-        <v>-1.5872029004725813e-05</v>
+        <v>-1.5872029002626797e-05</v>
       </c>
       <c r="I14" s="1">
-        <v>-0.00012635719190649385</v>
+        <v>-0.00012635719190429943</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.00068775951304060774</v>
+        <v>-0.00068775951304064797</v>
       </c>
       <c r="K14" s="1">
-        <v>1.4851878975627903e-05</v>
+        <v>1.4851878975625572e-05</v>
       </c>
       <c r="L14" s="1">
-        <v>-2.9249647700473134e-06</v>
+        <v>-2.9249647700422177e-06</v>
       </c>
       <c r="M14" s="1">
-        <v>0.00056407952063137503</v>
+        <v>0.00056407952063151424</v>
       </c>
       <c r="N14" s="1">
-        <v>-0.0002601629112278134</v>
+        <v>-0.00026016291122745854</v>
       </c>
       <c r="O14" s="1">
-        <v>0.007594851939534096</v>
+        <v>0.0075948519395370971</v>
       </c>
       <c r="P14" s="1">
-        <v>-0.00037251313273085548</v>
+        <v>-0.00037251313273070847</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.0017111975261598531</v>
+        <v>0.001711197526160403</v>
       </c>
       <c r="R14" s="1">
-        <v>-0.0062870829274421121</v>
+        <v>-0.0062870829274445598</v>
       </c>
       <c r="S14" s="1">
-        <v>0.0061417852561689926</v>
+        <v>0.0061417852561749114</v>
       </c>
       <c r="T14" s="1">
-        <v>0.0060848045623117242</v>
+        <v>0.0060848045623139169</v>
       </c>
       <c r="U14" s="1">
-        <v>0.0061307640570175161</v>
+        <v>0.0061307640570207704</v>
       </c>
       <c r="V14" s="1">
-        <v>0.00025547087324245214</v>
+        <v>0.00025547087324311567</v>
       </c>
       <c r="W14" s="1">
-        <v>-9.6540220808540717e-06</v>
+        <v>-9.6540220807647334e-06</v>
       </c>
       <c r="X14" s="1">
-        <v>-1.0069996538039291e-05</v>
+        <v>-1.0069996537914391e-05</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.00020151626409416028</v>
+        <v>0.00020151626409432247</v>
       </c>
       <c r="Z14" s="1">
-        <v>0.00014856053400961328</v>
+        <v>0.00014856053400962434</v>
       </c>
       <c r="AA14" s="1">
-        <v>0.0001270345434028694</v>
+        <v>0.00012703454340306196</v>
       </c>
       <c r="AB14" s="1">
-        <v>8.0592660727258486e-06</v>
+        <v>8.0592660727917681e-06</v>
       </c>
       <c r="AC14" s="1">
-        <v>-0.00043240290623325611</v>
+        <v>-0.00043240290623325957</v>
       </c>
       <c r="AD14" s="1">
-        <v>-3.5469225863355575e-05</v>
+        <v>-3.5469225863328686e-05</v>
       </c>
       <c r="AE14" s="1">
-        <v>-8.1705877430851559e-07</v>
+        <v>-8.1705877425126971e-07</v>
       </c>
       <c r="AF14" s="1">
-        <v>-1.1490207322627666e-05</v>
+        <v>-1.1490207322604573e-05</v>
       </c>
       <c r="AG14" s="1">
-        <v>-0.005751154607528397</v>
+        <v>-0.0057511546075397352</v>
       </c>
     </row>
     <row r="15">
@@ -6299,100 +6299,100 @@
         <v>47</v>
       </c>
       <c r="B15" s="1">
-        <v>0.092725278518696122</v>
+        <v>0.092725278518696344</v>
       </c>
       <c r="C15" s="1">
-        <v>3.3393533150383268e-05</v>
+        <v>3.3393533150399592e-05</v>
       </c>
       <c r="D15" s="1">
-        <v>-2.9850549362174939e-06</v>
+        <v>-2.9850549361984391e-06</v>
       </c>
       <c r="E15" s="1">
-        <v>1.617104642311154e-08</v>
+        <v>1.6171046422917781e-08</v>
       </c>
       <c r="F15" s="1">
-        <v>-2.5897101901336313e-05</v>
+        <v>-2.5897101900995223e-05</v>
       </c>
       <c r="G15" s="1">
-        <v>-4.2072508834227126e-05</v>
+        <v>-4.2072508833879748e-05</v>
       </c>
       <c r="H15" s="1">
-        <v>6.2178382513808361e-06</v>
+        <v>6.2178382517403576e-06</v>
       </c>
       <c r="I15" s="1">
-        <v>-0.00010002853302654591</v>
+        <v>-0.00010002853302616124</v>
       </c>
       <c r="J15" s="1">
-        <v>1.5278947759053148e-05</v>
+        <v>1.5278947759054822e-05</v>
       </c>
       <c r="K15" s="1">
-        <v>-0.00012512041329979854</v>
+        <v>-0.00012512041329979518</v>
       </c>
       <c r="L15" s="1">
-        <v>7.9964195053160251e-05</v>
+        <v>7.9964195053154301e-05</v>
       </c>
       <c r="M15" s="1">
-        <v>1.8239794488046403e-05</v>
+        <v>1.8239794488060938e-05</v>
       </c>
       <c r="N15" s="1">
-        <v>4.0239170956307276e-05</v>
+        <v>4.023917095641018e-05</v>
       </c>
       <c r="O15" s="1">
-        <v>-0.00037251313273085548</v>
+        <v>-0.00037251313273070847</v>
       </c>
       <c r="P15" s="1">
-        <v>0.0027190853671194117</v>
+        <v>0.0027190853671193501</v>
       </c>
       <c r="Q15" s="1">
-        <v>-0.0037388103203595409</v>
+        <v>-0.0037388103203595383</v>
       </c>
       <c r="R15" s="1">
-        <v>0.00068880251039061093</v>
+        <v>0.00068880251039071154</v>
       </c>
       <c r="S15" s="1">
-        <v>0.0014440329519780229</v>
+        <v>0.0014440329519790542</v>
       </c>
       <c r="T15" s="1">
-        <v>0.0014576385035319551</v>
+        <v>0.0014576385035321255</v>
       </c>
       <c r="U15" s="1">
-        <v>0.0014786427911949755</v>
+        <v>0.0014786427911953901</v>
       </c>
       <c r="V15" s="1">
-        <v>-0.00043048703692254566</v>
+        <v>-0.00043048703692242748</v>
       </c>
       <c r="W15" s="1">
-        <v>-0.00030382101624232998</v>
+        <v>-0.00030382101624231025</v>
       </c>
       <c r="X15" s="1">
-        <v>-0.00021807517445544784</v>
+        <v>-0.00021807517445539542</v>
       </c>
       <c r="Y15" s="1">
-        <v>2.0602633176556315e-05</v>
+        <v>2.0602633176584071e-05</v>
       </c>
       <c r="Z15" s="1">
-        <v>2.1208324294179446e-05</v>
+        <v>2.1208324294188553e-05</v>
       </c>
       <c r="AA15" s="1">
-        <v>8.6752368962019193e-05</v>
+        <v>8.6752368962056924e-05</v>
       </c>
       <c r="AB15" s="1">
-        <v>0.00017477400305719809</v>
+        <v>0.00017477400305722108</v>
       </c>
       <c r="AC15" s="1">
-        <v>9.117931194760928e-05</v>
+        <v>9.1179311947623158e-05</v>
       </c>
       <c r="AD15" s="1">
-        <v>-2.5851851986121105e-05</v>
+        <v>-2.5851851986102674e-05</v>
       </c>
       <c r="AE15" s="1">
-        <v>6.1673252275460874e-05</v>
+        <v>6.1673252275483426e-05</v>
       </c>
       <c r="AF15" s="1">
-        <v>-5.7854473027461255e-06</v>
+        <v>-5.7854473027423579e-06</v>
       </c>
       <c r="AG15" s="1">
-        <v>-0.0011535020475508433</v>
+        <v>-0.0011535020475529657</v>
       </c>
     </row>
     <row r="16">
@@ -6400,100 +6400,100 @@
         <v>48</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.1903353434036415</v>
+        <v>-0.19033534340364675</v>
       </c>
       <c r="C16" s="1">
-        <v>1.1208301938427276e-06</v>
+        <v>1.120830193841169e-06</v>
       </c>
       <c r="D16" s="1">
-        <v>8.2391666210945396e-06</v>
+        <v>8.2391666210911786e-06</v>
       </c>
       <c r="E16" s="1">
-        <v>-7.1675315913851051e-08</v>
+        <v>-7.1675315913814311e-08</v>
       </c>
       <c r="F16" s="1">
-        <v>2.9223457779913465e-05</v>
+        <v>2.9223457779938185e-05</v>
       </c>
       <c r="G16" s="1">
-        <v>8.5612408542838766e-05</v>
+        <v>8.5612408542866088e-05</v>
       </c>
       <c r="H16" s="1">
-        <v>-2.3833388394394351e-05</v>
+        <v>-2.3833388394365728e-05</v>
       </c>
       <c r="I16" s="1">
-        <v>0.00024116965178574176</v>
+        <v>0.00024116965178577385</v>
       </c>
       <c r="J16" s="1">
-        <v>1.6232317453289116e-05</v>
+        <v>1.6232317453300876e-05</v>
       </c>
       <c r="K16" s="1">
-        <v>8.6989218858997186e-05</v>
+        <v>8.6989218858992822e-05</v>
       </c>
       <c r="L16" s="1">
-        <v>-9.3108601017310576e-05</v>
+        <v>-9.310860101730502e-05</v>
       </c>
       <c r="M16" s="1">
-        <v>-2.7446660152643326e-05</v>
+        <v>-2.7446660152654541e-05</v>
       </c>
       <c r="N16" s="1">
-        <v>0.00027724624148147743</v>
+        <v>0.00027724624148138283</v>
       </c>
       <c r="O16" s="1">
-        <v>0.0017111975261598531</v>
+        <v>0.001711197526160403</v>
       </c>
       <c r="P16" s="1">
-        <v>-0.0037388103203595409</v>
+        <v>-0.0037388103203595383</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.0067348920506647156</v>
+        <v>0.0067348920506649567</v>
       </c>
       <c r="R16" s="1">
-        <v>-0.0018823744602505851</v>
+        <v>-0.0018823744602511484</v>
       </c>
       <c r="S16" s="1">
-        <v>-0.00051924856188685544</v>
+        <v>-0.0005192485618868794</v>
       </c>
       <c r="T16" s="1">
-        <v>-0.00054422994365079034</v>
+        <v>-0.00054422994365095157</v>
       </c>
       <c r="U16" s="1">
-        <v>-0.00057438156921500142</v>
+        <v>-0.00057438156921516079</v>
       </c>
       <c r="V16" s="1">
-        <v>5.3692139461420236e-05</v>
+        <v>5.3692139461476317e-05</v>
       </c>
       <c r="W16" s="1">
-        <v>2.5814108316817816e-05</v>
+        <v>2.581410831683023e-05</v>
       </c>
       <c r="X16" s="1">
-        <v>-1.5131260341680276e-05</v>
+        <v>-1.513126034168754e-05</v>
       </c>
       <c r="Y16" s="1">
-        <v>-1.2801732878625789e-05</v>
+        <v>-1.2801732878619881e-05</v>
       </c>
       <c r="Z16" s="1">
-        <v>-8.1196816918625804e-06</v>
+        <v>-8.1196816918589889e-06</v>
       </c>
       <c r="AA16" s="1">
-        <v>-3.7585556804825798e-05</v>
+        <v>-3.7585556804817667e-05</v>
       </c>
       <c r="AB16" s="1">
-        <v>-0.0001589865983666124</v>
+        <v>-0.00015898659836663192</v>
       </c>
       <c r="AC16" s="1">
-        <v>6.4742783925667772e-06</v>
+        <v>6.4742783925656388e-06</v>
       </c>
       <c r="AD16" s="1">
-        <v>4.4165492988795709e-05</v>
+        <v>4.4165492988776736e-05</v>
       </c>
       <c r="AE16" s="1">
-        <v>4.9579089101290481e-05</v>
+        <v>4.9579089101279422e-05</v>
       </c>
       <c r="AF16" s="1">
-        <v>1.0211394622058583e-05</v>
+        <v>1.0211394622061497e-05</v>
       </c>
       <c r="AG16" s="1">
-        <v>0.0001874139609287671</v>
+        <v>0.00018741396092867083</v>
       </c>
     </row>
     <row r="17">
@@ -6501,100 +6501,100 @@
         <v>70</v>
       </c>
       <c r="B17" s="1">
-        <v>-0.044479301832504474</v>
+        <v>-0.044479301832541208</v>
       </c>
       <c r="C17" s="1">
-        <v>3.9492816686277437e-05</v>
+        <v>3.9492816686296139e-05</v>
       </c>
       <c r="D17" s="1">
-        <v>1.0251132452634222e-05</v>
+        <v>1.0251132452651678e-05</v>
       </c>
       <c r="E17" s="1">
-        <v>-1.327694325121753e-07</v>
+        <v>-1.3276943251235148e-07</v>
       </c>
       <c r="F17" s="1">
-        <v>0.00020374946334861255</v>
+        <v>0.00020374946334810774</v>
       </c>
       <c r="G17" s="1">
-        <v>0.00036416345112393923</v>
+        <v>0.0003641634511234778</v>
       </c>
       <c r="H17" s="1">
-        <v>0.00012952114987662203</v>
+        <v>0.00012952114987611375</v>
       </c>
       <c r="I17" s="1">
-        <v>0.00015327081139388833</v>
+        <v>0.00015327081139335057</v>
       </c>
       <c r="J17" s="1">
-        <v>0.00052935085347081685</v>
+        <v>0.0005293508534709411</v>
       </c>
       <c r="K17" s="1">
-        <v>9.4517759596569092e-06</v>
+        <v>9.4517759596644715e-06</v>
       </c>
       <c r="L17" s="1">
-        <v>-1.8742266801432527e-06</v>
+        <v>-1.8742266801471627e-06</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.00068014145471993477</v>
+        <v>-0.00068014145472006108</v>
       </c>
       <c r="N17" s="1">
-        <v>-0.00091199988763497608</v>
+        <v>-0.00091199988763510879</v>
       </c>
       <c r="O17" s="1">
-        <v>-0.0062870829274421121</v>
+        <v>-0.0062870829274445598</v>
       </c>
       <c r="P17" s="1">
-        <v>0.00068880251039061093</v>
+        <v>0.00068880251039071154</v>
       </c>
       <c r="Q17" s="1">
-        <v>-0.0018823744602505851</v>
+        <v>-0.0018823744602511484</v>
       </c>
       <c r="R17" s="1">
-        <v>0.0063800178794011933</v>
+        <v>0.0063800178794034164</v>
       </c>
       <c r="S17" s="1">
-        <v>-0.0015523249693885136</v>
+        <v>-0.001552324969389614</v>
       </c>
       <c r="T17" s="1">
-        <v>-0.0014744777188995712</v>
+        <v>-0.0014744777189009872</v>
       </c>
       <c r="U17" s="1">
-        <v>-0.0012717542548056017</v>
+        <v>-0.001271754254806922</v>
       </c>
       <c r="V17" s="1">
-        <v>3.2700324811713681e-05</v>
+        <v>3.2700324811736957e-05</v>
       </c>
       <c r="W17" s="1">
-        <v>0.00012693989295350645</v>
+        <v>0.00012693989295354741</v>
       </c>
       <c r="X17" s="1">
-        <v>0.00011423920236361656</v>
+        <v>0.0001142392023637094</v>
       </c>
       <c r="Y17" s="1">
-        <v>-0.00016981563587370967</v>
+        <v>-0.00016981563587372398</v>
       </c>
       <c r="Z17" s="1">
-        <v>-6.7863698670650398e-05</v>
+        <v>-6.7863698670615297e-05</v>
       </c>
       <c r="AA17" s="1">
-        <v>-9.3705969443198486e-06</v>
+        <v>-9.3705969443084916e-06</v>
       </c>
       <c r="AB17" s="1">
-        <v>-0.00017147962722392299</v>
+        <v>-0.00017147962722391082</v>
       </c>
       <c r="AC17" s="1">
-        <v>0.00026445574276653971</v>
+        <v>0.0002644557427666104</v>
       </c>
       <c r="AD17" s="1">
-        <v>-0.00010851448363802929</v>
+        <v>-0.00010851448363802115</v>
       </c>
       <c r="AE17" s="1">
-        <v>-0.00016261950767807186</v>
+        <v>-0.00016261950767805598</v>
       </c>
       <c r="AF17" s="1">
-        <v>1.4722592374358358e-05</v>
+        <v>1.472259237436152e-05</v>
       </c>
       <c r="AG17" s="1">
-        <v>0.0014805283891910646</v>
+        <v>0.0014805283891921625</v>
       </c>
     </row>
     <row r="18">
@@ -6602,100 +6602,100 @@
         <v>50</v>
       </c>
       <c r="B18" s="1">
-        <v>0.40224292592224276</v>
+        <v>0.40224292592218386</v>
       </c>
       <c r="C18" s="1">
-        <v>-0.00037926386093542551</v>
+        <v>-0.00037926386093509239</v>
       </c>
       <c r="D18" s="1">
-        <v>3.9347954577622583e-05</v>
+        <v>3.9347954578175743e-05</v>
       </c>
       <c r="E18" s="1">
-        <v>-5.3557068817196715e-07</v>
+        <v>-5.3557068817756773e-07</v>
       </c>
       <c r="F18" s="1">
-        <v>-3.7378172552256575e-05</v>
+        <v>-3.7378172544236948e-05</v>
       </c>
       <c r="G18" s="1">
-        <v>-0.00013662097313786245</v>
+        <v>-0.00013662097312982027</v>
       </c>
       <c r="H18" s="1">
-        <v>-0.00034091509378690599</v>
+        <v>-0.00034091509377851686</v>
       </c>
       <c r="I18" s="1">
-        <v>-0.00024618869464664017</v>
+        <v>-0.00024618869463750859</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.00067037853362483509</v>
+        <v>-0.00067037853362436769</v>
       </c>
       <c r="K18" s="1">
-        <v>7.3199712313382759e-05</v>
+        <v>7.3199712313419513e-05</v>
       </c>
       <c r="L18" s="1">
-        <v>-6.3373557136240467e-06</v>
+        <v>-6.3373557136822277e-06</v>
       </c>
       <c r="M18" s="1">
-        <v>-0.00025015859317760415</v>
+        <v>-0.00025015859317772558</v>
       </c>
       <c r="N18" s="1">
-        <v>-0.0015780207153636061</v>
+        <v>-0.0015780207153625208</v>
       </c>
       <c r="O18" s="1">
-        <v>0.0061417852561689926</v>
+        <v>0.0061417852561749114</v>
       </c>
       <c r="P18" s="1">
-        <v>0.0014440329519780229</v>
+        <v>0.0014440329519790542</v>
       </c>
       <c r="Q18" s="1">
-        <v>-0.00051924856188685544</v>
+        <v>-0.0005192485618868794</v>
       </c>
       <c r="R18" s="1">
-        <v>-0.0015523249693885136</v>
+        <v>-0.001552324969389614</v>
       </c>
       <c r="S18" s="1">
-        <v>0.023376988401570223</v>
+        <v>0.023376988401592108</v>
       </c>
       <c r="T18" s="1">
-        <v>0.022164341657411255</v>
+        <v>0.022164341657414613</v>
       </c>
       <c r="U18" s="1">
-        <v>0.02273693726784709</v>
+        <v>0.02273693726785575</v>
       </c>
       <c r="V18" s="1">
-        <v>0.0050335107200127349</v>
+        <v>0.005033510720015906</v>
       </c>
       <c r="W18" s="1">
-        <v>0.00023695266345581667</v>
+        <v>0.00023695266345641688</v>
       </c>
       <c r="X18" s="1">
-        <v>0.00016853852100981621</v>
+        <v>0.00016853852101078072</v>
       </c>
       <c r="Y18" s="1">
-        <v>-9.0174471712389792e-05</v>
+        <v>-9.017447171170978e-05</v>
       </c>
       <c r="Z18" s="1">
-        <v>0.00024016602106297254</v>
+        <v>0.00024016602106319371</v>
       </c>
       <c r="AA18" s="1">
-        <v>-7.2671619523012598e-05</v>
+        <v>-7.2671619522096664e-05</v>
       </c>
       <c r="AB18" s="1">
-        <v>-0.00025689511402608028</v>
+        <v>-0.00025689511402574028</v>
       </c>
       <c r="AC18" s="1">
-        <v>-0.00055320955251512982</v>
+        <v>-0.00055320955251483145</v>
       </c>
       <c r="AD18" s="1">
-        <v>0.00027550934052472317</v>
+        <v>0.00027550934052488624</v>
       </c>
       <c r="AE18" s="1">
-        <v>-0.00018162150452560866</v>
+        <v>-0.00018162150452528947</v>
       </c>
       <c r="AF18" s="1">
-        <v>5.4838507387989024e-05</v>
+        <v>5.483850738810872e-05</v>
       </c>
       <c r="AG18" s="1">
-        <v>-0.020452865841487838</v>
+        <v>-0.020452865841534329</v>
       </c>
     </row>
     <row r="19">
@@ -6703,100 +6703,100 @@
         <v>51</v>
       </c>
       <c r="B19" s="1">
-        <v>0.47843856198505325</v>
+        <v>0.47843856198499446</v>
       </c>
       <c r="C19" s="1">
-        <v>-0.00033569246695577489</v>
+        <v>-0.0003356924669555232</v>
       </c>
       <c r="D19" s="1">
-        <v>2.3081702616830051e-05</v>
+        <v>2.3081702616858891e-05</v>
       </c>
       <c r="E19" s="1">
-        <v>-3.0657499079046117e-07</v>
+        <v>-3.0657499079080507e-07</v>
       </c>
       <c r="F19" s="1">
-        <v>0.00058181669874420895</v>
+        <v>0.00058181669874880944</v>
       </c>
       <c r="G19" s="1">
-        <v>0.00040105339158538755</v>
+        <v>0.00040105339159015284</v>
       </c>
       <c r="H19" s="1">
-        <v>0.00013625166984911063</v>
+        <v>0.00013625166985390541</v>
       </c>
       <c r="I19" s="1">
-        <v>6.3804789174243953e-05</v>
+        <v>6.380478917915669e-05</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.0006149110339232378</v>
+        <v>-0.00061491103392287004</v>
       </c>
       <c r="K19" s="1">
-        <v>6.6851448943402352e-05</v>
+        <v>6.6851448943539747e-05</v>
       </c>
       <c r="L19" s="1">
-        <v>-8.4988893052374544e-07</v>
+        <v>-8.4988893064356333e-07</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.00031603665453426355</v>
+        <v>-0.0003160366545341522</v>
       </c>
       <c r="N19" s="1">
-        <v>-0.0015964963793665334</v>
+        <v>-0.0015964963793656619</v>
       </c>
       <c r="O19" s="1">
-        <v>0.0060848045623117242</v>
+        <v>0.0060848045623139169</v>
       </c>
       <c r="P19" s="1">
-        <v>0.0014576385035319551</v>
+        <v>0.0014576385035321255</v>
       </c>
       <c r="Q19" s="1">
-        <v>-0.00054422994365079034</v>
+        <v>-0.00054422994365095157</v>
       </c>
       <c r="R19" s="1">
-        <v>-0.0014744777188995712</v>
+        <v>-0.0014744777189009872</v>
       </c>
       <c r="S19" s="1">
-        <v>0.022164341657411255</v>
+        <v>0.022164341657414613</v>
       </c>
       <c r="T19" s="1">
-        <v>0.022575960855013039</v>
+        <v>0.02257596085501587</v>
       </c>
       <c r="U19" s="1">
-        <v>0.022973965540856817</v>
+        <v>0.022973965540864699</v>
       </c>
       <c r="V19" s="1">
-        <v>0.0052452243626285276</v>
+        <v>0.0052452243626315773</v>
       </c>
       <c r="W19" s="1">
-        <v>0.0003828905637384937</v>
+        <v>0.00038289056373908004</v>
       </c>
       <c r="X19" s="1">
-        <v>0.00022481924746994321</v>
+        <v>0.00022481924747098751</v>
       </c>
       <c r="Y19" s="1">
-        <v>-1.4257478924681322e-05</v>
+        <v>-1.425747892400131e-05</v>
       </c>
       <c r="Z19" s="1">
-        <v>0.00034666014959906007</v>
+        <v>0.00034666014959928299</v>
       </c>
       <c r="AA19" s="1">
-        <v>9.0852054109150093e-05</v>
+        <v>9.0852054110066027e-05</v>
       </c>
       <c r="AB19" s="1">
-        <v>-0.0001121794469985879</v>
+        <v>-0.00011217944699824789</v>
       </c>
       <c r="AC19" s="1">
-        <v>-0.00043573741290494142</v>
+        <v>-0.00043573741290466733</v>
       </c>
       <c r="AD19" s="1">
-        <v>0.00024185499836162569</v>
+        <v>0.00024185499836178875</v>
       </c>
       <c r="AE19" s="1">
-        <v>-0.00017140635086634881</v>
+        <v>-0.00017140635086601574</v>
       </c>
       <c r="AF19" s="1">
-        <v>2.863592259376305e-05</v>
+        <v>2.863592259387971e-05</v>
       </c>
       <c r="AG19" s="1">
-        <v>-0.020596120860202294</v>
+        <v>-0.020596120860248063</v>
       </c>
     </row>
     <row r="20">
@@ -6804,100 +6804,100 @@
         <v>52</v>
       </c>
       <c r="B20" s="1">
-        <v>0.52734134466249516</v>
+        <v>0.52734134466243732</v>
       </c>
       <c r="C20" s="1">
-        <v>-0.00015267774938342125</v>
+        <v>-0.00015267774938319633</v>
       </c>
       <c r="D20" s="1">
-        <v>4.8338837890395505e-05</v>
+        <v>4.8338837890562472e-05</v>
       </c>
       <c r="E20" s="1">
-        <v>-5.8882490348818363e-07</v>
+        <v>-5.8882490348993529e-07</v>
       </c>
       <c r="F20" s="1">
-        <v>0.00083011177811210743</v>
+        <v>0.0008301117781180159</v>
       </c>
       <c r="G20" s="1">
-        <v>0.00063016810357386169</v>
+        <v>0.00063016810357987077</v>
       </c>
       <c r="H20" s="1">
-        <v>0.00029468384770915332</v>
+        <v>0.00029468384771534281</v>
       </c>
       <c r="I20" s="1">
-        <v>8.8121677255866004e-05</v>
+        <v>8.8121677262270603e-05</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.00069023195821488691</v>
+        <v>-0.00069023195821456208</v>
       </c>
       <c r="K20" s="1">
-        <v>5.7559850174592072e-05</v>
+        <v>5.7559850174702173e-05</v>
       </c>
       <c r="L20" s="1">
-        <v>-5.4263575489451482e-06</v>
+        <v>-5.4263575490151605e-06</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.00046582455830870145</v>
+        <v>-0.00046582455830861808</v>
       </c>
       <c r="N20" s="1">
-        <v>-0.0017584352693106751</v>
+        <v>-0.0017584352693096788</v>
       </c>
       <c r="O20" s="1">
-        <v>0.0061307640570175161</v>
+        <v>0.0061307640570207704</v>
       </c>
       <c r="P20" s="1">
-        <v>0.0014786427911949755</v>
+        <v>0.0014786427911953901</v>
       </c>
       <c r="Q20" s="1">
-        <v>-0.00057438156921500142</v>
+        <v>-0.00057438156921516079</v>
       </c>
       <c r="R20" s="1">
-        <v>-0.0012717542548056017</v>
+        <v>-0.001271754254806922</v>
       </c>
       <c r="S20" s="1">
-        <v>0.02273693726784709</v>
+        <v>0.02273693726785575</v>
       </c>
       <c r="T20" s="1">
-        <v>0.022973965540856817</v>
+        <v>0.022973965540864699</v>
       </c>
       <c r="U20" s="1">
-        <v>0.024812149546353968</v>
+        <v>0.024812149546361684</v>
       </c>
       <c r="V20" s="1">
-        <v>0.005288482810795192</v>
+        <v>0.0052884828107982243</v>
       </c>
       <c r="W20" s="1">
-        <v>0.00060188645724172651</v>
+        <v>0.00060188645724231805</v>
       </c>
       <c r="X20" s="1">
-        <v>0.00044498619486699198</v>
+        <v>0.00044498619486800506</v>
       </c>
       <c r="Y20" s="1">
-        <v>-3.6177618540009226e-05</v>
+        <v>-3.6177618539350032e-05</v>
       </c>
       <c r="Z20" s="1">
-        <v>0.00045493464717452029</v>
+        <v>0.00045493464717472412</v>
       </c>
       <c r="AA20" s="1">
-        <v>0.00024869343828051033</v>
+        <v>0.00024869343828142626</v>
       </c>
       <c r="AB20" s="1">
-        <v>-0.00024002029645060069</v>
+        <v>-0.00024002029645027456</v>
       </c>
       <c r="AC20" s="1">
-        <v>-0.00048760358415083152</v>
+        <v>-0.00048760358415053662</v>
       </c>
       <c r="AD20" s="1">
-        <v>0.00017844899324374885</v>
+        <v>0.00017844899324389804</v>
       </c>
       <c r="AE20" s="1">
-        <v>-0.00034100401916588308</v>
+        <v>-0.00034100401916557083</v>
       </c>
       <c r="AF20" s="1">
-        <v>2.4363727253978295e-05</v>
+        <v>2.4363727254094955e-05</v>
       </c>
       <c r="AG20" s="1">
-        <v>-0.021162249863819038</v>
+        <v>-0.021162249863864252</v>
       </c>
     </row>
     <row r="21">
@@ -6905,100 +6905,100 @@
         <v>53</v>
       </c>
       <c r="B21" s="1">
-        <v>-0.007751926723342204</v>
+        <v>-0.0077519267233501195</v>
       </c>
       <c r="C21" s="1">
-        <v>-7.8433900262784784e-05</v>
+        <v>-7.8433900262733406e-05</v>
       </c>
       <c r="D21" s="1">
-        <v>0.00013305191093106471</v>
+        <v>0.00013305191093110965</v>
       </c>
       <c r="E21" s="1">
-        <v>-1.0832780701910347e-06</v>
+        <v>-1.0832780701914478e-06</v>
       </c>
       <c r="F21" s="1">
-        <v>0.00059543285392457245</v>
+        <v>0.00059543285392597237</v>
       </c>
       <c r="G21" s="1">
-        <v>0.00051982459422149048</v>
+        <v>0.00051982459422294808</v>
       </c>
       <c r="H21" s="1">
-        <v>0.00061289258271415067</v>
+        <v>0.00061289258271565511</v>
       </c>
       <c r="I21" s="1">
-        <v>0.00067060269035464776</v>
+        <v>0.00067060269035624544</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.00019163649912793895</v>
+        <v>-0.00019163649912788542</v>
       </c>
       <c r="K21" s="1">
-        <v>0.00033282341580277545</v>
+        <v>0.00033282341580277426</v>
       </c>
       <c r="L21" s="1">
-        <v>-4.4825854992801742e-05</v>
+        <v>-4.4825854992802731e-05</v>
       </c>
       <c r="M21" s="1">
-        <v>2.036360918105083e-05</v>
+        <v>2.0363609181036386e-05</v>
       </c>
       <c r="N21" s="1">
-        <v>-8.3912013857698144e-05</v>
+        <v>-8.3912013857624906e-05</v>
       </c>
       <c r="O21" s="1">
-        <v>0.00025547087324245214</v>
+        <v>0.00025547087324311567</v>
       </c>
       <c r="P21" s="1">
-        <v>-0.00043048703692254566</v>
+        <v>-0.00043048703692242748</v>
       </c>
       <c r="Q21" s="1">
-        <v>5.3692139461420236e-05</v>
+        <v>5.3692139461476317e-05</v>
       </c>
       <c r="R21" s="1">
-        <v>3.2700324811713681e-05</v>
+        <v>3.2700324811736957e-05</v>
       </c>
       <c r="S21" s="1">
-        <v>0.0050335107200127349</v>
+        <v>0.005033510720015906</v>
       </c>
       <c r="T21" s="1">
-        <v>0.0052452243626285276</v>
+        <v>0.0052452243626315773</v>
       </c>
       <c r="U21" s="1">
-        <v>0.005288482810795192</v>
+        <v>0.0052884828107982243</v>
       </c>
       <c r="V21" s="1">
-        <v>0.0078447725291576342</v>
+        <v>0.0078447725291580523</v>
       </c>
       <c r="W21" s="1">
-        <v>0.0023198522412528101</v>
+        <v>0.0023198522412529029</v>
       </c>
       <c r="X21" s="1">
-        <v>0.0019616945112801766</v>
+        <v>0.0019616945112801557</v>
       </c>
       <c r="Y21" s="1">
-        <v>0.00050894058814127899</v>
+        <v>0.00050894058814137961</v>
       </c>
       <c r="Z21" s="1">
-        <v>0.00011631901643067229</v>
+        <v>0.00011631901643072054</v>
       </c>
       <c r="AA21" s="1">
-        <v>0.00019604203860612048</v>
+        <v>0.00019604203860624364</v>
       </c>
       <c r="AB21" s="1">
-        <v>-7.1775453925572094e-05</v>
+        <v>-7.1775453925507909e-05</v>
       </c>
       <c r="AC21" s="1">
-        <v>-0.00061601468137977271</v>
+        <v>-0.0006160146813797068</v>
       </c>
       <c r="AD21" s="1">
-        <v>0.00011058415358735935</v>
+        <v>0.00011058415358738971</v>
       </c>
       <c r="AE21" s="1">
-        <v>-0.00012933739434734838</v>
+        <v>-0.00012933739434730588</v>
       </c>
       <c r="AF21" s="1">
-        <v>1.299369418641201e-06</v>
+        <v>1.2993694186624514e-06</v>
       </c>
       <c r="AG21" s="1">
-        <v>-0.011221213583072182</v>
+        <v>-0.011221213583076473</v>
       </c>
     </row>
     <row r="22">
@@ -7006,100 +7006,100 @@
         <v>54</v>
       </c>
       <c r="B22" s="1">
-        <v>0.029091760175338429</v>
+        <v>0.029091760175339008</v>
       </c>
       <c r="C22" s="1">
-        <v>-4.4622951285627718e-05</v>
+        <v>-4.462295128562704e-05</v>
       </c>
       <c r="D22" s="1">
-        <v>2.0399969914487043e-05</v>
+        <v>2.0399969914492572e-05</v>
       </c>
       <c r="E22" s="1">
-        <v>-1.4705250733446665e-07</v>
+        <v>-1.4705250733452425e-07</v>
       </c>
       <c r="F22" s="1">
-        <v>0.00037935257794391138</v>
+        <v>0.00037935257794403715</v>
       </c>
       <c r="G22" s="1">
-        <v>0.00059815619062157654</v>
+        <v>0.00059815619062170101</v>
       </c>
       <c r="H22" s="1">
-        <v>0.00057387449215265136</v>
+        <v>0.00057387449215277799</v>
       </c>
       <c r="I22" s="1">
-        <v>0.0005796951234975649</v>
+        <v>0.00057969512349770064</v>
       </c>
       <c r="J22" s="1">
-        <v>4.9908737465546154e-06</v>
+        <v>4.9908737465598432e-06</v>
       </c>
       <c r="K22" s="1">
-        <v>0.00030158211493842954</v>
+        <v>0.00030158211493843502</v>
       </c>
       <c r="L22" s="1">
-        <v>-2.0644865361526364e-05</v>
+        <v>-2.064486536153044e-05</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.00011948310861770831</v>
+        <v>-0.0001194831086177157</v>
       </c>
       <c r="N22" s="1">
-        <v>4.2871151026074964e-05</v>
+        <v>4.2871151026082662e-05</v>
       </c>
       <c r="O22" s="1">
-        <v>-9.6540220808540717e-06</v>
+        <v>-9.6540220807647334e-06</v>
       </c>
       <c r="P22" s="1">
-        <v>-0.00030382101624232998</v>
+        <v>-0.00030382101624231025</v>
       </c>
       <c r="Q22" s="1">
-        <v>2.5814108316817816e-05</v>
+        <v>2.581410831683023e-05</v>
       </c>
       <c r="R22" s="1">
-        <v>0.00012693989295350645</v>
+        <v>0.00012693989295354741</v>
       </c>
       <c r="S22" s="1">
-        <v>0.00023695266345581667</v>
+        <v>0.00023695266345641688</v>
       </c>
       <c r="T22" s="1">
-        <v>0.0003828905637384937</v>
+        <v>0.00038289056373908004</v>
       </c>
       <c r="U22" s="1">
-        <v>0.00060188645724172651</v>
+        <v>0.00060188645724231805</v>
       </c>
       <c r="V22" s="1">
-        <v>0.0023198522412528101</v>
+        <v>0.0023198522412529029</v>
       </c>
       <c r="W22" s="1">
-        <v>0.0027608834509463952</v>
+        <v>0.0027608834509464117</v>
       </c>
       <c r="X22" s="1">
-        <v>0.0019255860444802751</v>
+        <v>0.0019255860444803031</v>
       </c>
       <c r="Y22" s="1">
-        <v>-4.7301490033906492e-05</v>
+        <v>-4.7301490033894457e-05</v>
       </c>
       <c r="Z22" s="1">
-        <v>3.8396999357074256e-05</v>
+        <v>3.8396999357094992e-05</v>
       </c>
       <c r="AA22" s="1">
-        <v>-0.00021039728322931562</v>
+        <v>-0.00021039728322929828</v>
       </c>
       <c r="AB22" s="1">
-        <v>-2.7225297011923381e-05</v>
+        <v>-2.7225297011917093e-05</v>
       </c>
       <c r="AC22" s="1">
-        <v>-4.5646462106337451e-05</v>
+        <v>-4.5646462106335608e-05</v>
       </c>
       <c r="AD22" s="1">
-        <v>5.0536034822499707e-05</v>
+        <v>5.0536034822504098e-05</v>
       </c>
       <c r="AE22" s="1">
-        <v>2.2562439070754965e-05</v>
+        <v>2.2562439070754857e-05</v>
       </c>
       <c r="AF22" s="1">
-        <v>-1.628976240681561e-07</v>
+        <v>-1.6289762406500514e-07</v>
       </c>
       <c r="AG22" s="1">
-        <v>-0.0033208616930401904</v>
+        <v>-0.0033208616930412893</v>
       </c>
     </row>
     <row r="23">
@@ -7107,100 +7107,100 @@
         <v>55</v>
       </c>
       <c r="B23" s="1">
-        <v>-0.049419544670595422</v>
+        <v>-0.049419544670597781</v>
       </c>
       <c r="C23" s="1">
-        <v>0.00011364653780756125</v>
+        <v>0.00011364653780754092</v>
       </c>
       <c r="D23" s="1">
-        <v>0.00017097207127786355</v>
+        <v>0.00017097207127780292</v>
       </c>
       <c r="E23" s="1">
-        <v>-2.2301552036290766e-06</v>
+        <v>-2.2301552036284142e-06</v>
       </c>
       <c r="F23" s="1">
-        <v>0.0010848267231048044</v>
+        <v>0.0010848267231050269</v>
       </c>
       <c r="G23" s="1">
-        <v>0.00080420689596160657</v>
+        <v>0.00080420689596189497</v>
       </c>
       <c r="H23" s="1">
-        <v>0.00073044439893198056</v>
+        <v>0.00073044439893226549</v>
       </c>
       <c r="I23" s="1">
-        <v>0.00078024845565661778</v>
+        <v>0.00078024845565685457</v>
       </c>
       <c r="J23" s="1">
-        <v>2.0432189783391473e-05</v>
+        <v>2.0432189783422739e-05</v>
       </c>
       <c r="K23" s="1">
-        <v>0.00022573448386252403</v>
+        <v>0.00022573448386251581</v>
       </c>
       <c r="L23" s="1">
-        <v>1.3075094486275733e-05</v>
+        <v>1.307509448629636e-05</v>
       </c>
       <c r="M23" s="1">
-        <v>-9.1053974870151453e-05</v>
+        <v>-9.1053974870172527e-05</v>
       </c>
       <c r="N23" s="1">
-        <v>-0.00012679262648712487</v>
+        <v>-0.00012679262648706679</v>
       </c>
       <c r="O23" s="1">
-        <v>-1.0069996538039291e-05</v>
+        <v>-1.0069996537914391e-05</v>
       </c>
       <c r="P23" s="1">
-        <v>-0.00021807517445544784</v>
+        <v>-0.00021807517445539542</v>
       </c>
       <c r="Q23" s="1">
-        <v>-1.5131260341680276e-05</v>
+        <v>-1.513126034168754e-05</v>
       </c>
       <c r="R23" s="1">
-        <v>0.00011423920236361656</v>
+        <v>0.0001142392023637094</v>
       </c>
       <c r="S23" s="1">
-        <v>0.00016853852100981621</v>
+        <v>0.00016853852101078072</v>
       </c>
       <c r="T23" s="1">
-        <v>0.00022481924746994321</v>
+        <v>0.00022481924747098751</v>
       </c>
       <c r="U23" s="1">
-        <v>0.00044498619486699198</v>
+        <v>0.00044498619486800506</v>
       </c>
       <c r="V23" s="1">
-        <v>0.0019616945112801766</v>
+        <v>0.0019616945112801557</v>
       </c>
       <c r="W23" s="1">
-        <v>0.0019255860444802751</v>
+        <v>0.0019255860444803031</v>
       </c>
       <c r="X23" s="1">
-        <v>0.0047151843627826007</v>
+        <v>0.0047151843627823552</v>
       </c>
       <c r="Y23" s="1">
-        <v>-3.6155088586796924e-05</v>
+        <v>-3.6155088586743581e-05</v>
       </c>
       <c r="Z23" s="1">
-        <v>0.00022636762845414969</v>
+        <v>0.00022636762845414227</v>
       </c>
       <c r="AA23" s="1">
-        <v>-8.1361246555503725e-05</v>
+        <v>-8.1361246555469464e-05</v>
       </c>
       <c r="AB23" s="1">
-        <v>-4.2779699290939558e-05</v>
+        <v>-4.2779699290885782e-05</v>
       </c>
       <c r="AC23" s="1">
-        <v>-0.00019339129599773349</v>
+        <v>-0.00019339129599767451</v>
       </c>
       <c r="AD23" s="1">
-        <v>-3.1531642576034706e-05</v>
+        <v>-3.1531642576015841e-05</v>
       </c>
       <c r="AE23" s="1">
-        <v>-2.4951340780711862e-05</v>
+        <v>-2.4951340780680637e-05</v>
       </c>
       <c r="AF23" s="1">
-        <v>-1.3981167166544401e-05</v>
+        <v>-1.3981167166537273e-05</v>
       </c>
       <c r="AG23" s="1">
-        <v>-0.0054552228789067573</v>
+        <v>-0.0054552228789080549</v>
       </c>
     </row>
     <row r="24">
@@ -7208,100 +7208,100 @@
         <v>56</v>
       </c>
       <c r="B24" s="1">
-        <v>0.085635035657697714</v>
+        <v>0.085635035657699518</v>
       </c>
       <c r="C24" s="1">
-        <v>0.00012476702225810968</v>
+        <v>0.00012476702225811261</v>
       </c>
       <c r="D24" s="1">
-        <v>1.1153319499612009e-05</v>
+        <v>1.1153319499621007e-05</v>
       </c>
       <c r="E24" s="1">
-        <v>1.854832317286762e-07</v>
+        <v>1.8548323172858048e-07</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.00054617911183649833</v>
+        <v>-0.00054617911183637777</v>
       </c>
       <c r="G24" s="1">
-        <v>-0.00041204696778012178</v>
+        <v>-0.00041204696777999861</v>
       </c>
       <c r="H24" s="1">
-        <v>-0.00034433282744365454</v>
+        <v>-0.00034433282744353397</v>
       </c>
       <c r="I24" s="1">
-        <v>-0.0002378797457067176</v>
+        <v>-0.00023787974570658663</v>
       </c>
       <c r="J24" s="1">
-        <v>-0.00014730311223573405</v>
+        <v>-0.00014730311223572478</v>
       </c>
       <c r="K24" s="1">
-        <v>3.7400048449972076e-06</v>
+        <v>3.7400048450002434e-06</v>
       </c>
       <c r="L24" s="1">
-        <v>-2.0825242689456352e-05</v>
+        <v>-2.0825242689459029e-05</v>
       </c>
       <c r="M24" s="1">
-        <v>0.00014312581436422687</v>
+        <v>0.00014312581436421709</v>
       </c>
       <c r="N24" s="1">
-        <v>-0.00012423568623270184</v>
+        <v>-0.00012423568623269989</v>
       </c>
       <c r="O24" s="1">
-        <v>0.00020151626409416028</v>
+        <v>0.00020151626409432247</v>
       </c>
       <c r="P24" s="1">
-        <v>2.0602633176556315e-05</v>
+        <v>2.0602633176584071e-05</v>
       </c>
       <c r="Q24" s="1">
-        <v>-1.2801732878625789e-05</v>
+        <v>-1.2801732878619881e-05</v>
       </c>
       <c r="R24" s="1">
-        <v>-0.00016981563587370967</v>
+        <v>-0.00016981563587372398</v>
       </c>
       <c r="S24" s="1">
-        <v>-9.0174471712389792e-05</v>
+        <v>-9.017447171170978e-05</v>
       </c>
       <c r="T24" s="1">
-        <v>-1.4257478924681322e-05</v>
+        <v>-1.425747892400131e-05</v>
       </c>
       <c r="U24" s="1">
-        <v>-3.6177618540009226e-05</v>
+        <v>-3.6177618539350032e-05</v>
       </c>
       <c r="V24" s="1">
-        <v>0.00050894058814127899</v>
+        <v>0.00050894058814137961</v>
       </c>
       <c r="W24" s="1">
-        <v>-4.7301490033906492e-05</v>
+        <v>-4.7301490033894457e-05</v>
       </c>
       <c r="X24" s="1">
-        <v>-3.6155088586796924e-05</v>
+        <v>-3.6155088586743581e-05</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.0020408988724432758</v>
+        <v>0.0020408988724432905</v>
       </c>
       <c r="Z24" s="1">
-        <v>0.0011261900698388897</v>
+        <v>0.0011261900698389122</v>
       </c>
       <c r="AA24" s="1">
-        <v>0.0015189986954756698</v>
+        <v>0.0015189986954756895</v>
       </c>
       <c r="AB24" s="1">
-        <v>-5.0774667800986993e-05</v>
+        <v>-5.0774667800981355e-05</v>
       </c>
       <c r="AC24" s="1">
-        <v>-0.00048271513975417242</v>
+        <v>-0.00048271513975417068</v>
       </c>
       <c r="AD24" s="1">
-        <v>-0.00019523744577627908</v>
+        <v>-0.00019523744577627105</v>
       </c>
       <c r="AE24" s="1">
-        <v>-0.00013343823562917139</v>
+        <v>-0.00013343823562916575</v>
       </c>
       <c r="AF24" s="1">
-        <v>-1.3807850022097426e-05</v>
+        <v>-1.3807850022094208e-05</v>
       </c>
       <c r="AG24" s="1">
-        <v>-0.0014038587316349961</v>
+        <v>-0.0014038587316362106</v>
       </c>
     </row>
     <row r="25">
@@ -7309,100 +7309,100 @@
         <v>57</v>
       </c>
       <c r="B25" s="1">
-        <v>0.087811737888431163</v>
+        <v>0.087811737888431232</v>
       </c>
       <c r="C25" s="1">
-        <v>0.00024688383600290296</v>
+        <v>0.00024688383600290366</v>
       </c>
       <c r="D25" s="1">
-        <v>0.00010018497687356532</v>
+        <v>0.0001001849768735624</v>
       </c>
       <c r="E25" s="1">
-        <v>-8.7686144722127035e-07</v>
+        <v>-8.7686144722122758e-07</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.00050637629835039604</v>
+        <v>-0.00050637629835017465</v>
       </c>
       <c r="G25" s="1">
-        <v>-0.00023712980616433666</v>
+        <v>-0.00023712980616409532</v>
       </c>
       <c r="H25" s="1">
-        <v>-0.00025737027065190392</v>
+        <v>-0.00025737027065165586</v>
       </c>
       <c r="I25" s="1">
-        <v>-0.00023278988812432404</v>
+        <v>-0.0002327898881240686</v>
       </c>
       <c r="J25" s="1">
-        <v>-0.00013186125767753601</v>
+        <v>-0.00013186125767750544</v>
       </c>
       <c r="K25" s="1">
-        <v>-1.1603075409240806e-05</v>
+        <v>-1.1603075409238841e-05</v>
       </c>
       <c r="L25" s="1">
-        <v>8.3168958492756631e-06</v>
+        <v>8.3168958492761374e-06</v>
       </c>
       <c r="M25" s="1">
-        <v>8.6301910462069112e-05</v>
+        <v>8.6301910462051291e-05</v>
       </c>
       <c r="N25" s="1">
-        <v>-0.00025185269242975188</v>
+        <v>-0.00025185269242975042</v>
       </c>
       <c r="O25" s="1">
-        <v>0.00014856053400961328</v>
+        <v>0.00014856053400962434</v>
       </c>
       <c r="P25" s="1">
-        <v>2.1208324294179446e-05</v>
+        <v>2.1208324294188553e-05</v>
       </c>
       <c r="Q25" s="1">
-        <v>-8.1196816918625804e-06</v>
+        <v>-8.1196816918589889e-06</v>
       </c>
       <c r="R25" s="1">
-        <v>-6.7863698670650398e-05</v>
+        <v>-6.7863698670615297e-05</v>
       </c>
       <c r="S25" s="1">
-        <v>0.00024016602106297254</v>
+        <v>0.00024016602106319371</v>
       </c>
       <c r="T25" s="1">
-        <v>0.00034666014959906007</v>
+        <v>0.00034666014959928299</v>
       </c>
       <c r="U25" s="1">
-        <v>0.00045493464717452029</v>
+        <v>0.00045493464717472412</v>
       </c>
       <c r="V25" s="1">
-        <v>0.00011631901643067229</v>
+        <v>0.00011631901643072054</v>
       </c>
       <c r="W25" s="1">
-        <v>3.8396999357074256e-05</v>
+        <v>3.8396999357094992e-05</v>
       </c>
       <c r="X25" s="1">
-        <v>0.00022636762845414969</v>
+        <v>0.00022636762845414227</v>
       </c>
       <c r="Y25" s="1">
-        <v>0.0011261900698388897</v>
+        <v>0.0011261900698389122</v>
       </c>
       <c r="Z25" s="1">
-        <v>0.0019255310204552005</v>
+        <v>0.0019255310204552096</v>
       </c>
       <c r="AA25" s="1">
-        <v>0.0012385051975720349</v>
+        <v>0.0012385051975720633</v>
       </c>
       <c r="AB25" s="1">
-        <v>6.0064881108626463e-05</v>
+        <v>6.0064881108652483e-05</v>
       </c>
       <c r="AC25" s="1">
-        <v>-0.00022508732740438649</v>
+        <v>-0.00022508732740436133</v>
       </c>
       <c r="AD25" s="1">
-        <v>6.3168295775918246e-05</v>
+        <v>6.3168295775933208e-05</v>
       </c>
       <c r="AE25" s="1">
-        <v>9.9699912801576047e-05</v>
+        <v>9.9699912801592527e-05</v>
       </c>
       <c r="AF25" s="1">
-        <v>-1.3740505637078107e-05</v>
+        <v>-1.3740505637072116e-05</v>
       </c>
       <c r="AG25" s="1">
-        <v>-0.0035027236299267155</v>
+        <v>-0.0035027236299279602</v>
       </c>
     </row>
     <row r="26">
@@ -7410,100 +7410,100 @@
         <v>58</v>
       </c>
       <c r="B26" s="1">
-        <v>0.13017926463680041</v>
+        <v>0.13017926463680157</v>
       </c>
       <c r="C26" s="1">
-        <v>0.00059012301569078961</v>
+        <v>0.00059012301569079568</v>
       </c>
       <c r="D26" s="1">
-        <v>1.7828568744848315e-05</v>
+        <v>1.7828568744855037e-05</v>
       </c>
       <c r="E26" s="1">
-        <v>7.3412141061194641e-08</v>
+        <v>7.3412141061128572e-08</v>
       </c>
       <c r="F26" s="1">
-        <v>-2.03152316665383e-05</v>
+        <v>-2.0315231666286765e-05</v>
       </c>
       <c r="G26" s="1">
-        <v>0.00010897237140907942</v>
+        <v>0.00010897237140933963</v>
       </c>
       <c r="H26" s="1">
-        <v>9.7252410781074883e-06</v>
+        <v>9.7252410783676968e-06</v>
       </c>
       <c r="I26" s="1">
-        <v>5.9047850961783249e-05</v>
+        <v>5.9047850962053866e-05</v>
       </c>
       <c r="J26" s="1">
-        <v>-0.00010442613433339955</v>
+        <v>-0.00010442613433339297</v>
       </c>
       <c r="K26" s="1">
-        <v>-3.5498178598404638e-05</v>
+        <v>-3.5498178598402348e-05</v>
       </c>
       <c r="L26" s="1">
-        <v>-2.1930698282460739e-05</v>
+        <v>-2.1930698282462467e-05</v>
       </c>
       <c r="M26" s="1">
-        <v>1.3517519335680308e-05</v>
+        <v>1.3517519335672692e-05</v>
       </c>
       <c r="N26" s="1">
-        <v>-0.00055524597503499296</v>
+        <v>-0.00055524597503498732</v>
       </c>
       <c r="O26" s="1">
-        <v>0.0001270345434028694</v>
+        <v>0.00012703454340306196</v>
       </c>
       <c r="P26" s="1">
-        <v>8.6752368962019193e-05</v>
+        <v>8.6752368962056924e-05</v>
       </c>
       <c r="Q26" s="1">
-        <v>-3.7585556804825798e-05</v>
+        <v>-3.7585556804817667e-05</v>
       </c>
       <c r="R26" s="1">
-        <v>-9.3705969443198486e-06</v>
+        <v>-9.3705969443084916e-06</v>
       </c>
       <c r="S26" s="1">
-        <v>-7.2671619523012598e-05</v>
+        <v>-7.2671619522096664e-05</v>
       </c>
       <c r="T26" s="1">
-        <v>9.0852054109150093e-05</v>
+        <v>9.0852054110066027e-05</v>
       </c>
       <c r="U26" s="1">
-        <v>0.00024869343828051033</v>
+        <v>0.00024869343828142626</v>
       </c>
       <c r="V26" s="1">
-        <v>0.00019604203860612048</v>
+        <v>0.00019604203860624364</v>
       </c>
       <c r="W26" s="1">
-        <v>-0.00021039728322931562</v>
+        <v>-0.00021039728322929828</v>
       </c>
       <c r="X26" s="1">
-        <v>-8.1361246555503725e-05</v>
+        <v>-8.1361246555469464e-05</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.0015189986954756698</v>
+        <v>0.0015189986954756895</v>
       </c>
       <c r="Z26" s="1">
-        <v>0.0012385051975720349</v>
+        <v>0.0012385051975720633</v>
       </c>
       <c r="AA26" s="1">
-        <v>0.0025968817099177254</v>
+        <v>0.0025968817099177406</v>
       </c>
       <c r="AB26" s="1">
-        <v>0.00015413976487661774</v>
+        <v>0.00015413976487662728</v>
       </c>
       <c r="AC26" s="1">
-        <v>-7.8970394950280201e-05</v>
+        <v>-7.8970394950274346e-05</v>
       </c>
       <c r="AD26" s="1">
-        <v>-8.1573441071297907e-06</v>
+        <v>-8.1573441071216592e-06</v>
       </c>
       <c r="AE26" s="1">
-        <v>0.00010805658202150286</v>
+        <v>0.00010805658202150915</v>
       </c>
       <c r="AF26" s="1">
-        <v>-1.04890042444879e-05</v>
+        <v>-1.0489004244484444e-05</v>
       </c>
       <c r="AG26" s="1">
-        <v>-0.0019435441378938094</v>
+        <v>-0.0019435441378948849</v>
       </c>
     </row>
     <row r="27">
@@ -7511,100 +7511,100 @@
         <v>59</v>
       </c>
       <c r="B27" s="1">
-        <v>0.066891749004262049</v>
+        <v>0.066891749004261897</v>
       </c>
       <c r="C27" s="1">
-        <v>-5.2426104394325814e-05</v>
+        <v>-5.2426104394323809e-05</v>
       </c>
       <c r="D27" s="1">
-        <v>-3.1417369092205422e-05</v>
+        <v>-3.141736909219317e-05</v>
       </c>
       <c r="E27" s="1">
-        <v>2.8972752488738926e-07</v>
+        <v>2.8972752488727152e-07</v>
       </c>
       <c r="F27" s="1">
-        <v>-4.4001561505363149e-05</v>
+        <v>-4.4001561505269474e-05</v>
       </c>
       <c r="G27" s="1">
-        <v>-3.637764454469429e-05</v>
+        <v>-3.637764454460235e-05</v>
       </c>
       <c r="H27" s="1">
-        <v>-1.7812746486356099e-05</v>
+        <v>-1.7812746486260689e-05</v>
       </c>
       <c r="I27" s="1">
-        <v>-0.00025231755418881133</v>
+        <v>-0.0002523175541887003</v>
       </c>
       <c r="J27" s="1">
-        <v>-7.1902526847598226e-05</v>
+        <v>-7.1902526847595082e-05</v>
       </c>
       <c r="K27" s="1">
-        <v>-8.0131796173866306e-06</v>
+        <v>-8.0131796173842995e-06</v>
       </c>
       <c r="L27" s="1">
-        <v>-8.8423774420776411e-06</v>
+        <v>-8.8423774420809208e-06</v>
       </c>
       <c r="M27" s="1">
-        <v>0.00012000097798650625</v>
+        <v>0.00012000097798650466</v>
       </c>
       <c r="N27" s="1">
-        <v>0.00038495303918796174</v>
+        <v>0.00038495303918797063</v>
       </c>
       <c r="O27" s="1">
-        <v>8.0592660727258486e-06</v>
+        <v>8.0592660727917681e-06</v>
       </c>
       <c r="P27" s="1">
-        <v>0.00017477400305719809</v>
+        <v>0.00017477400305722108</v>
       </c>
       <c r="Q27" s="1">
-        <v>-0.0001589865983666124</v>
+        <v>-0.00015898659836663192</v>
       </c>
       <c r="R27" s="1">
-        <v>-0.00017147962722392299</v>
+        <v>-0.00017147962722391082</v>
       </c>
       <c r="S27" s="1">
-        <v>-0.00025689511402608028</v>
+        <v>-0.00025689511402574028</v>
       </c>
       <c r="T27" s="1">
-        <v>-0.0001121794469985879</v>
+        <v>-0.00011217944699824789</v>
       </c>
       <c r="U27" s="1">
-        <v>-0.00024002029645060069</v>
+        <v>-0.00024002029645027456</v>
       </c>
       <c r="V27" s="1">
-        <v>-7.1775453925572094e-05</v>
+        <v>-7.1775453925507909e-05</v>
       </c>
       <c r="W27" s="1">
-        <v>-2.7225297011923381e-05</v>
+        <v>-2.7225297011917093e-05</v>
       </c>
       <c r="X27" s="1">
-        <v>-4.2779699290939558e-05</v>
+        <v>-4.2779699290885782e-05</v>
       </c>
       <c r="Y27" s="1">
-        <v>-5.0774667800986993e-05</v>
+        <v>-5.0774667800981355e-05</v>
       </c>
       <c r="Z27" s="1">
-        <v>6.0064881108626463e-05</v>
+        <v>6.0064881108652483e-05</v>
       </c>
       <c r="AA27" s="1">
-        <v>0.00015413976487661774</v>
+        <v>0.00015413976487662728</v>
       </c>
       <c r="AB27" s="1">
-        <v>0.0023795172861101059</v>
+        <v>0.0023795172861101246</v>
       </c>
       <c r="AC27" s="1">
-        <v>0.0017266793839323415</v>
+        <v>0.0017266793839323608</v>
       </c>
       <c r="AD27" s="1">
-        <v>0.0016929055525952089</v>
+        <v>0.0016929055525952306</v>
       </c>
       <c r="AE27" s="1">
-        <v>0.0017559363653602133</v>
+        <v>0.0017559363653602345</v>
       </c>
       <c r="AF27" s="1">
-        <v>-1.9271437142867246e-06</v>
+        <v>-1.9271437142851593e-06</v>
       </c>
       <c r="AG27" s="1">
-        <v>-0.00077977091123139649</v>
+        <v>-0.000779770911232137</v>
       </c>
     </row>
     <row r="28">
@@ -7612,100 +7612,100 @@
         <v>60</v>
       </c>
       <c r="B28" s="1">
-        <v>0.038391967805874061</v>
+        <v>0.038391967805874574</v>
       </c>
       <c r="C28" s="1">
-        <v>-4.9085181256343033e-05</v>
+        <v>-4.9085181256342978e-05</v>
       </c>
       <c r="D28" s="1">
-        <v>-7.0612681292189393e-05</v>
+        <v>-7.0612681292175894e-05</v>
       </c>
       <c r="E28" s="1">
-        <v>6.1016131946174865e-07</v>
+        <v>6.1016131946160762e-07</v>
       </c>
       <c r="F28" s="1">
-        <v>5.3047019707930243e-05</v>
+        <v>5.3047019707982285e-05</v>
       </c>
       <c r="G28" s="1">
-        <v>0.00019794183094271577</v>
+        <v>0.00019794183094276694</v>
       </c>
       <c r="H28" s="1">
-        <v>-5.6172368746205611e-05</v>
+        <v>-5.6172368746156172e-05</v>
       </c>
       <c r="I28" s="1">
-        <v>-0.00018564509010019197</v>
+        <v>-0.00018564509010013386</v>
       </c>
       <c r="J28" s="1">
-        <v>0.00027047740389852685</v>
+        <v>0.0002704774038985236</v>
       </c>
       <c r="K28" s="1">
-        <v>-1.4635770227950231e-05</v>
+        <v>-1.4635770227949615e-05</v>
       </c>
       <c r="L28" s="1">
-        <v>9.7004977714089765e-06</v>
+        <v>9.7004977714067878e-06</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.00031407113203542239</v>
+        <v>-0.00031407113203542249</v>
       </c>
       <c r="N28" s="1">
-        <v>0.00031350607108254482</v>
+        <v>0.00031350607108254823</v>
       </c>
       <c r="O28" s="1">
-        <v>-0.00043240290623325611</v>
+        <v>-0.00043240290623325957</v>
       </c>
       <c r="P28" s="1">
-        <v>9.117931194760928e-05</v>
+        <v>9.1179311947623158e-05</v>
       </c>
       <c r="Q28" s="1">
-        <v>6.4742783925667772e-06</v>
+        <v>6.4742783925656388e-06</v>
       </c>
       <c r="R28" s="1">
-        <v>0.00026445574276653971</v>
+        <v>0.0002644557427666104</v>
       </c>
       <c r="S28" s="1">
-        <v>-0.00055320955251512982</v>
+        <v>-0.00055320955251483145</v>
       </c>
       <c r="T28" s="1">
-        <v>-0.00043573741290494142</v>
+        <v>-0.00043573741290466733</v>
       </c>
       <c r="U28" s="1">
-        <v>-0.00048760358415083152</v>
+        <v>-0.00048760358415053662</v>
       </c>
       <c r="V28" s="1">
-        <v>-0.00061601468137977271</v>
+        <v>-0.0006160146813797068</v>
       </c>
       <c r="W28" s="1">
-        <v>-4.5646462106337451e-05</v>
+        <v>-4.5646462106335608e-05</v>
       </c>
       <c r="X28" s="1">
-        <v>-0.00019339129599773349</v>
+        <v>-0.00019339129599767451</v>
       </c>
       <c r="Y28" s="1">
-        <v>-0.00048271513975417242</v>
+        <v>-0.00048271513975417068</v>
       </c>
       <c r="Z28" s="1">
-        <v>-0.00022508732740438649</v>
+        <v>-0.00022508732740436133</v>
       </c>
       <c r="AA28" s="1">
-        <v>-7.8970394950280201e-05</v>
+        <v>-7.8970394950274346e-05</v>
       </c>
       <c r="AB28" s="1">
-        <v>0.0017266793839323415</v>
+        <v>0.0017266793839323608</v>
       </c>
       <c r="AC28" s="1">
-        <v>0.0035660434791023295</v>
+        <v>0.0035660434791023525</v>
       </c>
       <c r="AD28" s="1">
-        <v>0.0017364670984299896</v>
+        <v>0.0017364670984300126</v>
       </c>
       <c r="AE28" s="1">
-        <v>0.0017430186667035095</v>
+        <v>0.0017430186667035294</v>
       </c>
       <c r="AF28" s="1">
-        <v>-6.3781782425790714e-06</v>
+        <v>-6.3781782425781735e-06</v>
       </c>
       <c r="AG28" s="1">
-        <v>0.0011031335837891913</v>
+        <v>0.0011031335837886488</v>
       </c>
     </row>
     <row r="29">
@@ -7713,100 +7713,100 @@
         <v>61</v>
       </c>
       <c r="B29" s="1">
-        <v>0.088096563246457302</v>
+        <v>0.088096563246456844</v>
       </c>
       <c r="C29" s="1">
-        <v>7.2811379269905498e-05</v>
+        <v>7.2811379269905918e-05</v>
       </c>
       <c r="D29" s="1">
-        <v>-1.5371687661805888e-05</v>
+        <v>-1.5371687661801822e-05</v>
       </c>
       <c r="E29" s="1">
-        <v>6.7560590059206306e-08</v>
+        <v>6.7560590059174966e-08</v>
       </c>
       <c r="F29" s="1">
-        <v>8.6293782535488105e-05</v>
+        <v>8.629378253557831e-05</v>
       </c>
       <c r="G29" s="1">
-        <v>8.5265824404513572e-05</v>
+        <v>8.5265824404611584e-05</v>
       </c>
       <c r="H29" s="1">
-        <v>8.3251848522579788e-05</v>
+        <v>8.3251848522678668e-05</v>
       </c>
       <c r="I29" s="1">
-        <v>5.8868803333590736e-05</v>
+        <v>5.8868803333695686e-05</v>
       </c>
       <c r="J29" s="1">
-        <v>1.4781715064882692e-05</v>
+        <v>1.478171506488688e-05</v>
       </c>
       <c r="K29" s="1">
-        <v>5.1264264244140677e-06</v>
+        <v>5.1264264244125566e-06</v>
       </c>
       <c r="L29" s="1">
-        <v>-3.8721753493472041e-05</v>
+        <v>-3.8721753493470333e-05</v>
       </c>
       <c r="M29" s="1">
-        <v>-1.031219847218427e-05</v>
+        <v>-1.0312198472184744e-05</v>
       </c>
       <c r="N29" s="1">
-        <v>0.00029237774965709483</v>
+        <v>0.0002923777496571002</v>
       </c>
       <c r="O29" s="1">
-        <v>-3.5469225863355575e-05</v>
+        <v>-3.5469225863328686e-05</v>
       </c>
       <c r="P29" s="1">
-        <v>-2.5851851986121105e-05</v>
+        <v>-2.5851851986102674e-05</v>
       </c>
       <c r="Q29" s="1">
-        <v>4.4165492988795709e-05</v>
+        <v>4.4165492988776736e-05</v>
       </c>
       <c r="R29" s="1">
-        <v>-0.00010851448363802929</v>
+        <v>-0.00010851448363802115</v>
       </c>
       <c r="S29" s="1">
-        <v>0.00027550934052472317</v>
+        <v>0.00027550934052488624</v>
       </c>
       <c r="T29" s="1">
-        <v>0.00024185499836162569</v>
+        <v>0.00024185499836178875</v>
       </c>
       <c r="U29" s="1">
-        <v>0.00017844899324374885</v>
+        <v>0.00017844899324389804</v>
       </c>
       <c r="V29" s="1">
-        <v>0.00011058415358735935</v>
+        <v>0.00011058415358738971</v>
       </c>
       <c r="W29" s="1">
-        <v>5.0536034822499707e-05</v>
+        <v>5.0536034822504098e-05</v>
       </c>
       <c r="X29" s="1">
-        <v>-3.1531642576034706e-05</v>
+        <v>-3.1531642576015841e-05</v>
       </c>
       <c r="Y29" s="1">
-        <v>-0.00019523744577627908</v>
+        <v>-0.00019523744577627105</v>
       </c>
       <c r="Z29" s="1">
-        <v>6.3168295775918246e-05</v>
+        <v>6.3168295775933208e-05</v>
       </c>
       <c r="AA29" s="1">
-        <v>-8.1573441071297907e-06</v>
+        <v>-8.1573441071216592e-06</v>
       </c>
       <c r="AB29" s="1">
-        <v>0.0016929055525952089</v>
+        <v>0.0016929055525952306</v>
       </c>
       <c r="AC29" s="1">
-        <v>0.0017364670984299896</v>
+        <v>0.0017364670984300126</v>
       </c>
       <c r="AD29" s="1">
-        <v>0.002722659281811974</v>
+        <v>0.0027226592818120001</v>
       </c>
       <c r="AE29" s="1">
-        <v>0.0017295395639144785</v>
+        <v>0.0017295395639145028</v>
       </c>
       <c r="AF29" s="1">
-        <v>1.9114505873735202e-05</v>
+        <v>1.9114505873737031e-05</v>
       </c>
       <c r="AG29" s="1">
-        <v>-0.0016443894549465412</v>
+        <v>-0.0016443894549470254</v>
       </c>
     </row>
     <row r="30">
@@ -7814,100 +7814,100 @@
         <v>62</v>
       </c>
       <c r="B30" s="1">
-        <v>0.024182676323323212</v>
+        <v>0.024182676323322959</v>
       </c>
       <c r="C30" s="1">
-        <v>-8.0574579766557602e-05</v>
+        <v>-8.057457976655706e-05</v>
       </c>
       <c r="D30" s="1">
-        <v>-3.1569579549181603e-05</v>
+        <v>-3.1569579549175423e-05</v>
       </c>
       <c r="E30" s="1">
-        <v>3.1820888235853339e-07</v>
+        <v>3.1820888235846901e-07</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.00058485491823510524</v>
+        <v>-0.000584854918235048</v>
       </c>
       <c r="G30" s="1">
-        <v>-0.00051547561696388411</v>
+        <v>-0.00051547561696382339</v>
       </c>
       <c r="H30" s="1">
-        <v>-0.00044234699128296515</v>
+        <v>-0.00044234699128291137</v>
       </c>
       <c r="I30" s="1">
-        <v>-0.00061322226182228268</v>
+        <v>-0.00061322226182221502</v>
       </c>
       <c r="J30" s="1">
-        <v>-4.9240939010911653e-05</v>
+        <v>-4.9240939010910745e-05</v>
       </c>
       <c r="K30" s="1">
-        <v>9.6330986387519997e-06</v>
+        <v>9.6330986387510511e-06</v>
       </c>
       <c r="L30" s="1">
-        <v>-9.5503911746879462e-06</v>
+        <v>-9.55039117468777e-06</v>
       </c>
       <c r="M30" s="1">
-        <v>7.8934588127470092e-05</v>
+        <v>7.8934588127470268e-05</v>
       </c>
       <c r="N30" s="1">
-        <v>0.0002841986396675875</v>
+        <v>0.00028419863966759628</v>
       </c>
       <c r="O30" s="1">
-        <v>-8.1705877430851559e-07</v>
+        <v>-8.1705877425126971e-07</v>
       </c>
       <c r="P30" s="1">
-        <v>6.1673252275460874e-05</v>
+        <v>6.1673252275483426e-05</v>
       </c>
       <c r="Q30" s="1">
-        <v>4.9579089101290481e-05</v>
+        <v>4.9579089101279422e-05</v>
       </c>
       <c r="R30" s="1">
-        <v>-0.00016261950767807186</v>
+        <v>-0.00016261950767805598</v>
       </c>
       <c r="S30" s="1">
-        <v>-0.00018162150452560866</v>
+        <v>-0.00018162150452528947</v>
       </c>
       <c r="T30" s="1">
-        <v>-0.00017140635086634881</v>
+        <v>-0.00017140635086601574</v>
       </c>
       <c r="U30" s="1">
-        <v>-0.00034100401916588308</v>
+        <v>-0.00034100401916557083</v>
       </c>
       <c r="V30" s="1">
-        <v>-0.00012933739434734838</v>
+        <v>-0.00012933739434730588</v>
       </c>
       <c r="W30" s="1">
-        <v>2.2562439070754965e-05</v>
+        <v>2.2562439070754857e-05</v>
       </c>
       <c r="X30" s="1">
-        <v>-2.4951340780711862e-05</v>
+        <v>-2.4951340780680637e-05</v>
       </c>
       <c r="Y30" s="1">
-        <v>-0.00013343823562917139</v>
+        <v>-0.00013343823562916575</v>
       </c>
       <c r="Z30" s="1">
-        <v>9.9699912801576047e-05</v>
+        <v>9.9699912801592527e-05</v>
       </c>
       <c r="AA30" s="1">
-        <v>0.00010805658202150286</v>
+        <v>0.00010805658202150915</v>
       </c>
       <c r="AB30" s="1">
-        <v>0.0017559363653602133</v>
+        <v>0.0017559363653602345</v>
       </c>
       <c r="AC30" s="1">
-        <v>0.0017430186667035095</v>
+        <v>0.0017430186667035294</v>
       </c>
       <c r="AD30" s="1">
-        <v>0.0017295395639144785</v>
+        <v>0.0017295395639145028</v>
       </c>
       <c r="AE30" s="1">
-        <v>0.0022578223047643032</v>
+        <v>0.0022578223047643267</v>
       </c>
       <c r="AF30" s="1">
-        <v>-2.0926234334004914e-07</v>
+        <v>-2.0926234333813146e-07</v>
       </c>
       <c r="AG30" s="1">
-        <v>-0.00040889375494234</v>
+        <v>-0.00040889375494300743</v>
       </c>
     </row>
     <row r="31">
@@ -7915,100 +7915,100 @@
         <v>63</v>
       </c>
       <c r="B31" s="1">
-        <v>0.012682414352203266</v>
+        <v>0.012682414352203108</v>
       </c>
       <c r="C31" s="1">
-        <v>9.89090529956304e-06</v>
+        <v>9.8909052995635076e-06</v>
       </c>
       <c r="D31" s="1">
-        <v>-8.9254441796526943e-07</v>
+        <v>-8.925444179634534e-07</v>
       </c>
       <c r="E31" s="1">
-        <v>5.6514015506191151e-09</v>
+        <v>5.6514015506019098e-09</v>
       </c>
       <c r="F31" s="1">
-        <v>1.0700395052566278e-05</v>
+        <v>1.0700395052582975e-05</v>
       </c>
       <c r="G31" s="1">
-        <v>-3.2454133608501336e-08</v>
+        <v>-3.2454133591045681e-08</v>
       </c>
       <c r="H31" s="1">
-        <v>-1.3813260429492097e-06</v>
+        <v>-1.3813260429306699e-06</v>
       </c>
       <c r="I31" s="1">
-        <v>1.5350562552556317e-05</v>
+        <v>1.5350562552577784e-05</v>
       </c>
       <c r="J31" s="1">
-        <v>-2.5883664685689507e-07</v>
+        <v>-2.5883664685555507e-07</v>
       </c>
       <c r="K31" s="1">
-        <v>-4.2959753302346994e-08</v>
+        <v>-4.2959753301461845e-08</v>
       </c>
       <c r="L31" s="1">
-        <v>-1.9952545385008703e-06</v>
+        <v>-1.9952545385016068e-06</v>
       </c>
       <c r="M31" s="1">
-        <v>-9.3031498793091866e-06</v>
+        <v>-9.3031498793098626e-06</v>
       </c>
       <c r="N31" s="1">
-        <v>-1.7544922723330289e-05</v>
+        <v>-1.7544922723328605e-05</v>
       </c>
       <c r="O31" s="1">
-        <v>-1.1490207322627666e-05</v>
+        <v>-1.1490207322604573e-05</v>
       </c>
       <c r="P31" s="1">
-        <v>-5.7854473027461255e-06</v>
+        <v>-5.7854473027423579e-06</v>
       </c>
       <c r="Q31" s="1">
-        <v>1.0211394622058583e-05</v>
+        <v>1.0211394622061497e-05</v>
       </c>
       <c r="R31" s="1">
-        <v>1.4722592374358358e-05</v>
+        <v>1.472259237436152e-05</v>
       </c>
       <c r="S31" s="1">
-        <v>5.4838507387989024e-05</v>
+        <v>5.483850738810872e-05</v>
       </c>
       <c r="T31" s="1">
-        <v>2.863592259376305e-05</v>
+        <v>2.863592259387971e-05</v>
       </c>
       <c r="U31" s="1">
-        <v>2.4363727253978295e-05</v>
+        <v>2.4363727254094955e-05</v>
       </c>
       <c r="V31" s="1">
-        <v>1.299369418641201e-06</v>
+        <v>1.2993694186624514e-06</v>
       </c>
       <c r="W31" s="1">
-        <v>-1.628976240681561e-07</v>
+        <v>-1.6289762406500514e-07</v>
       </c>
       <c r="X31" s="1">
-        <v>-1.3981167166544401e-05</v>
+        <v>-1.3981167166537273e-05</v>
       </c>
       <c r="Y31" s="1">
-        <v>-1.3807850022097426e-05</v>
+        <v>-1.3807850022094208e-05</v>
       </c>
       <c r="Z31" s="1">
-        <v>-1.3740505637078107e-05</v>
+        <v>-1.3740505637072116e-05</v>
       </c>
       <c r="AA31" s="1">
-        <v>-1.04890042444879e-05</v>
+        <v>-1.0489004244484444e-05</v>
       </c>
       <c r="AB31" s="1">
-        <v>-1.9271437142867246e-06</v>
+        <v>-1.9271437142851593e-06</v>
       </c>
       <c r="AC31" s="1">
-        <v>-6.3781782425790714e-06</v>
+        <v>-6.3781782425781735e-06</v>
       </c>
       <c r="AD31" s="1">
-        <v>1.9114505873735202e-05</v>
+        <v>1.9114505873737031e-05</v>
       </c>
       <c r="AE31" s="1">
-        <v>-2.0926234334004914e-07</v>
+        <v>-2.0926234333813146e-07</v>
       </c>
       <c r="AF31" s="1">
-        <v>1.5518248763503343e-05</v>
+        <v>1.5518248763503635e-05</v>
       </c>
       <c r="AG31" s="1">
-        <v>-0.00020404381843700653</v>
+        <v>-0.00020404381843721383</v>
       </c>
     </row>
     <row r="32">
@@ -8016,100 +8016,100 @@
         <v>64</v>
       </c>
       <c r="B32" s="1">
-        <v>-0.00064209715795504607</v>
+        <v>-0.00064209715791063715</v>
       </c>
       <c r="C32" s="1">
-        <v>-0.0010837478335164194</v>
+        <v>-0.0010837478335165916</v>
       </c>
       <c r="D32" s="1">
-        <v>-0.0011764663930049425</v>
+        <v>-0.0011764663930050575</v>
       </c>
       <c r="E32" s="1">
-        <v>1.173248343135216e-05</v>
+        <v>1.1732483431352887e-05</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.033051009480211661</v>
+        <v>-0.033051009480229057</v>
       </c>
       <c r="G32" s="1">
-        <v>-0.033092621769745006</v>
+        <v>-0.033092621769763061</v>
       </c>
       <c r="H32" s="1">
-        <v>-0.03337167446689631</v>
+        <v>-0.033371674466914698</v>
       </c>
       <c r="I32" s="1">
-        <v>-0.034700470401991756</v>
+        <v>-0.034700470402010679</v>
       </c>
       <c r="J32" s="1">
-        <v>0.00027740404537670107</v>
+        <v>0.00027740404537594516</v>
       </c>
       <c r="K32" s="1">
-        <v>-0.00045771073886345453</v>
+        <v>-0.00045771073886348532</v>
       </c>
       <c r="L32" s="1">
-        <v>0.00038421640520633853</v>
+        <v>0.0003842164052062757</v>
       </c>
       <c r="M32" s="1">
-        <v>0.00036637251601717285</v>
+        <v>0.00036637251601745642</v>
       </c>
       <c r="N32" s="1">
-        <v>0.0031175344859868813</v>
+        <v>0.0031175344859850824</v>
       </c>
       <c r="O32" s="1">
-        <v>-0.005751154607528397</v>
+        <v>-0.0057511546075397352</v>
       </c>
       <c r="P32" s="1">
-        <v>-0.0011535020475508433</v>
+        <v>-0.0011535020475529657</v>
       </c>
       <c r="Q32" s="1">
-        <v>0.0001874139609287671</v>
+        <v>0.00018741396092867083</v>
       </c>
       <c r="R32" s="1">
-        <v>0.0014805283891910646</v>
+        <v>0.0014805283891921625</v>
       </c>
       <c r="S32" s="1">
-        <v>-0.020452865841487838</v>
+        <v>-0.020452865841534329</v>
       </c>
       <c r="T32" s="1">
-        <v>-0.020596120860202294</v>
+        <v>-0.020596120860248063</v>
       </c>
       <c r="U32" s="1">
-        <v>-0.021162249863819038</v>
+        <v>-0.021162249863864252</v>
       </c>
       <c r="V32" s="1">
-        <v>-0.011221213583072182</v>
+        <v>-0.011221213583076473</v>
       </c>
       <c r="W32" s="1">
-        <v>-0.0033208616930401904</v>
+        <v>-0.0033208616930412893</v>
       </c>
       <c r="X32" s="1">
-        <v>-0.0054552228789067573</v>
+        <v>-0.0054552228789080549</v>
       </c>
       <c r="Y32" s="1">
-        <v>-0.0014038587316349961</v>
+        <v>-0.0014038587316362106</v>
       </c>
       <c r="Z32" s="1">
-        <v>-0.0035027236299267155</v>
+        <v>-0.0035027236299279602</v>
       </c>
       <c r="AA32" s="1">
-        <v>-0.0019435441378938094</v>
+        <v>-0.0019435441378948849</v>
       </c>
       <c r="AB32" s="1">
-        <v>-0.00077977091123139649</v>
+        <v>-0.000779770911232137</v>
       </c>
       <c r="AC32" s="1">
-        <v>0.0011031335837891913</v>
+        <v>0.0011031335837886488</v>
       </c>
       <c r="AD32" s="1">
-        <v>-0.0016443894549465412</v>
+        <v>-0.0016443894549470254</v>
       </c>
       <c r="AE32" s="1">
-        <v>-0.00040889375494234</v>
+        <v>-0.00040889375494300743</v>
       </c>
       <c r="AF32" s="1">
-        <v>-0.00020404381843700653</v>
+        <v>-0.00020404381843721383</v>
       </c>
       <c r="AG32" s="1">
-        <v>0.086482345347771439</v>
+        <v>0.086482345347846379</v>
       </c>
     </row>
   </sheetData>
